--- a/jogos_2025-07-12.xlsx
+++ b/jogos_2025-07-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="272">
   <si>
     <t>Date</t>
   </si>
@@ -125,60 +125,6 @@
   </si>
   <si>
     <t>awayGoals</t>
-  </si>
-  <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
   </si>
   <si>
     <t>DateTime</t>
@@ -1247,10 +1193,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD92"/>
+  <dimension ref="A1:AL92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1365,79 +1311,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45850</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1452,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L2">
         <v>5.4</v>
@@ -1527,87 +1419,33 @@
         <v>1.27</v>
       </c>
       <c r="AJ2" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK2" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL2">
-        <v>2.1</v>
-      </c>
-      <c r="AM2">
-        <v>1.15</v>
-      </c>
-      <c r="AN2">
-        <v>1.18</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>3</v>
-      </c>
-      <c r="BC2">
-        <v>1.36</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45850.125</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45850</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="F3" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1622,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L3">
         <v>3.3</v>
@@ -1697,87 +1535,33 @@
         <v>1.2</v>
       </c>
       <c r="AJ3" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK3" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL3">
-        <v>1.2</v>
-      </c>
-      <c r="AM3">
-        <v>1.16</v>
-      </c>
-      <c r="AN3">
-        <v>1.22</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>2.5</v>
-      </c>
-      <c r="BC3">
-        <v>1.53</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45850.16666666666</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45850</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="F4" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1792,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L4">
         <v>4.9</v>
@@ -1867,87 +1651,33 @@
         <v>1.35</v>
       </c>
       <c r="AJ4" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK4" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL4">
-        <v>1.18</v>
-      </c>
-      <c r="AM4">
-        <v>1.12</v>
-      </c>
-      <c r="AN4">
-        <v>1.17</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>2.71</v>
-      </c>
-      <c r="BC4">
-        <v>1.41</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45850.25</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45850</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F5" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1962,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L5">
         <v>1.61</v>
@@ -2037,87 +1767,33 @@
         <v>1.06</v>
       </c>
       <c r="AJ5" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK5" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL5">
-        <v>1.11</v>
-      </c>
-      <c r="AM5">
-        <v>1.24</v>
-      </c>
-      <c r="AN5">
-        <v>2.14</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>1.29</v>
-      </c>
-      <c r="AQ5">
-        <v>1.57</v>
-      </c>
-      <c r="AR5">
-        <v>1.95</v>
-      </c>
-      <c r="AS5">
-        <v>2.52</v>
-      </c>
-      <c r="AT5">
-        <v>3.46</v>
-      </c>
-      <c r="AU5">
-        <v>3.06</v>
-      </c>
-      <c r="AV5">
-        <v>2.22</v>
-      </c>
-      <c r="AW5">
-        <v>1.76</v>
-      </c>
-      <c r="AX5">
-        <v>1.44</v>
-      </c>
-      <c r="AY5">
-        <v>1.22</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.53</v>
-      </c>
-      <c r="BC5">
-        <v>3</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45850.25</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45850</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="F6" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2132,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L6">
         <v>3.34</v>
@@ -2207,87 +1883,33 @@
         <v>1.11</v>
       </c>
       <c r="AJ6" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK6" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL6">
-        <v>1.66</v>
-      </c>
-      <c r="AM6">
-        <v>1.25</v>
-      </c>
-      <c r="AN6">
-        <v>1.31</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>1.23</v>
-      </c>
-      <c r="AQ6">
-        <v>1.48</v>
-      </c>
-      <c r="AR6">
-        <v>1.82</v>
-      </c>
-      <c r="AS6">
-        <v>2.3</v>
-      </c>
-      <c r="AT6">
-        <v>3.08</v>
-      </c>
-      <c r="AU6">
-        <v>3.4</v>
-      </c>
-      <c r="AV6">
-        <v>2.42</v>
-      </c>
-      <c r="AW6">
-        <v>1.88</v>
-      </c>
-      <c r="AX6">
-        <v>1.53</v>
-      </c>
-      <c r="AY6">
-        <v>1.29</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>2.2</v>
-      </c>
-      <c r="BC6">
-        <v>1.78</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45850.25</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45850</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="F7" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2302,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L7">
         <v>2.61</v>
@@ -2377,87 +1999,33 @@
         <v>1.05</v>
       </c>
       <c r="AJ7" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK7" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL7">
-        <v>1.48</v>
-      </c>
-      <c r="AM7">
-        <v>1.3</v>
-      </c>
-      <c r="AN7">
-        <v>1.38</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>1.22</v>
-      </c>
-      <c r="AQ7">
-        <v>1.46</v>
-      </c>
-      <c r="AR7">
-        <v>1.8</v>
-      </c>
-      <c r="AS7">
-        <v>2.26</v>
-      </c>
-      <c r="AT7">
-        <v>3</v>
-      </c>
-      <c r="AU7">
-        <v>3.49</v>
-      </c>
-      <c r="AV7">
-        <v>2.46</v>
-      </c>
-      <c r="AW7">
-        <v>1.91</v>
-      </c>
-      <c r="AX7">
-        <v>1.55</v>
-      </c>
-      <c r="AY7">
-        <v>1.3</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>2.13</v>
-      </c>
-      <c r="BC7">
-        <v>1.95</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45850.25</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45850</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2472,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L8">
         <v>1.54</v>
@@ -2547,87 +2115,33 @@
         <v>1.08</v>
       </c>
       <c r="AJ8" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK8" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL8">
-        <v>1.12</v>
-      </c>
-      <c r="AM8">
-        <v>1.2</v>
-      </c>
-      <c r="AN8">
-        <v>2.24</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>1.14</v>
-      </c>
-      <c r="AQ8">
-        <v>1.34</v>
-      </c>
-      <c r="AR8">
-        <v>1.62</v>
-      </c>
-      <c r="AS8">
-        <v>2</v>
-      </c>
-      <c r="AT8">
-        <v>2.55</v>
-      </c>
-      <c r="AU8">
-        <v>4.22</v>
-      </c>
-      <c r="AV8">
-        <v>2.86</v>
-      </c>
-      <c r="AW8">
-        <v>2.14</v>
-      </c>
-      <c r="AX8">
-        <v>1.72</v>
-      </c>
-      <c r="AY8">
-        <v>1.42</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>1.44</v>
-      </c>
-      <c r="BC8">
-        <v>2.92</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45850.25347222222</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45850</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="F9" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2642,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L9">
         <v>2.95</v>
@@ -2717,87 +2231,33 @@
         <v>1.05</v>
       </c>
       <c r="AJ9" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK9" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL9">
-        <v>1.59</v>
-      </c>
-      <c r="AM9">
-        <v>1.28</v>
-      </c>
-      <c r="AN9">
-        <v>1.32</v>
-      </c>
-      <c r="AO9">
-        <v>-1</v>
-      </c>
-      <c r="AP9">
-        <v>1.35</v>
-      </c>
-      <c r="AQ9">
-        <v>1.67</v>
-      </c>
-      <c r="AR9">
-        <v>2.09</v>
-      </c>
-      <c r="AS9">
-        <v>2.75</v>
-      </c>
-      <c r="AT9">
-        <v>3.88</v>
-      </c>
-      <c r="AU9">
-        <v>2.79</v>
-      </c>
-      <c r="AV9">
-        <v>2.07</v>
-      </c>
-      <c r="AW9">
-        <v>1.66</v>
-      </c>
-      <c r="AX9">
-        <v>1.36</v>
-      </c>
-      <c r="AY9">
-        <v>1.17</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>2.2</v>
-      </c>
-      <c r="BC9">
-        <v>1.88</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45850.27083333334</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45850</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F10" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2812,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L10">
         <v>1.34</v>
@@ -2887,87 +2347,33 @@
         <v>1.18</v>
       </c>
       <c r="AJ10" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK10" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL10">
-        <v>1.05</v>
-      </c>
-      <c r="AM10">
-        <v>1.15</v>
-      </c>
-      <c r="AN10">
-        <v>2.82</v>
-      </c>
-      <c r="AO10">
-        <v>-1</v>
-      </c>
-      <c r="AP10">
-        <v>1.38</v>
-      </c>
-      <c r="AQ10">
-        <v>1.71</v>
-      </c>
-      <c r="AR10">
-        <v>2.15</v>
-      </c>
-      <c r="AS10">
-        <v>2.86</v>
-      </c>
-      <c r="AT10">
-        <v>4.08</v>
-      </c>
-      <c r="AU10">
-        <v>2.69</v>
-      </c>
-      <c r="AV10">
-        <v>2.02</v>
-      </c>
-      <c r="AW10">
-        <v>1.61</v>
-      </c>
-      <c r="AX10">
-        <v>1.33</v>
-      </c>
-      <c r="AY10">
-        <v>1.15</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.33</v>
-      </c>
-      <c r="BC10">
-        <v>3.32</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45850.29166666666</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45850</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="F11" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2982,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L11">
         <v>2.13</v>
@@ -3057,87 +2463,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ11" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK11" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL11">
-        <v>1.28</v>
-      </c>
-      <c r="AM11">
-        <v>1.33</v>
-      </c>
-      <c r="AN11">
-        <v>1.56</v>
-      </c>
-      <c r="AO11">
-        <v>-1</v>
-      </c>
-      <c r="AP11">
-        <v>1.28</v>
-      </c>
-      <c r="AQ11">
-        <v>1.56</v>
-      </c>
-      <c r="AR11">
-        <v>1.94</v>
-      </c>
-      <c r="AS11">
-        <v>2.49</v>
-      </c>
-      <c r="AT11">
-        <v>3.41</v>
-      </c>
-      <c r="AU11">
-        <v>3.1</v>
-      </c>
-      <c r="AV11">
-        <v>2.24</v>
-      </c>
-      <c r="AW11">
-        <v>1.77</v>
-      </c>
-      <c r="AX11">
-        <v>1.45</v>
-      </c>
-      <c r="AY11">
-        <v>1.23</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>1.88</v>
-      </c>
-      <c r="BC11">
-        <v>2.4</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45850.29166666666</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45850</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="F12" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3152,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L12">
         <v>1.82</v>
@@ -3227,87 +2579,33 @@
         <v>1.05</v>
       </c>
       <c r="AJ12" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK12" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL12">
-        <v>1.22</v>
-      </c>
-      <c r="AM12">
-        <v>1.27</v>
-      </c>
-      <c r="AN12">
-        <v>1.77</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>1.51</v>
-      </c>
-      <c r="AQ12">
-        <v>1.95</v>
-      </c>
-      <c r="AR12">
-        <v>2.45</v>
-      </c>
-      <c r="AS12">
-        <v>3.4</v>
-      </c>
-      <c r="AT12">
-        <v>5.08</v>
-      </c>
-      <c r="AU12">
-        <v>2.34</v>
-      </c>
-      <c r="AV12">
-        <v>1.85</v>
-      </c>
-      <c r="AW12">
-        <v>1.46</v>
-      </c>
-      <c r="AX12">
-        <v>1.23</v>
-      </c>
-      <c r="AY12">
-        <v>1.08</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>1.67</v>
-      </c>
-      <c r="BC12">
-        <v>2.6</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45850.29166666666</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45850</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="F13" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3322,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3397,87 +2695,33 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK13" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>0</v>
-      </c>
-      <c r="BC13">
-        <v>0</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45850.29166666666</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45850</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F14" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3492,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L14">
         <v>3.15</v>
@@ -3567,87 +2811,33 @@
         <v>1.07</v>
       </c>
       <c r="AJ14" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK14" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL14">
-        <v>1.56</v>
-      </c>
-      <c r="AM14">
-        <v>1.3</v>
-      </c>
-      <c r="AN14">
-        <v>1.32</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>1.27</v>
-      </c>
-      <c r="AQ14">
-        <v>1.54</v>
-      </c>
-      <c r="AR14">
-        <v>1.9</v>
-      </c>
-      <c r="AS14">
-        <v>2.43</v>
-      </c>
-      <c r="AT14">
-        <v>3.3</v>
-      </c>
-      <c r="AU14">
-        <v>3.18</v>
-      </c>
-      <c r="AV14">
-        <v>2.29</v>
-      </c>
-      <c r="AW14">
-        <v>1.8</v>
-      </c>
-      <c r="AX14">
-        <v>1.47</v>
-      </c>
-      <c r="AY14">
-        <v>1.25</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>2.25</v>
-      </c>
-      <c r="BC14">
-        <v>1.83</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45850.29166666666</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45850</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" t="s">
         <v>93</v>
       </c>
-      <c r="D15" t="s">
-        <v>111</v>
-      </c>
       <c r="E15" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="F15" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3662,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L15">
         <v>1.45</v>
@@ -3737,87 +2927,33 @@
         <v>1.18</v>
       </c>
       <c r="AJ15" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK15" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL15">
-        <v>1.13</v>
-      </c>
-      <c r="AM15">
-        <v>1.15</v>
-      </c>
-      <c r="AN15">
-        <v>2.5</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>1.34</v>
-      </c>
-      <c r="AQ15">
-        <v>1.58</v>
-      </c>
-      <c r="AR15">
-        <v>1.95</v>
-      </c>
-      <c r="AS15">
-        <v>2.45</v>
-      </c>
-      <c r="AT15">
-        <v>3.15</v>
-      </c>
-      <c r="AU15">
-        <v>2.9</v>
-      </c>
-      <c r="AV15">
-        <v>2.18</v>
-      </c>
-      <c r="AW15">
-        <v>1.74</v>
-      </c>
-      <c r="AX15">
-        <v>1.48</v>
-      </c>
-      <c r="AY15">
-        <v>1.29</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>1.36</v>
-      </c>
-      <c r="BC15">
-        <v>3.25</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45850.29166666666</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45850</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F16" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3832,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L16">
         <v>3.16</v>
@@ -3907,87 +3043,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ16" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK16" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL16">
-        <v>1.51</v>
-      </c>
-      <c r="AM16">
-        <v>1.36</v>
-      </c>
-      <c r="AN16">
-        <v>1.29</v>
-      </c>
-      <c r="AO16">
-        <v>-1</v>
-      </c>
-      <c r="AP16">
-        <v>1.35</v>
-      </c>
-      <c r="AQ16">
-        <v>1.67</v>
-      </c>
-      <c r="AR16">
-        <v>2.09</v>
-      </c>
-      <c r="AS16">
-        <v>2.75</v>
-      </c>
-      <c r="AT16">
-        <v>3.88</v>
-      </c>
-      <c r="AU16">
-        <v>2.79</v>
-      </c>
-      <c r="AV16">
-        <v>2.07</v>
-      </c>
-      <c r="AW16">
-        <v>1.66</v>
-      </c>
-      <c r="AX16">
-        <v>1.36</v>
-      </c>
-      <c r="AY16">
-        <v>1.17</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>2.4</v>
-      </c>
-      <c r="BC16">
-        <v>1.95</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45850.29166666666</v>
       </c>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>45850</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="F17" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -4002,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L17">
         <v>2.64</v>
@@ -4077,87 +3159,33 @@
         <v>1.05</v>
       </c>
       <c r="AJ17" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK17" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL17">
-        <v>1.38</v>
-      </c>
-      <c r="AM17">
-        <v>1.3</v>
-      </c>
-      <c r="AN17">
-        <v>1.48</v>
-      </c>
-      <c r="AO17">
-        <v>-1</v>
-      </c>
-      <c r="AP17">
-        <v>1.47</v>
-      </c>
-      <c r="AQ17">
-        <v>1.88</v>
-      </c>
-      <c r="AR17">
-        <v>2.35</v>
-      </c>
-      <c r="AS17">
-        <v>3.21</v>
-      </c>
-      <c r="AT17">
-        <v>4.73</v>
-      </c>
-      <c r="AU17">
-        <v>2.44</v>
-      </c>
-      <c r="AV17">
-        <v>1.92</v>
-      </c>
-      <c r="AW17">
-        <v>1.51</v>
-      </c>
-      <c r="AX17">
-        <v>1.26</v>
-      </c>
-      <c r="AY17">
-        <v>1.1</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>2.05</v>
-      </c>
-      <c r="BC17">
-        <v>2.05</v>
-      </c>
-      <c r="BD17" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL17" s="3">
         <v>45850.29166666666</v>
       </c>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:38">
       <c r="A18" s="2">
         <v>45850</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E18" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="F18" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -4172,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L18">
         <v>1.68</v>
@@ -4247,87 +3275,33 @@
         <v>1.11</v>
       </c>
       <c r="AJ18" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK18" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL18">
-        <v>1.17</v>
-      </c>
-      <c r="AM18">
-        <v>1.21</v>
-      </c>
-      <c r="AN18">
-        <v>2.03</v>
-      </c>
-      <c r="AO18">
-        <v>-1</v>
-      </c>
-      <c r="AP18">
-        <v>1.51</v>
-      </c>
-      <c r="AQ18">
-        <v>1.95</v>
-      </c>
-      <c r="AR18">
-        <v>2.45</v>
-      </c>
-      <c r="AS18">
-        <v>3.4</v>
-      </c>
-      <c r="AT18">
-        <v>5.08</v>
-      </c>
-      <c r="AU18">
-        <v>2.34</v>
-      </c>
-      <c r="AV18">
-        <v>1.85</v>
-      </c>
-      <c r="AW18">
-        <v>1.46</v>
-      </c>
-      <c r="AX18">
-        <v>1.23</v>
-      </c>
-      <c r="AY18">
-        <v>1.08</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>1.51</v>
-      </c>
-      <c r="BC18">
-        <v>2.58</v>
-      </c>
-      <c r="BD18" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL18" s="3">
         <v>45850.29166666666</v>
       </c>
     </row>
-    <row r="19" spans="1:56">
+    <row r="19" spans="1:38">
       <c r="A19" s="2">
         <v>45850</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" t="s">
         <v>111</v>
       </c>
-      <c r="E19" t="s">
-        <v>129</v>
-      </c>
       <c r="F19" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -4342,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L19">
         <v>2.86</v>
@@ -4417,87 +3391,33 @@
         <v>1.08</v>
       </c>
       <c r="AJ19" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK19" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL19">
-        <v>1.46</v>
-      </c>
-      <c r="AM19">
-        <v>1.28</v>
-      </c>
-      <c r="AN19">
-        <v>1.41</v>
-      </c>
-      <c r="AO19">
-        <v>-1</v>
-      </c>
-      <c r="AP19">
-        <v>1.25</v>
-      </c>
-      <c r="AQ19">
-        <v>1.51</v>
-      </c>
-      <c r="AR19">
-        <v>1.87</v>
-      </c>
-      <c r="AS19">
-        <v>2.38</v>
-      </c>
-      <c r="AT19">
-        <v>3.21</v>
-      </c>
-      <c r="AU19">
-        <v>3.26</v>
-      </c>
-      <c r="AV19">
-        <v>2.34</v>
-      </c>
-      <c r="AW19">
-        <v>1.83</v>
-      </c>
-      <c r="AX19">
-        <v>1.49</v>
-      </c>
-      <c r="AY19">
-        <v>1.26</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>2.03</v>
-      </c>
-      <c r="BC19">
-        <v>1.97</v>
-      </c>
-      <c r="BD19" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL19" s="3">
         <v>45850.29166666666</v>
       </c>
     </row>
-    <row r="20" spans="1:56">
+    <row r="20" spans="1:38">
       <c r="A20" s="2">
         <v>45850</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="F20" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4512,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L20">
         <v>1.82</v>
@@ -4587,87 +3507,33 @@
         <v>1.13</v>
       </c>
       <c r="AJ20" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK20" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL20">
-        <v>1.25</v>
-      </c>
-      <c r="AM20">
-        <v>1.22</v>
-      </c>
-      <c r="AN20">
-        <v>1.8</v>
-      </c>
-      <c r="AO20">
-        <v>-1</v>
-      </c>
-      <c r="AP20">
-        <v>1.26</v>
-      </c>
-      <c r="AQ20">
-        <v>1.52</v>
-      </c>
-      <c r="AR20">
-        <v>1.88</v>
-      </c>
-      <c r="AS20">
-        <v>2.39</v>
-      </c>
-      <c r="AT20">
-        <v>3.24</v>
-      </c>
-      <c r="AU20">
-        <v>3.24</v>
-      </c>
-      <c r="AV20">
-        <v>2.33</v>
-      </c>
-      <c r="AW20">
-        <v>1.82</v>
-      </c>
-      <c r="AX20">
-        <v>1.49</v>
-      </c>
-      <c r="AY20">
-        <v>1.26</v>
-      </c>
-      <c r="AZ20">
-        <v>0</v>
-      </c>
-      <c r="BA20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>1.62</v>
-      </c>
-      <c r="BC20">
-        <v>2.29</v>
-      </c>
-      <c r="BD20" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL20" s="3">
         <v>45850.3125</v>
       </c>
     </row>
-    <row r="21" spans="1:56">
+    <row r="21" spans="1:38">
       <c r="A21" s="2">
         <v>45850</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="F21" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4682,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -4757,87 +3623,33 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK21" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>0</v>
-      </c>
-      <c r="AO21">
-        <v>-1</v>
-      </c>
-      <c r="AP21">
-        <v>0</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21">
-        <v>0</v>
-      </c>
-      <c r="AV21">
-        <v>0</v>
-      </c>
-      <c r="AW21">
-        <v>0</v>
-      </c>
-      <c r="AX21">
-        <v>0</v>
-      </c>
-      <c r="AY21">
-        <v>0</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>0</v>
-      </c>
-      <c r="BC21">
-        <v>0</v>
-      </c>
-      <c r="BD21" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL21" s="3">
         <v>45850.33333333334</v>
       </c>
     </row>
-    <row r="22" spans="1:56">
+    <row r="22" spans="1:38">
       <c r="A22" s="2">
         <v>45850</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="F22" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4852,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -4927,87 +3739,33 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK22" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
-        <v>0</v>
-      </c>
-      <c r="AN22">
-        <v>0</v>
-      </c>
-      <c r="AO22">
-        <v>-1</v>
-      </c>
-      <c r="AP22">
-        <v>0</v>
-      </c>
-      <c r="AQ22">
-        <v>0</v>
-      </c>
-      <c r="AR22">
-        <v>0</v>
-      </c>
-      <c r="AS22">
-        <v>0</v>
-      </c>
-      <c r="AT22">
-        <v>0</v>
-      </c>
-      <c r="AU22">
-        <v>0</v>
-      </c>
-      <c r="AV22">
-        <v>0</v>
-      </c>
-      <c r="AW22">
-        <v>0</v>
-      </c>
-      <c r="AX22">
-        <v>0</v>
-      </c>
-      <c r="AY22">
-        <v>0</v>
-      </c>
-      <c r="AZ22">
-        <v>0</v>
-      </c>
-      <c r="BA22">
-        <v>0</v>
-      </c>
-      <c r="BB22">
-        <v>0</v>
-      </c>
-      <c r="BC22">
-        <v>0</v>
-      </c>
-      <c r="BD22" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL22" s="3">
         <v>45850.33333333334</v>
       </c>
     </row>
-    <row r="23" spans="1:56">
+    <row r="23" spans="1:38">
       <c r="A23" s="2">
         <v>45850</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="F23" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -5022,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L23">
         <v>4.2</v>
@@ -5097,87 +3855,33 @@
         <v>1.18</v>
       </c>
       <c r="AJ23" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK23" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL23">
-        <v>1.22</v>
-      </c>
-      <c r="AM23">
-        <v>1.22</v>
-      </c>
-      <c r="AN23">
-        <v>1.22</v>
-      </c>
-      <c r="AO23">
-        <v>-1</v>
-      </c>
-      <c r="AP23">
-        <v>0</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23">
-        <v>0</v>
-      </c>
-      <c r="AV23">
-        <v>0</v>
-      </c>
-      <c r="AW23">
-        <v>0</v>
-      </c>
-      <c r="AX23">
-        <v>0</v>
-      </c>
-      <c r="AY23">
-        <v>0</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
-      </c>
-      <c r="BA23">
-        <v>0</v>
-      </c>
-      <c r="BB23">
-        <v>2.5</v>
-      </c>
-      <c r="BC23">
-        <v>1.53</v>
-      </c>
-      <c r="BD23" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL23" s="3">
         <v>45850.35416666666</v>
       </c>
     </row>
-    <row r="24" spans="1:56">
+    <row r="24" spans="1:38">
       <c r="A24" s="2">
         <v>45850</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="F24" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -5192,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -5267,87 +3971,33 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK24" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>0</v>
-      </c>
-      <c r="AN24">
-        <v>0</v>
-      </c>
-      <c r="AO24">
-        <v>-1</v>
-      </c>
-      <c r="AP24">
-        <v>0</v>
-      </c>
-      <c r="AQ24">
-        <v>0</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24">
-        <v>0</v>
-      </c>
-      <c r="AV24">
-        <v>0</v>
-      </c>
-      <c r="AW24">
-        <v>0</v>
-      </c>
-      <c r="AX24">
-        <v>0</v>
-      </c>
-      <c r="AY24">
-        <v>0</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>0</v>
-      </c>
-      <c r="BC24">
-        <v>0</v>
-      </c>
-      <c r="BD24" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL24" s="3">
         <v>45850.35416666666</v>
       </c>
     </row>
-    <row r="25" spans="1:56">
+    <row r="25" spans="1:38">
       <c r="A25" s="2">
         <v>45850</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F25" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5362,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -5437,87 +4087,33 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK25" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>0</v>
-      </c>
-      <c r="AO25">
-        <v>-1</v>
-      </c>
-      <c r="AP25">
-        <v>0</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25">
-        <v>0</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
-      </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
-      <c r="AX25">
-        <v>0</v>
-      </c>
-      <c r="AY25">
-        <v>0</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>0</v>
-      </c>
-      <c r="BC25">
-        <v>0</v>
-      </c>
-      <c r="BD25" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL25" s="3">
         <v>45850.35416666666</v>
       </c>
     </row>
-    <row r="26" spans="1:56">
+    <row r="26" spans="1:38">
       <c r="A26" s="2">
         <v>45850</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E26" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="F26" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5532,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L26">
         <v>4.62</v>
@@ -5607,87 +4203,33 @@
         <v>1.09</v>
       </c>
       <c r="AJ26" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK26" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL26">
-        <v>1.29</v>
-      </c>
-      <c r="AM26">
-        <v>1.24</v>
-      </c>
-      <c r="AN26">
-        <v>1.22</v>
-      </c>
-      <c r="AO26">
-        <v>-1</v>
-      </c>
-      <c r="AP26">
-        <v>0</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26">
-        <v>0</v>
-      </c>
-      <c r="AV26">
-        <v>0</v>
-      </c>
-      <c r="AW26">
-        <v>0</v>
-      </c>
-      <c r="AX26">
-        <v>0</v>
-      </c>
-      <c r="AY26">
-        <v>0</v>
-      </c>
-      <c r="AZ26">
-        <v>0</v>
-      </c>
-      <c r="BA26">
-        <v>0</v>
-      </c>
-      <c r="BB26">
-        <v>2.84</v>
-      </c>
-      <c r="BC26">
-        <v>1.56</v>
-      </c>
-      <c r="BD26" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL26" s="3">
         <v>45850.375</v>
       </c>
     </row>
-    <row r="27" spans="1:56">
+    <row r="27" spans="1:38">
       <c r="A27" s="2">
         <v>45850</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="F27" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5702,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L27">
         <v>2.4</v>
@@ -5777,87 +4319,33 @@
         <v>1.14</v>
       </c>
       <c r="AJ27" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK27" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL27">
-        <v>1.44</v>
-      </c>
-      <c r="AM27">
-        <v>1.25</v>
-      </c>
-      <c r="AN27">
-        <v>1.53</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>1.15</v>
-      </c>
-      <c r="AQ27">
-        <v>1.27</v>
-      </c>
-      <c r="AR27">
-        <v>1.48</v>
-      </c>
-      <c r="AS27">
-        <v>1.75</v>
-      </c>
-      <c r="AT27">
-        <v>2.17</v>
-      </c>
-      <c r="AU27">
-        <v>4.6</v>
-      </c>
-      <c r="AV27">
-        <v>3.3</v>
-      </c>
-      <c r="AW27">
-        <v>2.48</v>
-      </c>
-      <c r="AX27">
-        <v>1.95</v>
-      </c>
-      <c r="AY27">
-        <v>1.6</v>
-      </c>
-      <c r="AZ27">
-        <v>0</v>
-      </c>
-      <c r="BA27">
-        <v>0</v>
-      </c>
-      <c r="BB27">
-        <v>1.8</v>
-      </c>
-      <c r="BC27">
-        <v>2.1</v>
-      </c>
-      <c r="BD27" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL27" s="3">
         <v>45850.41666666666</v>
       </c>
     </row>
-    <row r="28" spans="1:56">
+    <row r="28" spans="1:38">
       <c r="A28" s="2">
         <v>45850</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="F28" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -5872,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L28">
         <v>2.01</v>
@@ -5947,87 +4435,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ28" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK28" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL28">
-        <v>1.3</v>
-      </c>
-      <c r="AM28">
-        <v>0</v>
-      </c>
-      <c r="AN28">
-        <v>1.82</v>
-      </c>
-      <c r="AO28">
-        <v>-1</v>
-      </c>
-      <c r="AP28">
-        <v>0</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28">
-        <v>0</v>
-      </c>
-      <c r="AV28">
-        <v>0</v>
-      </c>
-      <c r="AW28">
-        <v>0</v>
-      </c>
-      <c r="AX28">
-        <v>0</v>
-      </c>
-      <c r="AY28">
-        <v>0</v>
-      </c>
-      <c r="AZ28">
-        <v>0</v>
-      </c>
-      <c r="BA28">
-        <v>0</v>
-      </c>
-      <c r="BB28">
-        <v>0</v>
-      </c>
-      <c r="BC28">
-        <v>0</v>
-      </c>
-      <c r="BD28" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL28" s="3">
         <v>45850.41666666666</v>
       </c>
     </row>
-    <row r="29" spans="1:56">
+    <row r="29" spans="1:38">
       <c r="A29" s="2">
         <v>45850</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="F29" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6042,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L29">
         <v>1.2</v>
@@ -6117,87 +4551,33 @@
         <v>1.22</v>
       </c>
       <c r="AJ29" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK29" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL29">
-        <v>1.18</v>
-      </c>
-      <c r="AM29">
-        <v>1.16</v>
-      </c>
-      <c r="AN29">
-        <v>3.2</v>
-      </c>
-      <c r="AO29">
-        <v>-1</v>
-      </c>
-      <c r="AP29">
-        <v>1.26</v>
-      </c>
-      <c r="AQ29">
-        <v>1.45</v>
-      </c>
-      <c r="AR29">
-        <v>1.95</v>
-      </c>
-      <c r="AS29">
-        <v>2.18</v>
-      </c>
-      <c r="AT29">
-        <v>2.73</v>
-      </c>
-      <c r="AU29">
-        <v>3.4</v>
-      </c>
-      <c r="AV29">
-        <v>2.57</v>
-      </c>
-      <c r="AW29">
-        <v>2.01</v>
-      </c>
-      <c r="AX29">
-        <v>1.64</v>
-      </c>
-      <c r="AY29">
-        <v>1.4</v>
-      </c>
-      <c r="AZ29">
-        <v>0</v>
-      </c>
-      <c r="BA29">
-        <v>0</v>
-      </c>
-      <c r="BB29">
-        <v>1.25</v>
-      </c>
-      <c r="BC29">
-        <v>4.33</v>
-      </c>
-      <c r="BD29" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL29" s="3">
         <v>45850.45833333334</v>
       </c>
     </row>
-    <row r="30" spans="1:56">
+    <row r="30" spans="1:38">
       <c r="A30" s="2">
         <v>45850</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E30" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F30" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6212,7 +4592,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L30">
         <v>1.26</v>
@@ -6287,87 +4667,33 @@
         <v>1.44</v>
       </c>
       <c r="AJ30" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK30" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL30">
-        <v>1.05</v>
-      </c>
-      <c r="AM30">
-        <v>1.11</v>
-      </c>
-      <c r="AN30">
-        <v>3.75</v>
-      </c>
-      <c r="AO30">
-        <v>-1</v>
-      </c>
-      <c r="AP30">
-        <v>1.2</v>
-      </c>
-      <c r="AQ30">
-        <v>1.38</v>
-      </c>
-      <c r="AR30">
-        <v>1.64</v>
-      </c>
-      <c r="AS30">
-        <v>2.01</v>
-      </c>
-      <c r="AT30">
-        <v>2.5</v>
-      </c>
-      <c r="AU30">
-        <v>3.9</v>
-      </c>
-      <c r="AV30">
-        <v>2.8</v>
-      </c>
-      <c r="AW30">
-        <v>2.18</v>
-      </c>
-      <c r="AX30">
-        <v>1.75</v>
-      </c>
-      <c r="AY30">
-        <v>1.47</v>
-      </c>
-      <c r="AZ30">
-        <v>0</v>
-      </c>
-      <c r="BA30">
-        <v>0</v>
-      </c>
-      <c r="BB30">
-        <v>1.22</v>
-      </c>
-      <c r="BC30">
-        <v>4</v>
-      </c>
-      <c r="BD30" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL30" s="3">
         <v>45850.45833333334</v>
       </c>
     </row>
-    <row r="31" spans="1:56">
+    <row r="31" spans="1:38">
       <c r="A31" s="2">
         <v>45850</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="F31" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -6382,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -6457,87 +4783,33 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK31" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>0</v>
-      </c>
-      <c r="AN31">
-        <v>0</v>
-      </c>
-      <c r="AO31">
-        <v>-1</v>
-      </c>
-      <c r="AP31">
-        <v>0</v>
-      </c>
-      <c r="AQ31">
-        <v>0</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
-      <c r="AS31">
-        <v>0</v>
-      </c>
-      <c r="AT31">
-        <v>0</v>
-      </c>
-      <c r="AU31">
-        <v>0</v>
-      </c>
-      <c r="AV31">
-        <v>0</v>
-      </c>
-      <c r="AW31">
-        <v>0</v>
-      </c>
-      <c r="AX31">
-        <v>0</v>
-      </c>
-      <c r="AY31">
-        <v>0</v>
-      </c>
-      <c r="AZ31">
-        <v>0</v>
-      </c>
-      <c r="BA31">
-        <v>0</v>
-      </c>
-      <c r="BB31">
-        <v>0</v>
-      </c>
-      <c r="BC31">
-        <v>0</v>
-      </c>
-      <c r="BD31" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL31" s="3">
         <v>45850.45833333334</v>
       </c>
     </row>
-    <row r="32" spans="1:56">
+    <row r="32" spans="1:38">
       <c r="A32" s="2">
         <v>45850</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E32" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="F32" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -6552,7 +4824,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L32">
         <v>3.22</v>
@@ -6627,87 +4899,33 @@
         <v>1.04</v>
       </c>
       <c r="AJ32" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK32" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL32">
-        <v>1.3</v>
-      </c>
-      <c r="AM32">
-        <v>1.25</v>
-      </c>
-      <c r="AN32">
-        <v>1.15</v>
-      </c>
-      <c r="AO32">
-        <v>-1</v>
-      </c>
-      <c r="AP32">
-        <v>0</v>
-      </c>
-      <c r="AQ32">
-        <v>0</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32">
-        <v>0</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
-      </c>
-      <c r="AU32">
-        <v>0</v>
-      </c>
-      <c r="AV32">
-        <v>0</v>
-      </c>
-      <c r="AW32">
-        <v>0</v>
-      </c>
-      <c r="AX32">
-        <v>0</v>
-      </c>
-      <c r="AY32">
-        <v>0</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>3.18</v>
-      </c>
-      <c r="BC32">
-        <v>1.47</v>
-      </c>
-      <c r="BD32" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL32" s="3">
         <v>45850.5</v>
       </c>
     </row>
-    <row r="33" spans="1:56">
+    <row r="33" spans="1:38">
       <c r="A33" s="2">
         <v>45850</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E33" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="F33" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -6722,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L33">
         <v>1.46</v>
@@ -6797,87 +5015,33 @@
         <v>1.3</v>
       </c>
       <c r="AJ33" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK33" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL33">
-        <v>1.07</v>
-      </c>
-      <c r="AM33">
-        <v>1.1</v>
-      </c>
-      <c r="AN33">
-        <v>3.3</v>
-      </c>
-      <c r="AO33">
-        <v>-1</v>
-      </c>
-      <c r="AP33">
-        <v>1.12</v>
-      </c>
-      <c r="AQ33">
-        <v>1.24</v>
-      </c>
-      <c r="AR33">
-        <v>1.44</v>
-      </c>
-      <c r="AS33">
-        <v>1.71</v>
-      </c>
-      <c r="AT33">
-        <v>2.1</v>
-      </c>
-      <c r="AU33">
-        <v>5</v>
-      </c>
-      <c r="AV33">
-        <v>3.5</v>
-      </c>
-      <c r="AW33">
-        <v>2.6</v>
-      </c>
-      <c r="AX33">
-        <v>2.06</v>
-      </c>
-      <c r="AY33">
-        <v>1.68</v>
-      </c>
-      <c r="AZ33">
-        <v>0</v>
-      </c>
-      <c r="BA33">
-        <v>0</v>
-      </c>
-      <c r="BB33">
-        <v>1.22</v>
-      </c>
-      <c r="BC33">
-        <v>4</v>
-      </c>
-      <c r="BD33" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL33" s="3">
         <v>45850.52083333334</v>
       </c>
     </row>
-    <row r="34" spans="1:56">
+    <row r="34" spans="1:38">
       <c r="A34" s="2">
         <v>45850</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E34" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F34" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -6892,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L34">
         <v>2.55</v>
@@ -6967,87 +5131,33 @@
         <v>1.06</v>
       </c>
       <c r="AJ34" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK34" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL34">
-        <v>1.35</v>
-      </c>
-      <c r="AM34">
-        <v>1.3</v>
-      </c>
-      <c r="AN34">
-        <v>1.5</v>
-      </c>
-      <c r="AO34">
-        <v>-1</v>
-      </c>
-      <c r="AP34">
-        <v>0</v>
-      </c>
-      <c r="AQ34">
-        <v>0</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34">
-        <v>0</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
-      </c>
-      <c r="AU34">
-        <v>0</v>
-      </c>
-      <c r="AV34">
-        <v>0</v>
-      </c>
-      <c r="AW34">
-        <v>0</v>
-      </c>
-      <c r="AX34">
-        <v>0</v>
-      </c>
-      <c r="AY34">
-        <v>0</v>
-      </c>
-      <c r="AZ34">
-        <v>0</v>
-      </c>
-      <c r="BA34">
-        <v>0</v>
-      </c>
-      <c r="BB34">
-        <v>2.03</v>
-      </c>
-      <c r="BC34">
-        <v>2.02</v>
-      </c>
-      <c r="BD34" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL34" s="3">
         <v>45850.54166666666</v>
       </c>
     </row>
-    <row r="35" spans="1:56">
+    <row r="35" spans="1:38">
       <c r="A35" s="2">
         <v>45850</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D35" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E35" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="F35" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -7062,7 +5172,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L35">
         <v>2.27</v>
@@ -7137,87 +5247,33 @@
         <v>1.07</v>
       </c>
       <c r="AJ35" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK35" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL35">
-        <v>1.35</v>
-      </c>
-      <c r="AM35">
-        <v>1.3</v>
-      </c>
-      <c r="AN35">
-        <v>1.55</v>
-      </c>
-      <c r="AO35">
-        <v>-1</v>
-      </c>
-      <c r="AP35">
-        <v>0</v>
-      </c>
-      <c r="AQ35">
-        <v>0</v>
-      </c>
-      <c r="AR35">
-        <v>0</v>
-      </c>
-      <c r="AS35">
-        <v>0</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35">
-        <v>0</v>
-      </c>
-      <c r="AV35">
-        <v>0</v>
-      </c>
-      <c r="AW35">
-        <v>0</v>
-      </c>
-      <c r="AX35">
-        <v>0</v>
-      </c>
-      <c r="AY35">
-        <v>0</v>
-      </c>
-      <c r="AZ35">
-        <v>0</v>
-      </c>
-      <c r="BA35">
-        <v>0</v>
-      </c>
-      <c r="BB35">
-        <v>1.91</v>
-      </c>
-      <c r="BC35">
-        <v>2.18</v>
-      </c>
-      <c r="BD35" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL35" s="3">
         <v>45850.54166666666</v>
       </c>
     </row>
-    <row r="36" spans="1:56">
+    <row r="36" spans="1:38">
       <c r="A36" s="2">
         <v>45850</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E36" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="F36" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -7232,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L36">
         <v>2.62</v>
@@ -7307,87 +5363,33 @@
         <v>1.1</v>
       </c>
       <c r="AJ36" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK36" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL36">
-        <v>1.44</v>
-      </c>
-      <c r="AM36">
-        <v>1.25</v>
-      </c>
-      <c r="AN36">
-        <v>1.5</v>
-      </c>
-      <c r="AO36">
-        <v>-1</v>
-      </c>
-      <c r="AP36">
-        <v>1.22</v>
-      </c>
-      <c r="AQ36">
-        <v>1.42</v>
-      </c>
-      <c r="AR36">
-        <v>1.69</v>
-      </c>
-      <c r="AS36">
-        <v>2.09</v>
-      </c>
-      <c r="AT36">
-        <v>2.62</v>
-      </c>
-      <c r="AU36">
-        <v>3.7</v>
-      </c>
-      <c r="AV36">
-        <v>2.67</v>
-      </c>
-      <c r="AW36">
-        <v>2.09</v>
-      </c>
-      <c r="AX36">
-        <v>1.69</v>
-      </c>
-      <c r="AY36">
-        <v>1.43</v>
-      </c>
-      <c r="AZ36">
-        <v>0</v>
-      </c>
-      <c r="BA36">
-        <v>0</v>
-      </c>
-      <c r="BB36">
-        <v>1.83</v>
-      </c>
-      <c r="BC36">
-        <v>2.1</v>
-      </c>
-      <c r="BD36" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL36" s="3">
         <v>45850.54166666666</v>
       </c>
     </row>
-    <row r="37" spans="1:56">
+    <row r="37" spans="1:38">
       <c r="A37" s="2">
         <v>45850</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E37" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="F37" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -7402,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L37">
         <v>3.27</v>
@@ -7477,87 +5479,33 @@
         <v>1.04</v>
       </c>
       <c r="AJ37" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK37" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL37">
-        <v>1.33</v>
-      </c>
-      <c r="AM37">
-        <v>1.36</v>
-      </c>
-      <c r="AN37">
-        <v>1.4</v>
-      </c>
-      <c r="AO37">
-        <v>-1</v>
-      </c>
-      <c r="AP37">
-        <v>1.52</v>
-      </c>
-      <c r="AQ37">
-        <v>1.86</v>
-      </c>
-      <c r="AR37">
-        <v>2.35</v>
-      </c>
-      <c r="AS37">
-        <v>3.05</v>
-      </c>
-      <c r="AT37">
-        <v>4.1</v>
-      </c>
-      <c r="AU37">
-        <v>2.33</v>
-      </c>
-      <c r="AV37">
-        <v>1.82</v>
-      </c>
-      <c r="AW37">
-        <v>1.5</v>
-      </c>
-      <c r="AX37">
-        <v>1.3</v>
-      </c>
-      <c r="AY37">
-        <v>1.18</v>
-      </c>
-      <c r="AZ37">
-        <v>0</v>
-      </c>
-      <c r="BA37">
-        <v>0</v>
-      </c>
-      <c r="BB37">
-        <v>2.1</v>
-      </c>
-      <c r="BC37">
-        <v>2.1</v>
-      </c>
-      <c r="BD37" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL37" s="3">
         <v>45850.625</v>
       </c>
     </row>
-    <row r="38" spans="1:56">
+    <row r="38" spans="1:38">
       <c r="A38" s="2">
         <v>45850</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D38" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E38" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="F38" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -7572,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L38">
         <v>2.75</v>
@@ -7647,87 +5595,33 @@
         <v>1.03</v>
       </c>
       <c r="AJ38" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK38" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL38">
-        <v>1.42</v>
-      </c>
-      <c r="AM38">
-        <v>1.4</v>
-      </c>
-      <c r="AN38">
-        <v>1.38</v>
-      </c>
-      <c r="AO38">
-        <v>-1</v>
-      </c>
-      <c r="AP38">
-        <v>0</v>
-      </c>
-      <c r="AQ38">
-        <v>0</v>
-      </c>
-      <c r="AR38">
-        <v>0</v>
-      </c>
-      <c r="AS38">
-        <v>0</v>
-      </c>
-      <c r="AT38">
-        <v>0</v>
-      </c>
-      <c r="AU38">
-        <v>0</v>
-      </c>
-      <c r="AV38">
-        <v>0</v>
-      </c>
-      <c r="AW38">
-        <v>0</v>
-      </c>
-      <c r="AX38">
-        <v>0</v>
-      </c>
-      <c r="AY38">
-        <v>0</v>
-      </c>
-      <c r="AZ38">
-        <v>0</v>
-      </c>
-      <c r="BA38">
-        <v>0</v>
-      </c>
-      <c r="BB38">
-        <v>2.25</v>
-      </c>
-      <c r="BC38">
-        <v>2.05</v>
-      </c>
-      <c r="BD38" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL38" s="3">
         <v>45850.625</v>
       </c>
     </row>
-    <row r="39" spans="1:56">
+    <row r="39" spans="1:38">
       <c r="A39" s="2">
         <v>45850</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D39" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E39" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="F39" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -7742,7 +5636,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L39">
         <v>1.57</v>
@@ -7817,87 +5711,33 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK39" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL39">
-        <v>0</v>
-      </c>
-      <c r="AM39">
-        <v>0</v>
-      </c>
-      <c r="AN39">
-        <v>0</v>
-      </c>
-      <c r="AO39">
-        <v>-1</v>
-      </c>
-      <c r="AP39">
-        <v>0</v>
-      </c>
-      <c r="AQ39">
-        <v>0</v>
-      </c>
-      <c r="AR39">
-        <v>0</v>
-      </c>
-      <c r="AS39">
-        <v>0</v>
-      </c>
-      <c r="AT39">
-        <v>0</v>
-      </c>
-      <c r="AU39">
-        <v>0</v>
-      </c>
-      <c r="AV39">
-        <v>0</v>
-      </c>
-      <c r="AW39">
-        <v>0</v>
-      </c>
-      <c r="AX39">
-        <v>0</v>
-      </c>
-      <c r="AY39">
-        <v>0</v>
-      </c>
-      <c r="AZ39">
-        <v>0</v>
-      </c>
-      <c r="BA39">
-        <v>0</v>
-      </c>
-      <c r="BB39">
-        <v>0</v>
-      </c>
-      <c r="BC39">
-        <v>0</v>
-      </c>
-      <c r="BD39" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL39" s="3">
         <v>45850.625</v>
       </c>
     </row>
-    <row r="40" spans="1:56">
+    <row r="40" spans="1:38">
       <c r="A40" s="2">
         <v>45850</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D40" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E40" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="F40" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -7912,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L40">
         <v>1.85</v>
@@ -7987,87 +5827,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ40" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK40" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL40">
-        <v>1.36</v>
-      </c>
-      <c r="AM40">
-        <v>0</v>
-      </c>
-      <c r="AN40">
-        <v>1.85</v>
-      </c>
-      <c r="AO40">
-        <v>-1</v>
-      </c>
-      <c r="AP40">
-        <v>1.49</v>
-      </c>
-      <c r="AQ40">
-        <v>1.83</v>
-      </c>
-      <c r="AR40">
-        <v>2.32</v>
-      </c>
-      <c r="AS40">
-        <v>3.05</v>
-      </c>
-      <c r="AT40">
-        <v>4.1</v>
-      </c>
-      <c r="AU40">
-        <v>2.4</v>
-      </c>
-      <c r="AV40">
-        <v>1.85</v>
-      </c>
-      <c r="AW40">
-        <v>1.52</v>
-      </c>
-      <c r="AX40">
-        <v>1.32</v>
-      </c>
-      <c r="AY40">
-        <v>1.19</v>
-      </c>
-      <c r="AZ40">
-        <v>0</v>
-      </c>
-      <c r="BA40">
-        <v>0</v>
-      </c>
-      <c r="BB40">
-        <v>1.62</v>
-      </c>
-      <c r="BC40">
-        <v>3.2</v>
-      </c>
-      <c r="BD40" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL40" s="3">
         <v>45850.625</v>
       </c>
     </row>
-    <row r="41" spans="1:56">
+    <row r="41" spans="1:38">
       <c r="A41" s="2">
         <v>45850</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D41" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E41" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="F41" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -8082,7 +5868,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L41">
         <v>2.41</v>
@@ -8157,87 +5943,33 @@
         <v>1.02</v>
       </c>
       <c r="AJ41" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK41" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL41">
-        <v>1.5</v>
-      </c>
-      <c r="AM41">
-        <v>0</v>
-      </c>
-      <c r="AN41">
-        <v>1.44</v>
-      </c>
-      <c r="AO41">
-        <v>-1</v>
-      </c>
-      <c r="AP41">
-        <v>1.61</v>
-      </c>
-      <c r="AQ41">
-        <v>2</v>
-      </c>
-      <c r="AR41">
-        <v>2.63</v>
-      </c>
-      <c r="AS41">
-        <v>3.45</v>
-      </c>
-      <c r="AT41">
-        <v>4.8</v>
-      </c>
-      <c r="AU41">
-        <v>2.15</v>
-      </c>
-      <c r="AV41">
-        <v>1.7</v>
-      </c>
-      <c r="AW41">
-        <v>1.43</v>
-      </c>
-      <c r="AX41">
-        <v>1.25</v>
-      </c>
-      <c r="AY41">
-        <v>1.14</v>
-      </c>
-      <c r="AZ41">
-        <v>0</v>
-      </c>
-      <c r="BA41">
-        <v>0</v>
-      </c>
-      <c r="BB41">
-        <v>1.95</v>
-      </c>
-      <c r="BC41">
-        <v>2.5</v>
-      </c>
-      <c r="BD41" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL41" s="3">
         <v>45850.625</v>
       </c>
     </row>
-    <row r="42" spans="1:56">
+    <row r="42" spans="1:38">
       <c r="A42" s="2">
         <v>45850</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D42" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E42" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="F42" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -8252,7 +5984,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L42">
         <v>3.58</v>
@@ -8327,87 +6059,33 @@
         <v>1.05</v>
       </c>
       <c r="AJ42" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK42" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL42">
-        <v>1.3</v>
-      </c>
-      <c r="AM42">
-        <v>0</v>
-      </c>
-      <c r="AN42">
-        <v>1.13</v>
-      </c>
-      <c r="AO42">
-        <v>-1</v>
-      </c>
-      <c r="AP42">
-        <v>0</v>
-      </c>
-      <c r="AQ42">
-        <v>0</v>
-      </c>
-      <c r="AR42">
-        <v>0</v>
-      </c>
-      <c r="AS42">
-        <v>0</v>
-      </c>
-      <c r="AT42">
-        <v>0</v>
-      </c>
-      <c r="AU42">
-        <v>0</v>
-      </c>
-      <c r="AV42">
-        <v>0</v>
-      </c>
-      <c r="AW42">
-        <v>0</v>
-      </c>
-      <c r="AX42">
-        <v>0</v>
-      </c>
-      <c r="AY42">
-        <v>0</v>
-      </c>
-      <c r="AZ42">
-        <v>0</v>
-      </c>
-      <c r="BA42">
-        <v>0</v>
-      </c>
-      <c r="BB42">
-        <v>3.6</v>
-      </c>
-      <c r="BC42">
-        <v>1.44</v>
-      </c>
-      <c r="BD42" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL42" s="3">
         <v>45850.64583333334</v>
       </c>
     </row>
-    <row r="43" spans="1:56">
+    <row r="43" spans="1:38">
       <c r="A43" s="2">
         <v>45850</v>
       </c>
       <c r="B43" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D43" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E43" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="F43" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -8422,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L43">
         <v>2.6</v>
@@ -8497,87 +6175,33 @@
         <v>1.08</v>
       </c>
       <c r="AJ43" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK43" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL43">
-        <v>1.3</v>
-      </c>
-      <c r="AM43">
-        <v>1.25</v>
-      </c>
-      <c r="AN43">
-        <v>1.45</v>
-      </c>
-      <c r="AO43">
-        <v>-1</v>
-      </c>
-      <c r="AP43">
-        <v>0</v>
-      </c>
-      <c r="AQ43">
-        <v>0</v>
-      </c>
-      <c r="AR43">
-        <v>0</v>
-      </c>
-      <c r="AS43">
-        <v>0</v>
-      </c>
-      <c r="AT43">
-        <v>0</v>
-      </c>
-      <c r="AU43">
-        <v>0</v>
-      </c>
-      <c r="AV43">
-        <v>0</v>
-      </c>
-      <c r="AW43">
-        <v>0</v>
-      </c>
-      <c r="AX43">
-        <v>0</v>
-      </c>
-      <c r="AY43">
-        <v>0</v>
-      </c>
-      <c r="AZ43">
-        <v>0</v>
-      </c>
-      <c r="BA43">
-        <v>0</v>
-      </c>
-      <c r="BB43">
-        <v>2.1</v>
-      </c>
-      <c r="BC43">
-        <v>1.95</v>
-      </c>
-      <c r="BD43" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL43" s="3">
         <v>45850.64583333334</v>
       </c>
     </row>
-    <row r="44" spans="1:56">
+    <row r="44" spans="1:38">
       <c r="A44" s="2">
         <v>45850</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D44" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E44" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="F44" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -8592,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L44">
         <v>1.7</v>
@@ -8667,87 +6291,33 @@
         <v>1.04</v>
       </c>
       <c r="AJ44" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK44" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL44">
-        <v>1.33</v>
-      </c>
-      <c r="AM44">
-        <v>0</v>
-      </c>
-      <c r="AN44">
-        <v>1.9</v>
-      </c>
-      <c r="AO44">
-        <v>-1</v>
-      </c>
-      <c r="AP44">
-        <v>1.71</v>
-      </c>
-      <c r="AQ44">
-        <v>2.17</v>
-      </c>
-      <c r="AR44">
-        <v>2.8</v>
-      </c>
-      <c r="AS44">
-        <v>3.8</v>
-      </c>
-      <c r="AT44">
-        <v>5.1</v>
-      </c>
-      <c r="AU44">
-        <v>2</v>
-      </c>
-      <c r="AV44">
-        <v>1.6</v>
-      </c>
-      <c r="AW44">
-        <v>1.36</v>
-      </c>
-      <c r="AX44">
-        <v>1.22</v>
-      </c>
-      <c r="AY44">
-        <v>1.12</v>
-      </c>
-      <c r="AZ44">
-        <v>0</v>
-      </c>
-      <c r="BA44">
-        <v>0</v>
-      </c>
-      <c r="BB44">
-        <v>1.57</v>
-      </c>
-      <c r="BC44">
-        <v>3.4</v>
-      </c>
-      <c r="BD44" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL44" s="3">
         <v>45850.64583333334</v>
       </c>
     </row>
-    <row r="45" spans="1:56">
+    <row r="45" spans="1:38">
       <c r="A45" s="2">
         <v>45850</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D45" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E45" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="F45" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -8762,7 +6332,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L45">
         <v>2.03</v>
@@ -8837,87 +6407,33 @@
         <v>1.03</v>
       </c>
       <c r="AJ45" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK45" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL45">
-        <v>1.32</v>
-      </c>
-      <c r="AM45">
-        <v>0</v>
-      </c>
-      <c r="AN45">
-        <v>1.53</v>
-      </c>
-      <c r="AO45">
-        <v>-1</v>
-      </c>
-      <c r="AP45">
-        <v>0</v>
-      </c>
-      <c r="AQ45">
-        <v>0</v>
-      </c>
-      <c r="AR45">
-        <v>0</v>
-      </c>
-      <c r="AS45">
-        <v>0</v>
-      </c>
-      <c r="AT45">
-        <v>0</v>
-      </c>
-      <c r="AU45">
-        <v>0</v>
-      </c>
-      <c r="AV45">
-        <v>0</v>
-      </c>
-      <c r="AW45">
-        <v>0</v>
-      </c>
-      <c r="AX45">
-        <v>0</v>
-      </c>
-      <c r="AY45">
-        <v>0</v>
-      </c>
-      <c r="AZ45">
-        <v>0</v>
-      </c>
-      <c r="BA45">
-        <v>0</v>
-      </c>
-      <c r="BB45">
-        <v>1.83</v>
-      </c>
-      <c r="BC45">
-        <v>2.6</v>
-      </c>
-      <c r="BD45" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL45" s="3">
         <v>45850.64583333334</v>
       </c>
     </row>
-    <row r="46" spans="1:56">
+    <row r="46" spans="1:38">
       <c r="A46" s="2">
         <v>45850</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="D46" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E46" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="F46" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -8932,7 +6448,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L46">
         <v>4.6</v>
@@ -9007,87 +6523,33 @@
         <v>1.04</v>
       </c>
       <c r="AJ46" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK46" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL46">
-        <v>1.3</v>
-      </c>
-      <c r="AM46">
-        <v>1.25</v>
-      </c>
-      <c r="AN46">
-        <v>1.15</v>
-      </c>
-      <c r="AO46">
-        <v>-1</v>
-      </c>
-      <c r="AP46">
-        <v>1.4</v>
-      </c>
-      <c r="AQ46">
-        <v>1.66</v>
-      </c>
-      <c r="AR46">
-        <v>4.15</v>
-      </c>
-      <c r="AS46">
-        <v>5.95</v>
-      </c>
-      <c r="AT46">
-        <v>6.41</v>
-      </c>
-      <c r="AU46">
-        <v>2.65</v>
-      </c>
-      <c r="AV46">
-        <v>2.04</v>
-      </c>
-      <c r="AW46">
-        <v>1.17</v>
-      </c>
-      <c r="AX46">
-        <v>1.08</v>
-      </c>
-      <c r="AY46">
-        <v>1.03</v>
-      </c>
-      <c r="AZ46">
-        <v>0</v>
-      </c>
-      <c r="BA46">
-        <v>0</v>
-      </c>
-      <c r="BB46">
-        <v>3</v>
-      </c>
-      <c r="BC46">
-        <v>1.57</v>
-      </c>
-      <c r="BD46" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL46" s="3">
         <v>45850.65625</v>
       </c>
     </row>
-    <row r="47" spans="1:56">
+    <row r="47" spans="1:38">
       <c r="A47" s="2">
         <v>45850</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D47" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E47" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="F47" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -9102,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L47">
         <v>2.24</v>
@@ -9177,87 +6639,33 @@
         <v>0</v>
       </c>
       <c r="AJ47" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK47" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL47">
-        <v>0</v>
-      </c>
-      <c r="AM47">
-        <v>0</v>
-      </c>
-      <c r="AN47">
-        <v>0</v>
-      </c>
-      <c r="AO47">
-        <v>-1</v>
-      </c>
-      <c r="AP47">
-        <v>0</v>
-      </c>
-      <c r="AQ47">
-        <v>0</v>
-      </c>
-      <c r="AR47">
-        <v>0</v>
-      </c>
-      <c r="AS47">
-        <v>0</v>
-      </c>
-      <c r="AT47">
-        <v>0</v>
-      </c>
-      <c r="AU47">
-        <v>0</v>
-      </c>
-      <c r="AV47">
-        <v>0</v>
-      </c>
-      <c r="AW47">
-        <v>0</v>
-      </c>
-      <c r="AX47">
-        <v>0</v>
-      </c>
-      <c r="AY47">
-        <v>0</v>
-      </c>
-      <c r="AZ47">
-        <v>0</v>
-      </c>
-      <c r="BA47">
-        <v>0</v>
-      </c>
-      <c r="BB47">
-        <v>1.67</v>
-      </c>
-      <c r="BC47">
-        <v>2.38</v>
-      </c>
-      <c r="BD47" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL47" s="3">
         <v>45850.66666666666</v>
       </c>
     </row>
-    <row r="48" spans="1:56">
+    <row r="48" spans="1:38">
       <c r="A48" s="2">
         <v>45850</v>
       </c>
       <c r="B48" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D48" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E48" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="F48" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -9272,7 +6680,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L48">
         <v>1.8</v>
@@ -9347,87 +6755,33 @@
         <v>0</v>
       </c>
       <c r="AJ48" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK48" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL48">
-        <v>0</v>
-      </c>
-      <c r="AM48">
-        <v>0</v>
-      </c>
-      <c r="AN48">
-        <v>0</v>
-      </c>
-      <c r="AO48">
-        <v>-1</v>
-      </c>
-      <c r="AP48">
-        <v>0</v>
-      </c>
-      <c r="AQ48">
-        <v>0</v>
-      </c>
-      <c r="AR48">
-        <v>0</v>
-      </c>
-      <c r="AS48">
-        <v>0</v>
-      </c>
-      <c r="AT48">
-        <v>0</v>
-      </c>
-      <c r="AU48">
-        <v>0</v>
-      </c>
-      <c r="AV48">
-        <v>0</v>
-      </c>
-      <c r="AW48">
-        <v>0</v>
-      </c>
-      <c r="AX48">
-        <v>0</v>
-      </c>
-      <c r="AY48">
-        <v>0</v>
-      </c>
-      <c r="AZ48">
-        <v>0</v>
-      </c>
-      <c r="BA48">
-        <v>0</v>
-      </c>
-      <c r="BB48">
-        <v>1.53</v>
-      </c>
-      <c r="BC48">
-        <v>3.4</v>
-      </c>
-      <c r="BD48" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL48" s="3">
         <v>45850.66666666666</v>
       </c>
     </row>
-    <row r="49" spans="1:56">
+    <row r="49" spans="1:38">
       <c r="A49" s="2">
         <v>45850</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D49" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E49" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="F49" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -9442,7 +6796,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L49">
         <v>2.3</v>
@@ -9517,87 +6871,33 @@
         <v>1.08</v>
       </c>
       <c r="AJ49" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK49" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL49">
-        <v>1.37</v>
-      </c>
-      <c r="AM49">
-        <v>1.31</v>
-      </c>
-      <c r="AN49">
-        <v>1.58</v>
-      </c>
-      <c r="AO49">
-        <v>-1</v>
-      </c>
-      <c r="AP49">
-        <v>1.24</v>
-      </c>
-      <c r="AQ49">
-        <v>1.44</v>
-      </c>
-      <c r="AR49">
-        <v>1.78</v>
-      </c>
-      <c r="AS49">
-        <v>2.35</v>
-      </c>
-      <c r="AT49">
-        <v>3.2</v>
-      </c>
-      <c r="AU49">
-        <v>3.6</v>
-      </c>
-      <c r="AV49">
-        <v>2.45</v>
-      </c>
-      <c r="AW49">
-        <v>1.85</v>
-      </c>
-      <c r="AX49">
-        <v>1.49</v>
-      </c>
-      <c r="AY49">
-        <v>1.28</v>
-      </c>
-      <c r="AZ49">
-        <v>0</v>
-      </c>
-      <c r="BA49">
-        <v>0</v>
-      </c>
-      <c r="BB49">
-        <v>1.87</v>
-      </c>
-      <c r="BC49">
-        <v>2.2</v>
-      </c>
-      <c r="BD49" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL49" s="3">
         <v>45850.66666666666</v>
       </c>
     </row>
-    <row r="50" spans="1:56">
+    <row r="50" spans="1:38">
       <c r="A50" s="2">
         <v>45850</v>
       </c>
       <c r="B50" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D50" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E50" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="F50" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -9612,7 +6912,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L50">
         <v>1.74</v>
@@ -9687,87 +6987,33 @@
         <v>1.03</v>
       </c>
       <c r="AJ50" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK50" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL50">
-        <v>1.36</v>
-      </c>
-      <c r="AM50">
-        <v>1.35</v>
-      </c>
-      <c r="AN50">
-        <v>1.75</v>
-      </c>
-      <c r="AO50">
-        <v>-1</v>
-      </c>
-      <c r="AP50">
-        <v>1.21</v>
-      </c>
-      <c r="AQ50">
-        <v>1.44</v>
-      </c>
-      <c r="AR50">
-        <v>1.99</v>
-      </c>
-      <c r="AS50">
-        <v>2.15</v>
-      </c>
-      <c r="AT50">
-        <v>2.94</v>
-      </c>
-      <c r="AU50">
-        <v>3.56</v>
-      </c>
-      <c r="AV50">
-        <v>2.5</v>
-      </c>
-      <c r="AW50">
-        <v>1.93</v>
-      </c>
-      <c r="AX50">
-        <v>1.57</v>
-      </c>
-      <c r="AY50">
-        <v>1.32</v>
-      </c>
-      <c r="AZ50">
-        <v>0</v>
-      </c>
-      <c r="BA50">
-        <v>0</v>
-      </c>
-      <c r="BB50">
-        <v>1.67</v>
-      </c>
-      <c r="BC50">
-        <v>2.88</v>
-      </c>
-      <c r="BD50" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL50" s="3">
         <v>45850.66666666666</v>
       </c>
     </row>
-    <row r="51" spans="1:56">
+    <row r="51" spans="1:38">
       <c r="A51" s="2">
         <v>45850</v>
       </c>
       <c r="B51" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D51" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E51" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="F51" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -9782,7 +7028,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -9857,87 +7103,33 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK51" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL51">
-        <v>0</v>
-      </c>
-      <c r="AM51">
-        <v>0</v>
-      </c>
-      <c r="AN51">
-        <v>0</v>
-      </c>
-      <c r="AO51">
-        <v>-1</v>
-      </c>
-      <c r="AP51">
-        <v>0</v>
-      </c>
-      <c r="AQ51">
-        <v>0</v>
-      </c>
-      <c r="AR51">
-        <v>0</v>
-      </c>
-      <c r="AS51">
-        <v>0</v>
-      </c>
-      <c r="AT51">
-        <v>0</v>
-      </c>
-      <c r="AU51">
-        <v>0</v>
-      </c>
-      <c r="AV51">
-        <v>0</v>
-      </c>
-      <c r="AW51">
-        <v>0</v>
-      </c>
-      <c r="AX51">
-        <v>0</v>
-      </c>
-      <c r="AY51">
-        <v>0</v>
-      </c>
-      <c r="AZ51">
-        <v>0</v>
-      </c>
-      <c r="BA51">
-        <v>0</v>
-      </c>
-      <c r="BB51">
-        <v>0</v>
-      </c>
-      <c r="BC51">
-        <v>0</v>
-      </c>
-      <c r="BD51" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL51" s="3">
         <v>45850.66666666666</v>
       </c>
     </row>
-    <row r="52" spans="1:56">
+    <row r="52" spans="1:38">
       <c r="A52" s="2">
         <v>45850</v>
       </c>
       <c r="B52" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D52" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E52" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="F52" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -9952,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L52">
         <v>1.59</v>
@@ -10027,87 +7219,33 @@
         <v>1.07</v>
       </c>
       <c r="AJ52" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK52" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL52">
-        <v>1.3</v>
-      </c>
-      <c r="AM52">
-        <v>1.28</v>
-      </c>
-      <c r="AN52">
-        <v>2.1</v>
-      </c>
-      <c r="AO52">
-        <v>-1</v>
-      </c>
-      <c r="AP52">
-        <v>1.28</v>
-      </c>
-      <c r="AQ52">
-        <v>1.5</v>
-      </c>
-      <c r="AR52">
-        <v>1.88</v>
-      </c>
-      <c r="AS52">
-        <v>2.5</v>
-      </c>
-      <c r="AT52">
-        <v>3.5</v>
-      </c>
-      <c r="AU52">
-        <v>3.2</v>
-      </c>
-      <c r="AV52">
-        <v>2.3</v>
-      </c>
-      <c r="AW52">
-        <v>1.75</v>
-      </c>
-      <c r="AX52">
-        <v>1.44</v>
-      </c>
-      <c r="AY52">
-        <v>1.24</v>
-      </c>
-      <c r="AZ52">
-        <v>0</v>
-      </c>
-      <c r="BA52">
-        <v>0</v>
-      </c>
-      <c r="BB52">
-        <v>1.44</v>
-      </c>
-      <c r="BC52">
-        <v>3.25</v>
-      </c>
-      <c r="BD52" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL52" s="3">
         <v>45850.6875</v>
       </c>
     </row>
-    <row r="53" spans="1:56">
+    <row r="53" spans="1:38">
       <c r="A53" s="2">
         <v>45850</v>
       </c>
       <c r="B53" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D53" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E53" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="F53" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -10122,7 +7260,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -10197,87 +7335,33 @@
         <v>0</v>
       </c>
       <c r="AJ53" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK53" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL53">
-        <v>0</v>
-      </c>
-      <c r="AM53">
-        <v>0</v>
-      </c>
-      <c r="AN53">
-        <v>0</v>
-      </c>
-      <c r="AO53">
-        <v>-1</v>
-      </c>
-      <c r="AP53">
-        <v>0</v>
-      </c>
-      <c r="AQ53">
-        <v>0</v>
-      </c>
-      <c r="AR53">
-        <v>0</v>
-      </c>
-      <c r="AS53">
-        <v>0</v>
-      </c>
-      <c r="AT53">
-        <v>0</v>
-      </c>
-      <c r="AU53">
-        <v>0</v>
-      </c>
-      <c r="AV53">
-        <v>0</v>
-      </c>
-      <c r="AW53">
-        <v>0</v>
-      </c>
-      <c r="AX53">
-        <v>0</v>
-      </c>
-      <c r="AY53">
-        <v>0</v>
-      </c>
-      <c r="AZ53">
-        <v>0</v>
-      </c>
-      <c r="BA53">
-        <v>0</v>
-      </c>
-      <c r="BB53">
-        <v>0</v>
-      </c>
-      <c r="BC53">
-        <v>0</v>
-      </c>
-      <c r="BD53" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL53" s="3">
         <v>45850.70833333334</v>
       </c>
     </row>
-    <row r="54" spans="1:56">
+    <row r="54" spans="1:38">
       <c r="A54" s="2">
         <v>45850</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D54" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E54" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="F54" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -10292,7 +7376,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L54">
         <v>2.05</v>
@@ -10367,87 +7451,33 @@
         <v>1.03</v>
       </c>
       <c r="AJ54" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK54" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL54">
-        <v>1.35</v>
-      </c>
-      <c r="AM54">
-        <v>1.33</v>
-      </c>
-      <c r="AN54">
-        <v>1.62</v>
-      </c>
-      <c r="AO54">
-        <v>-1</v>
-      </c>
-      <c r="AP54">
-        <v>1.13</v>
-      </c>
-      <c r="AQ54">
-        <v>1.25</v>
-      </c>
-      <c r="AR54">
-        <v>1.44</v>
-      </c>
-      <c r="AS54">
-        <v>1.7</v>
-      </c>
-      <c r="AT54">
-        <v>2.08</v>
-      </c>
-      <c r="AU54">
-        <v>4.9</v>
-      </c>
-      <c r="AV54">
-        <v>3.45</v>
-      </c>
-      <c r="AW54">
-        <v>2.55</v>
-      </c>
-      <c r="AX54">
-        <v>2</v>
-      </c>
-      <c r="AY54">
-        <v>1.66</v>
-      </c>
-      <c r="AZ54">
-        <v>0</v>
-      </c>
-      <c r="BA54">
-        <v>0</v>
-      </c>
-      <c r="BB54">
-        <v>1.8</v>
-      </c>
-      <c r="BC54">
-        <v>2.4</v>
-      </c>
-      <c r="BD54" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL54" s="3">
         <v>45850.70833333334</v>
       </c>
     </row>
-    <row r="55" spans="1:56">
+    <row r="55" spans="1:38">
       <c r="A55" s="2">
         <v>45850</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D55" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E55" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="F55" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -10462,7 +7492,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L55">
         <v>2.2</v>
@@ -10537,87 +7567,33 @@
         <v>1.03</v>
       </c>
       <c r="AJ55" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK55" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL55">
-        <v>1.38</v>
-      </c>
-      <c r="AM55">
-        <v>1.35</v>
-      </c>
-      <c r="AN55">
-        <v>1.62</v>
-      </c>
-      <c r="AO55">
-        <v>-1</v>
-      </c>
-      <c r="AP55">
-        <v>1.22</v>
-      </c>
-      <c r="AQ55">
-        <v>1.38</v>
-      </c>
-      <c r="AR55">
-        <v>1.66</v>
-      </c>
-      <c r="AS55">
-        <v>2.02</v>
-      </c>
-      <c r="AT55">
-        <v>2.55</v>
-      </c>
-      <c r="AU55">
-        <v>3.8</v>
-      </c>
-      <c r="AV55">
-        <v>2.7</v>
-      </c>
-      <c r="AW55">
-        <v>2.08</v>
-      </c>
-      <c r="AX55">
-        <v>1.68</v>
-      </c>
-      <c r="AY55">
-        <v>1.44</v>
-      </c>
-      <c r="AZ55">
-        <v>0</v>
-      </c>
-      <c r="BA55">
-        <v>0</v>
-      </c>
-      <c r="BB55">
-        <v>1.8</v>
-      </c>
-      <c r="BC55">
-        <v>2.5</v>
-      </c>
-      <c r="BD55" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL55" s="3">
         <v>45850.70833333334</v>
       </c>
     </row>
-    <row r="56" spans="1:56">
+    <row r="56" spans="1:38">
       <c r="A56" s="2">
         <v>45850</v>
       </c>
       <c r="B56" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C56" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E56" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="F56" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -10632,7 +7608,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="L56">
         <v>1.5</v>
@@ -10707,87 +7683,33 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK56" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL56">
-        <v>0</v>
-      </c>
-      <c r="AM56">
-        <v>0</v>
-      </c>
-      <c r="AN56">
-        <v>0</v>
-      </c>
-      <c r="AO56">
-        <v>-1</v>
-      </c>
-      <c r="AP56">
-        <v>0</v>
-      </c>
-      <c r="AQ56">
-        <v>0</v>
-      </c>
-      <c r="AR56">
-        <v>0</v>
-      </c>
-      <c r="AS56">
-        <v>0</v>
-      </c>
-      <c r="AT56">
-        <v>0</v>
-      </c>
-      <c r="AU56">
-        <v>0</v>
-      </c>
-      <c r="AV56">
-        <v>0</v>
-      </c>
-      <c r="AW56">
-        <v>0</v>
-      </c>
-      <c r="AX56">
-        <v>0</v>
-      </c>
-      <c r="AY56">
-        <v>0</v>
-      </c>
-      <c r="AZ56">
-        <v>0</v>
-      </c>
-      <c r="BA56">
-        <v>0</v>
-      </c>
-      <c r="BB56">
-        <v>0</v>
-      </c>
-      <c r="BC56">
-        <v>0</v>
-      </c>
-      <c r="BD56" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL56" s="3">
         <v>45850.70833333334</v>
       </c>
     </row>
-    <row r="57" spans="1:56">
+    <row r="57" spans="1:38">
       <c r="A57" s="2">
         <v>45850</v>
       </c>
       <c r="B57" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C57" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D57" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E57" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="F57" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -10802,7 +7724,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="L57">
         <v>1.87</v>
@@ -10877,87 +7799,33 @@
         <v>0</v>
       </c>
       <c r="AJ57" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK57" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL57">
-        <v>0</v>
-      </c>
-      <c r="AM57">
-        <v>0</v>
-      </c>
-      <c r="AN57">
-        <v>0</v>
-      </c>
-      <c r="AO57">
-        <v>-1</v>
-      </c>
-      <c r="AP57">
-        <v>0</v>
-      </c>
-      <c r="AQ57">
-        <v>0</v>
-      </c>
-      <c r="AR57">
-        <v>0</v>
-      </c>
-      <c r="AS57">
-        <v>0</v>
-      </c>
-      <c r="AT57">
-        <v>0</v>
-      </c>
-      <c r="AU57">
-        <v>0</v>
-      </c>
-      <c r="AV57">
-        <v>0</v>
-      </c>
-      <c r="AW57">
-        <v>0</v>
-      </c>
-      <c r="AX57">
-        <v>0</v>
-      </c>
-      <c r="AY57">
-        <v>0</v>
-      </c>
-      <c r="AZ57">
-        <v>0</v>
-      </c>
-      <c r="BA57">
-        <v>0</v>
-      </c>
-      <c r="BB57">
-        <v>0</v>
-      </c>
-      <c r="BC57">
-        <v>0</v>
-      </c>
-      <c r="BD57" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL57" s="3">
         <v>45850.70833333334</v>
       </c>
     </row>
-    <row r="58" spans="1:56">
+    <row r="58" spans="1:38">
       <c r="A58" s="2">
         <v>45850</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C58" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D58" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E58" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="F58" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -10972,7 +7840,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L58">
         <v>1.87</v>
@@ -11047,87 +7915,33 @@
         <v>0</v>
       </c>
       <c r="AJ58" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK58" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL58">
-        <v>0</v>
-      </c>
-      <c r="AM58">
-        <v>0</v>
-      </c>
-      <c r="AN58">
-        <v>0</v>
-      </c>
-      <c r="AO58">
-        <v>-1</v>
-      </c>
-      <c r="AP58">
-        <v>0</v>
-      </c>
-      <c r="AQ58">
-        <v>0</v>
-      </c>
-      <c r="AR58">
-        <v>0</v>
-      </c>
-      <c r="AS58">
-        <v>0</v>
-      </c>
-      <c r="AT58">
-        <v>0</v>
-      </c>
-      <c r="AU58">
-        <v>0</v>
-      </c>
-      <c r="AV58">
-        <v>0</v>
-      </c>
-      <c r="AW58">
-        <v>0</v>
-      </c>
-      <c r="AX58">
-        <v>0</v>
-      </c>
-      <c r="AY58">
-        <v>0</v>
-      </c>
-      <c r="AZ58">
-        <v>0</v>
-      </c>
-      <c r="BA58">
-        <v>0</v>
-      </c>
-      <c r="BB58">
-        <v>0</v>
-      </c>
-      <c r="BC58">
-        <v>0</v>
-      </c>
-      <c r="BD58" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL58" s="3">
         <v>45850.70833333334</v>
       </c>
     </row>
-    <row r="59" spans="1:56">
+    <row r="59" spans="1:38">
       <c r="A59" s="2">
         <v>45850</v>
       </c>
       <c r="B59" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C59" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D59" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E59" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F59" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -11142,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -11217,87 +8031,33 @@
         <v>0</v>
       </c>
       <c r="AJ59" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK59" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL59">
-        <v>0</v>
-      </c>
-      <c r="AM59">
-        <v>0</v>
-      </c>
-      <c r="AN59">
-        <v>0</v>
-      </c>
-      <c r="AO59">
-        <v>-1</v>
-      </c>
-      <c r="AP59">
-        <v>0</v>
-      </c>
-      <c r="AQ59">
-        <v>0</v>
-      </c>
-      <c r="AR59">
-        <v>0</v>
-      </c>
-      <c r="AS59">
-        <v>0</v>
-      </c>
-      <c r="AT59">
-        <v>0</v>
-      </c>
-      <c r="AU59">
-        <v>0</v>
-      </c>
-      <c r="AV59">
-        <v>0</v>
-      </c>
-      <c r="AW59">
-        <v>0</v>
-      </c>
-      <c r="AX59">
-        <v>0</v>
-      </c>
-      <c r="AY59">
-        <v>0</v>
-      </c>
-      <c r="AZ59">
-        <v>0</v>
-      </c>
-      <c r="BA59">
-        <v>0</v>
-      </c>
-      <c r="BB59">
-        <v>0</v>
-      </c>
-      <c r="BC59">
-        <v>0</v>
-      </c>
-      <c r="BD59" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL59" s="3">
         <v>45850.70833333334</v>
       </c>
     </row>
-    <row r="60" spans="1:56">
+    <row r="60" spans="1:38">
       <c r="A60" s="2">
         <v>45850</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D60" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E60" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F60" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -11312,7 +8072,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="L60">
         <v>1.86</v>
@@ -11387,87 +8147,33 @@
         <v>0</v>
       </c>
       <c r="AJ60" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK60" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL60">
-        <v>0</v>
-      </c>
-      <c r="AM60">
-        <v>0</v>
-      </c>
-      <c r="AN60">
-        <v>0</v>
-      </c>
-      <c r="AO60">
-        <v>-1</v>
-      </c>
-      <c r="AP60">
-        <v>0</v>
-      </c>
-      <c r="AQ60">
-        <v>0</v>
-      </c>
-      <c r="AR60">
-        <v>0</v>
-      </c>
-      <c r="AS60">
-        <v>0</v>
-      </c>
-      <c r="AT60">
-        <v>0</v>
-      </c>
-      <c r="AU60">
-        <v>0</v>
-      </c>
-      <c r="AV60">
-        <v>0</v>
-      </c>
-      <c r="AW60">
-        <v>0</v>
-      </c>
-      <c r="AX60">
-        <v>0</v>
-      </c>
-      <c r="AY60">
-        <v>0</v>
-      </c>
-      <c r="AZ60">
-        <v>0</v>
-      </c>
-      <c r="BA60">
-        <v>0</v>
-      </c>
-      <c r="BB60">
-        <v>0</v>
-      </c>
-      <c r="BC60">
-        <v>0</v>
-      </c>
-      <c r="BD60" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL60" s="3">
         <v>45850.70833333334</v>
       </c>
     </row>
-    <row r="61" spans="1:56">
+    <row r="61" spans="1:38">
       <c r="A61" s="2">
         <v>45850</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C61" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D61" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E61" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="F61" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -11482,7 +8188,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="L61">
         <v>2.28</v>
@@ -11557,87 +8263,33 @@
         <v>0</v>
       </c>
       <c r="AJ61" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK61" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL61">
-        <v>0</v>
-      </c>
-      <c r="AM61">
-        <v>0</v>
-      </c>
-      <c r="AN61">
-        <v>0</v>
-      </c>
-      <c r="AO61">
-        <v>-1</v>
-      </c>
-      <c r="AP61">
-        <v>0</v>
-      </c>
-      <c r="AQ61">
-        <v>0</v>
-      </c>
-      <c r="AR61">
-        <v>0</v>
-      </c>
-      <c r="AS61">
-        <v>0</v>
-      </c>
-      <c r="AT61">
-        <v>0</v>
-      </c>
-      <c r="AU61">
-        <v>0</v>
-      </c>
-      <c r="AV61">
-        <v>0</v>
-      </c>
-      <c r="AW61">
-        <v>0</v>
-      </c>
-      <c r="AX61">
-        <v>0</v>
-      </c>
-      <c r="AY61">
-        <v>0</v>
-      </c>
-      <c r="AZ61">
-        <v>0</v>
-      </c>
-      <c r="BA61">
-        <v>0</v>
-      </c>
-      <c r="BB61">
-        <v>0</v>
-      </c>
-      <c r="BC61">
-        <v>0</v>
-      </c>
-      <c r="BD61" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL61" s="3">
         <v>45850.70833333334</v>
       </c>
     </row>
-    <row r="62" spans="1:56">
+    <row r="62" spans="1:38">
       <c r="A62" s="2">
         <v>45850</v>
       </c>
       <c r="B62" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C62" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D62" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E62" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="F62" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -11652,7 +8304,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="L62">
         <v>2.02</v>
@@ -11727,87 +8379,33 @@
         <v>0</v>
       </c>
       <c r="AJ62" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK62" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL62">
-        <v>0</v>
-      </c>
-      <c r="AM62">
-        <v>0</v>
-      </c>
-      <c r="AN62">
-        <v>0</v>
-      </c>
-      <c r="AO62">
-        <v>-1</v>
-      </c>
-      <c r="AP62">
-        <v>0</v>
-      </c>
-      <c r="AQ62">
-        <v>0</v>
-      </c>
-      <c r="AR62">
-        <v>0</v>
-      </c>
-      <c r="AS62">
-        <v>0</v>
-      </c>
-      <c r="AT62">
-        <v>0</v>
-      </c>
-      <c r="AU62">
-        <v>0</v>
-      </c>
-      <c r="AV62">
-        <v>0</v>
-      </c>
-      <c r="AW62">
-        <v>0</v>
-      </c>
-      <c r="AX62">
-        <v>0</v>
-      </c>
-      <c r="AY62">
-        <v>0</v>
-      </c>
-      <c r="AZ62">
-        <v>0</v>
-      </c>
-      <c r="BA62">
-        <v>0</v>
-      </c>
-      <c r="BB62">
-        <v>0</v>
-      </c>
-      <c r="BC62">
-        <v>0</v>
-      </c>
-      <c r="BD62" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL62" s="3">
         <v>45850.70833333334</v>
       </c>
     </row>
-    <row r="63" spans="1:56">
+    <row r="63" spans="1:38">
       <c r="A63" s="2">
         <v>45850</v>
       </c>
       <c r="B63" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D63" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E63" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="F63" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -11822,7 +8420,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L63">
         <v>2.15</v>
@@ -11897,87 +8495,33 @@
         <v>0</v>
       </c>
       <c r="AJ63" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK63" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL63">
-        <v>0</v>
-      </c>
-      <c r="AM63">
-        <v>0</v>
-      </c>
-      <c r="AN63">
-        <v>0</v>
-      </c>
-      <c r="AO63">
-        <v>-1</v>
-      </c>
-      <c r="AP63">
-        <v>0</v>
-      </c>
-      <c r="AQ63">
-        <v>0</v>
-      </c>
-      <c r="AR63">
-        <v>0</v>
-      </c>
-      <c r="AS63">
-        <v>0</v>
-      </c>
-      <c r="AT63">
-        <v>0</v>
-      </c>
-      <c r="AU63">
-        <v>0</v>
-      </c>
-      <c r="AV63">
-        <v>0</v>
-      </c>
-      <c r="AW63">
-        <v>0</v>
-      </c>
-      <c r="AX63">
-        <v>0</v>
-      </c>
-      <c r="AY63">
-        <v>0</v>
-      </c>
-      <c r="AZ63">
-        <v>0</v>
-      </c>
-      <c r="BA63">
-        <v>0</v>
-      </c>
-      <c r="BB63">
-        <v>1.73</v>
-      </c>
-      <c r="BC63">
-        <v>2.75</v>
-      </c>
-      <c r="BD63" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL63" s="3">
         <v>45850.77083333334</v>
       </c>
     </row>
-    <row r="64" spans="1:56">
+    <row r="64" spans="1:38">
       <c r="A64" s="2">
         <v>45850</v>
       </c>
       <c r="B64" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D64" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E64" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="F64" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -11992,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L64">
         <v>1.95</v>
@@ -12067,87 +8611,33 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK64" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL64">
-        <v>0</v>
-      </c>
-      <c r="AM64">
-        <v>0</v>
-      </c>
-      <c r="AN64">
-        <v>0</v>
-      </c>
-      <c r="AO64">
-        <v>-1</v>
-      </c>
-      <c r="AP64">
-        <v>0</v>
-      </c>
-      <c r="AQ64">
-        <v>0</v>
-      </c>
-      <c r="AR64">
-        <v>0</v>
-      </c>
-      <c r="AS64">
-        <v>0</v>
-      </c>
-      <c r="AT64">
-        <v>0</v>
-      </c>
-      <c r="AU64">
-        <v>0</v>
-      </c>
-      <c r="AV64">
-        <v>0</v>
-      </c>
-      <c r="AW64">
-        <v>0</v>
-      </c>
-      <c r="AX64">
-        <v>0</v>
-      </c>
-      <c r="AY64">
-        <v>0</v>
-      </c>
-      <c r="AZ64">
-        <v>0</v>
-      </c>
-      <c r="BA64">
-        <v>0</v>
-      </c>
-      <c r="BB64">
-        <v>1.62</v>
-      </c>
-      <c r="BC64">
-        <v>3.1</v>
-      </c>
-      <c r="BD64" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL64" s="3">
         <v>45850.77083333334</v>
       </c>
     </row>
-    <row r="65" spans="1:56">
+    <row r="65" spans="1:38">
       <c r="A65" s="2">
         <v>45850</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D65" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E65" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="F65" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -12162,7 +8652,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L65">
         <v>2.95</v>
@@ -12237,87 +8727,33 @@
         <v>0</v>
       </c>
       <c r="AJ65" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK65" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL65">
-        <v>0</v>
-      </c>
-      <c r="AM65">
-        <v>0</v>
-      </c>
-      <c r="AN65">
-        <v>0</v>
-      </c>
-      <c r="AO65">
-        <v>-1</v>
-      </c>
-      <c r="AP65">
-        <v>0</v>
-      </c>
-      <c r="AQ65">
-        <v>0</v>
-      </c>
-      <c r="AR65">
-        <v>0</v>
-      </c>
-      <c r="AS65">
-        <v>0</v>
-      </c>
-      <c r="AT65">
-        <v>0</v>
-      </c>
-      <c r="AU65">
-        <v>0</v>
-      </c>
-      <c r="AV65">
-        <v>0</v>
-      </c>
-      <c r="AW65">
-        <v>0</v>
-      </c>
-      <c r="AX65">
-        <v>0</v>
-      </c>
-      <c r="AY65">
-        <v>0</v>
-      </c>
-      <c r="AZ65">
-        <v>0</v>
-      </c>
-      <c r="BA65">
-        <v>0</v>
-      </c>
-      <c r="BB65">
-        <v>2.3</v>
-      </c>
-      <c r="BC65">
-        <v>1.73</v>
-      </c>
-      <c r="BD65" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL65" s="3">
         <v>45850.79166666666</v>
       </c>
     </row>
-    <row r="66" spans="1:56">
+    <row r="66" spans="1:38">
       <c r="A66" s="2">
         <v>45850</v>
       </c>
       <c r="B66" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C66" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D66" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E66" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="F66" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -12332,7 +8768,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L66">
         <v>2.2</v>
@@ -12407,87 +8843,33 @@
         <v>1.02</v>
       </c>
       <c r="AJ66" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK66" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL66">
-        <v>1.38</v>
-      </c>
-      <c r="AM66">
-        <v>1.37</v>
-      </c>
-      <c r="AN66">
-        <v>1.62</v>
-      </c>
-      <c r="AO66">
-        <v>-1</v>
-      </c>
-      <c r="AP66">
-        <v>1.23</v>
-      </c>
-      <c r="AQ66">
-        <v>1.41</v>
-      </c>
-      <c r="AR66">
-        <v>1.68</v>
-      </c>
-      <c r="AS66">
-        <v>2.05</v>
-      </c>
-      <c r="AT66">
-        <v>2.65</v>
-      </c>
-      <c r="AU66">
-        <v>3.65</v>
-      </c>
-      <c r="AV66">
-        <v>2.65</v>
-      </c>
-      <c r="AW66">
-        <v>2.05</v>
-      </c>
-      <c r="AX66">
-        <v>1.68</v>
-      </c>
-      <c r="AY66">
-        <v>1.42</v>
-      </c>
-      <c r="AZ66">
-        <v>0</v>
-      </c>
-      <c r="BA66">
-        <v>0</v>
-      </c>
-      <c r="BB66">
-        <v>1.8</v>
-      </c>
-      <c r="BC66">
-        <v>2.5</v>
-      </c>
-      <c r="BD66" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL66" s="3">
         <v>45850.8125</v>
       </c>
     </row>
-    <row r="67" spans="1:56">
+    <row r="67" spans="1:38">
       <c r="A67" s="2">
         <v>45850</v>
       </c>
       <c r="B67" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C67" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D67" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E67" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="F67" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -12502,7 +8884,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L67">
         <v>2.05</v>
@@ -12577,87 +8959,33 @@
         <v>1.03</v>
       </c>
       <c r="AJ67" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK67" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL67">
-        <v>1.22</v>
-      </c>
-      <c r="AM67">
-        <v>1.35</v>
-      </c>
-      <c r="AN67">
-        <v>1.74</v>
-      </c>
-      <c r="AO67">
-        <v>-1</v>
-      </c>
-      <c r="AP67">
-        <v>0</v>
-      </c>
-      <c r="AQ67">
-        <v>0</v>
-      </c>
-      <c r="AR67">
-        <v>0</v>
-      </c>
-      <c r="AS67">
-        <v>0</v>
-      </c>
-      <c r="AT67">
-        <v>0</v>
-      </c>
-      <c r="AU67">
-        <v>0</v>
-      </c>
-      <c r="AV67">
-        <v>0</v>
-      </c>
-      <c r="AW67">
-        <v>0</v>
-      </c>
-      <c r="AX67">
-        <v>0</v>
-      </c>
-      <c r="AY67">
-        <v>0</v>
-      </c>
-      <c r="AZ67">
-        <v>0</v>
-      </c>
-      <c r="BA67">
-        <v>0</v>
-      </c>
-      <c r="BB67">
-        <v>1.73</v>
-      </c>
-      <c r="BC67">
-        <v>2.75</v>
-      </c>
-      <c r="BD67" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL67" s="3">
         <v>45850.8125</v>
       </c>
     </row>
-    <row r="68" spans="1:56">
+    <row r="68" spans="1:38">
       <c r="A68" s="2">
         <v>45850</v>
       </c>
       <c r="B68" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C68" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D68" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E68" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="F68" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -12672,7 +9000,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L68">
         <v>2.21</v>
@@ -12747,87 +9075,33 @@
         <v>1.05</v>
       </c>
       <c r="AJ68" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK68" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL68">
-        <v>1.35</v>
-      </c>
-      <c r="AM68">
-        <v>1.3</v>
-      </c>
-      <c r="AN68">
-        <v>1.6</v>
-      </c>
-      <c r="AO68">
-        <v>-1</v>
-      </c>
-      <c r="AP68">
-        <v>0</v>
-      </c>
-      <c r="AQ68">
-        <v>0</v>
-      </c>
-      <c r="AR68">
-        <v>0</v>
-      </c>
-      <c r="AS68">
-        <v>0</v>
-      </c>
-      <c r="AT68">
-        <v>0</v>
-      </c>
-      <c r="AU68">
-        <v>0</v>
-      </c>
-      <c r="AV68">
-        <v>0</v>
-      </c>
-      <c r="AW68">
-        <v>0</v>
-      </c>
-      <c r="AX68">
-        <v>0</v>
-      </c>
-      <c r="AY68">
-        <v>0</v>
-      </c>
-      <c r="AZ68">
-        <v>0</v>
-      </c>
-      <c r="BA68">
-        <v>0</v>
-      </c>
-      <c r="BB68">
-        <v>1.85</v>
-      </c>
-      <c r="BC68">
-        <v>2.24</v>
-      </c>
-      <c r="BD68" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL68" s="3">
         <v>45850.83333333334</v>
       </c>
     </row>
-    <row r="69" spans="1:56">
+    <row r="69" spans="1:38">
       <c r="A69" s="2">
         <v>45850</v>
       </c>
       <c r="B69" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C69" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="D69" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E69" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -12842,7 +9116,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L69">
         <v>1.63</v>
@@ -12917,87 +9191,33 @@
         <v>1.1</v>
       </c>
       <c r="AJ69" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK69" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL69">
-        <v>1.2</v>
-      </c>
-      <c r="AM69">
-        <v>1.23</v>
-      </c>
-      <c r="AN69">
-        <v>2.1</v>
-      </c>
-      <c r="AO69">
-        <v>-1</v>
-      </c>
-      <c r="AP69">
-        <v>0</v>
-      </c>
-      <c r="AQ69">
-        <v>0</v>
-      </c>
-      <c r="AR69">
-        <v>0</v>
-      </c>
-      <c r="AS69">
-        <v>0</v>
-      </c>
-      <c r="AT69">
-        <v>0</v>
-      </c>
-      <c r="AU69">
-        <v>0</v>
-      </c>
-      <c r="AV69">
-        <v>0</v>
-      </c>
-      <c r="AW69">
-        <v>0</v>
-      </c>
-      <c r="AX69">
-        <v>0</v>
-      </c>
-      <c r="AY69">
-        <v>0</v>
-      </c>
-      <c r="AZ69">
-        <v>0</v>
-      </c>
-      <c r="BA69">
-        <v>0</v>
-      </c>
-      <c r="BB69">
-        <v>1.47</v>
-      </c>
-      <c r="BC69">
-        <v>2.88</v>
-      </c>
-      <c r="BD69" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL69" s="3">
         <v>45850.83333333334</v>
       </c>
     </row>
-    <row r="70" spans="1:56">
+    <row r="70" spans="1:38">
       <c r="A70" s="2">
         <v>45850</v>
       </c>
       <c r="B70" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C70" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="D70" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E70" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="F70" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -13012,7 +9232,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L70">
         <v>2.01</v>
@@ -13087,87 +9307,33 @@
         <v>1.1</v>
       </c>
       <c r="AJ70" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK70" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL70">
-        <v>1.25</v>
-      </c>
-      <c r="AM70">
-        <v>1.26</v>
-      </c>
-      <c r="AN70">
-        <v>1.67</v>
-      </c>
-      <c r="AO70">
-        <v>-1</v>
-      </c>
-      <c r="AP70">
-        <v>0</v>
-      </c>
-      <c r="AQ70">
-        <v>0</v>
-      </c>
-      <c r="AR70">
-        <v>0</v>
-      </c>
-      <c r="AS70">
-        <v>0</v>
-      </c>
-      <c r="AT70">
-        <v>0</v>
-      </c>
-      <c r="AU70">
-        <v>0</v>
-      </c>
-      <c r="AV70">
-        <v>0</v>
-      </c>
-      <c r="AW70">
-        <v>0</v>
-      </c>
-      <c r="AX70">
-        <v>0</v>
-      </c>
-      <c r="AY70">
-        <v>0</v>
-      </c>
-      <c r="AZ70">
-        <v>0</v>
-      </c>
-      <c r="BA70">
-        <v>0</v>
-      </c>
-      <c r="BB70">
-        <v>1.7</v>
-      </c>
-      <c r="BC70">
-        <v>2.26</v>
-      </c>
-      <c r="BD70" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL70" s="3">
         <v>45850.83333333334</v>
       </c>
     </row>
-    <row r="71" spans="1:56">
+    <row r="71" spans="1:38">
       <c r="A71" s="2">
         <v>45850</v>
       </c>
       <c r="B71" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C71" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D71" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E71" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="F71" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -13182,7 +9348,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L71">
         <v>1.76</v>
@@ -13257,87 +9423,33 @@
         <v>1.05</v>
       </c>
       <c r="AJ71" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK71" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL71">
-        <v>1.31</v>
-      </c>
-      <c r="AM71">
-        <v>1.31</v>
-      </c>
-      <c r="AN71">
-        <v>2</v>
-      </c>
-      <c r="AO71">
-        <v>-1</v>
-      </c>
-      <c r="AP71">
-        <v>1.09</v>
-      </c>
-      <c r="AQ71">
-        <v>1.26</v>
-      </c>
-      <c r="AR71">
-        <v>1.5</v>
-      </c>
-      <c r="AS71">
-        <v>1.84</v>
-      </c>
-      <c r="AT71">
-        <v>2.2</v>
-      </c>
-      <c r="AU71">
-        <v>4.35</v>
-      </c>
-      <c r="AV71">
-        <v>3.23</v>
-      </c>
-      <c r="AW71">
-        <v>2.36</v>
-      </c>
-      <c r="AX71">
-        <v>1.9</v>
-      </c>
-      <c r="AY71">
-        <v>1.58</v>
-      </c>
-      <c r="AZ71">
-        <v>0</v>
-      </c>
-      <c r="BA71">
-        <v>0</v>
-      </c>
-      <c r="BB71">
-        <v>1.5</v>
-      </c>
-      <c r="BC71">
-        <v>3.4</v>
-      </c>
-      <c r="BD71" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL71" s="3">
         <v>45850.85416666666</v>
       </c>
     </row>
-    <row r="72" spans="1:56">
+    <row r="72" spans="1:38">
       <c r="A72" s="2">
         <v>45850</v>
       </c>
       <c r="B72" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C72" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D72" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E72" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="F72" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -13352,7 +9464,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L72">
         <v>1.9</v>
@@ -13427,87 +9539,33 @@
         <v>1.22</v>
       </c>
       <c r="AJ72" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK72" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL72">
-        <v>1.3</v>
-      </c>
-      <c r="AM72">
-        <v>1.22</v>
-      </c>
-      <c r="AN72">
-        <v>1.77</v>
-      </c>
-      <c r="AO72">
-        <v>-1</v>
-      </c>
-      <c r="AP72">
-        <v>1.23</v>
-      </c>
-      <c r="AQ72">
-        <v>1.41</v>
-      </c>
-      <c r="AR72">
-        <v>1.66</v>
-      </c>
-      <c r="AS72">
-        <v>2.02</v>
-      </c>
-      <c r="AT72">
-        <v>2.55</v>
-      </c>
-      <c r="AU72">
-        <v>3.65</v>
-      </c>
-      <c r="AV72">
-        <v>2.65</v>
-      </c>
-      <c r="AW72">
-        <v>2.07</v>
-      </c>
-      <c r="AX72">
-        <v>1.68</v>
-      </c>
-      <c r="AY72">
-        <v>1.44</v>
-      </c>
-      <c r="AZ72">
-        <v>0</v>
-      </c>
-      <c r="BA72">
-        <v>0</v>
-      </c>
-      <c r="BB72">
-        <v>1.7</v>
-      </c>
-      <c r="BC72">
-        <v>2.25</v>
-      </c>
-      <c r="BD72" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL72" s="3">
         <v>45850.85416666666</v>
       </c>
     </row>
-    <row r="73" spans="1:56">
+    <row r="73" spans="1:38">
       <c r="A73" s="2">
         <v>45850</v>
       </c>
       <c r="B73" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C73" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D73" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E73" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="F73" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -13522,7 +9580,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L73">
         <v>1.78</v>
@@ -13597,87 +9655,33 @@
         <v>1.1</v>
       </c>
       <c r="AJ73" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK73" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL73">
-        <v>1.25</v>
-      </c>
-      <c r="AM73">
-        <v>1.28</v>
-      </c>
-      <c r="AN73">
-        <v>1.91</v>
-      </c>
-      <c r="AO73">
-        <v>-1</v>
-      </c>
-      <c r="AP73">
-        <v>1.33</v>
-      </c>
-      <c r="AQ73">
-        <v>1.57</v>
-      </c>
-      <c r="AR73">
-        <v>1.92</v>
-      </c>
-      <c r="AS73">
-        <v>2.43</v>
-      </c>
-      <c r="AT73">
-        <v>3.15</v>
-      </c>
-      <c r="AU73">
-        <v>2.95</v>
-      </c>
-      <c r="AV73">
-        <v>2.23</v>
-      </c>
-      <c r="AW73">
-        <v>1.77</v>
-      </c>
-      <c r="AX73">
-        <v>1.48</v>
-      </c>
-      <c r="AY73">
-        <v>1.3</v>
-      </c>
-      <c r="AZ73">
-        <v>0</v>
-      </c>
-      <c r="BA73">
-        <v>0</v>
-      </c>
-      <c r="BB73">
-        <v>1.68</v>
-      </c>
-      <c r="BC73">
-        <v>2.57</v>
-      </c>
-      <c r="BD73" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL73" s="3">
         <v>45850.85416666666</v>
       </c>
     </row>
-    <row r="74" spans="1:56">
+    <row r="74" spans="1:38">
       <c r="A74" s="2">
         <v>45850</v>
       </c>
       <c r="B74" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C74" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D74" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E74" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="F74" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -13692,7 +9696,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L74">
         <v>2.02</v>
@@ -13767,102 +9771,48 @@
         <v>1.25</v>
       </c>
       <c r="AJ74" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK74" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL74">
-        <v>1.36</v>
-      </c>
-      <c r="AM74">
-        <v>1.22</v>
-      </c>
-      <c r="AN74">
-        <v>1.67</v>
-      </c>
-      <c r="AO74">
-        <v>-1</v>
-      </c>
-      <c r="AP74">
-        <v>1.35</v>
-      </c>
-      <c r="AQ74">
-        <v>1.7</v>
-      </c>
-      <c r="AR74">
-        <v>1.96</v>
-      </c>
-      <c r="AS74">
-        <v>2.5</v>
-      </c>
-      <c r="AT74">
-        <v>3.3</v>
-      </c>
-      <c r="AU74">
-        <v>2.9</v>
-      </c>
-      <c r="AV74">
-        <v>2.05</v>
-      </c>
-      <c r="AW74">
-        <v>1.73</v>
-      </c>
-      <c r="AX74">
-        <v>1.46</v>
-      </c>
-      <c r="AY74">
-        <v>1.28</v>
-      </c>
-      <c r="AZ74">
-        <v>0</v>
-      </c>
-      <c r="BA74">
-        <v>0</v>
-      </c>
-      <c r="BB74">
-        <v>1.67</v>
-      </c>
-      <c r="BC74">
-        <v>2.2</v>
-      </c>
-      <c r="BD74" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL74" s="3">
         <v>45850.85416666666</v>
       </c>
     </row>
-    <row r="75" spans="1:56">
+    <row r="75" spans="1:38">
       <c r="A75" s="2">
         <v>45850</v>
       </c>
       <c r="B75" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C75" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="D75" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E75" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="F75" t="s">
+        <v>251</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75" t="s">
         <v>269</v>
-      </c>
-      <c r="G75">
-        <v>0</v>
-      </c>
-      <c r="H75">
-        <v>0</v>
-      </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75">
-        <v>0</v>
-      </c>
-      <c r="K75" t="s">
-        <v>287</v>
       </c>
       <c r="L75">
         <v>2.19</v>
@@ -13937,87 +9887,33 @@
         <v>1.08</v>
       </c>
       <c r="AJ75" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK75" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL75">
-        <v>1.28</v>
-      </c>
-      <c r="AM75">
-        <v>1.28</v>
-      </c>
-      <c r="AN75">
-        <v>1.5</v>
-      </c>
-      <c r="AO75">
-        <v>-1</v>
-      </c>
-      <c r="AP75">
-        <v>0</v>
-      </c>
-      <c r="AQ75">
-        <v>0</v>
-      </c>
-      <c r="AR75">
-        <v>0</v>
-      </c>
-      <c r="AS75">
-        <v>0</v>
-      </c>
-      <c r="AT75">
-        <v>0</v>
-      </c>
-      <c r="AU75">
-        <v>0</v>
-      </c>
-      <c r="AV75">
-        <v>0</v>
-      </c>
-      <c r="AW75">
-        <v>0</v>
-      </c>
-      <c r="AX75">
-        <v>0</v>
-      </c>
-      <c r="AY75">
-        <v>0</v>
-      </c>
-      <c r="AZ75">
-        <v>0</v>
-      </c>
-      <c r="BA75">
-        <v>0</v>
-      </c>
-      <c r="BB75">
-        <v>1.85</v>
-      </c>
-      <c r="BC75">
-        <v>2.14</v>
-      </c>
-      <c r="BD75" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL75" s="3">
         <v>45850.85416666666</v>
       </c>
     </row>
-    <row r="76" spans="1:56">
+    <row r="76" spans="1:38">
       <c r="A76" s="2">
         <v>45850</v>
       </c>
       <c r="B76" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C76" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D76" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E76" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="F76" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -14032,7 +9928,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L76">
         <v>2.46</v>
@@ -14107,87 +10003,33 @@
         <v>1.1</v>
       </c>
       <c r="AJ76" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK76" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL76">
-        <v>1.48</v>
-      </c>
-      <c r="AM76">
-        <v>1.29</v>
-      </c>
-      <c r="AN76">
-        <v>1.53</v>
-      </c>
-      <c r="AO76">
-        <v>-1</v>
-      </c>
-      <c r="AP76">
-        <v>1.27</v>
-      </c>
-      <c r="AQ76">
-        <v>1.47</v>
-      </c>
-      <c r="AR76">
-        <v>1.76</v>
-      </c>
-      <c r="AS76">
-        <v>2.18</v>
-      </c>
-      <c r="AT76">
-        <v>2.8</v>
-      </c>
-      <c r="AU76">
-        <v>3.3</v>
-      </c>
-      <c r="AV76">
-        <v>2.48</v>
-      </c>
-      <c r="AW76">
-        <v>1.94</v>
-      </c>
-      <c r="AX76">
-        <v>1.58</v>
-      </c>
-      <c r="AY76">
-        <v>1.37</v>
-      </c>
-      <c r="AZ76">
-        <v>0</v>
-      </c>
-      <c r="BA76">
-        <v>0</v>
-      </c>
-      <c r="BB76">
-        <v>1.93</v>
-      </c>
-      <c r="BC76">
-        <v>1.98</v>
-      </c>
-      <c r="BD76" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL76" s="3">
         <v>45850.85416666666</v>
       </c>
     </row>
-    <row r="77" spans="1:56">
+    <row r="77" spans="1:38">
       <c r="A77" s="2">
         <v>45850</v>
       </c>
       <c r="B77" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C77" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D77" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E77" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F77" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -14202,7 +10044,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L77">
         <v>1.92</v>
@@ -14277,87 +10119,33 @@
         <v>1.33</v>
       </c>
       <c r="AJ77" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK77" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL77">
-        <v>1.33</v>
-      </c>
-      <c r="AM77">
-        <v>1.2</v>
-      </c>
-      <c r="AN77">
-        <v>1.77</v>
-      </c>
-      <c r="AO77">
-        <v>-1</v>
-      </c>
-      <c r="AP77">
-        <v>1.24</v>
-      </c>
-      <c r="AQ77">
-        <v>1.44</v>
-      </c>
-      <c r="AR77">
-        <v>1.72</v>
-      </c>
-      <c r="AS77">
-        <v>2.1</v>
-      </c>
-      <c r="AT77">
-        <v>2.65</v>
-      </c>
-      <c r="AU77">
-        <v>3.55</v>
-      </c>
-      <c r="AV77">
-        <v>2.55</v>
-      </c>
-      <c r="AW77">
-        <v>1.98</v>
-      </c>
-      <c r="AX77">
-        <v>1.64</v>
-      </c>
-      <c r="AY77">
-        <v>1.4</v>
-      </c>
-      <c r="AZ77">
-        <v>0</v>
-      </c>
-      <c r="BA77">
-        <v>0</v>
-      </c>
-      <c r="BB77">
-        <v>1.73</v>
-      </c>
-      <c r="BC77">
-        <v>2.1</v>
-      </c>
-      <c r="BD77" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL77" s="3">
         <v>45850.85416666666</v>
       </c>
     </row>
-    <row r="78" spans="1:56">
+    <row r="78" spans="1:38">
       <c r="A78" s="2">
         <v>45850</v>
       </c>
       <c r="B78" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C78" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D78" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E78" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="F78" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -14372,7 +10160,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L78">
         <v>1.39</v>
@@ -14447,87 +10235,33 @@
         <v>1.18</v>
       </c>
       <c r="AJ78" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK78" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL78">
-        <v>1.09</v>
-      </c>
-      <c r="AM78">
-        <v>1.17</v>
-      </c>
-      <c r="AN78">
-        <v>2.94</v>
-      </c>
-      <c r="AO78">
-        <v>-1</v>
-      </c>
-      <c r="AP78">
-        <v>1.3</v>
-      </c>
-      <c r="AQ78">
-        <v>1.52</v>
-      </c>
-      <c r="AR78">
-        <v>1.84</v>
-      </c>
-      <c r="AS78">
-        <v>2.3</v>
-      </c>
-      <c r="AT78">
-        <v>2.95</v>
-      </c>
-      <c r="AU78">
-        <v>3.1</v>
-      </c>
-      <c r="AV78">
-        <v>2.33</v>
-      </c>
-      <c r="AW78">
-        <v>1.84</v>
-      </c>
-      <c r="AX78">
-        <v>1.53</v>
-      </c>
-      <c r="AY78">
-        <v>1.33</v>
-      </c>
-      <c r="AZ78">
-        <v>0</v>
-      </c>
-      <c r="BA78">
-        <v>0</v>
-      </c>
-      <c r="BB78">
-        <v>1.35</v>
-      </c>
-      <c r="BC78">
-        <v>3.4</v>
-      </c>
-      <c r="BD78" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL78" s="3">
         <v>45850.85416666666</v>
       </c>
     </row>
-    <row r="79" spans="1:56">
+    <row r="79" spans="1:38">
       <c r="A79" s="2">
         <v>45850</v>
       </c>
       <c r="B79" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C79" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D79" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E79" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="F79" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -14542,7 +10276,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L79">
         <v>1.48</v>
@@ -14617,87 +10351,33 @@
         <v>0</v>
       </c>
       <c r="AJ79" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK79" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL79">
-        <v>0</v>
-      </c>
-      <c r="AM79">
-        <v>0</v>
-      </c>
-      <c r="AN79">
-        <v>0</v>
-      </c>
-      <c r="AO79">
-        <v>-1</v>
-      </c>
-      <c r="AP79">
-        <v>0</v>
-      </c>
-      <c r="AQ79">
-        <v>0</v>
-      </c>
-      <c r="AR79">
-        <v>0</v>
-      </c>
-      <c r="AS79">
-        <v>0</v>
-      </c>
-      <c r="AT79">
-        <v>0</v>
-      </c>
-      <c r="AU79">
-        <v>0</v>
-      </c>
-      <c r="AV79">
-        <v>0</v>
-      </c>
-      <c r="AW79">
-        <v>0</v>
-      </c>
-      <c r="AX79">
-        <v>0</v>
-      </c>
-      <c r="AY79">
-        <v>0</v>
-      </c>
-      <c r="AZ79">
-        <v>0</v>
-      </c>
-      <c r="BA79">
-        <v>0</v>
-      </c>
-      <c r="BB79">
-        <v>1.33</v>
-      </c>
-      <c r="BC79">
-        <v>4</v>
-      </c>
-      <c r="BD79" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL79" s="3">
         <v>45850.86458333334</v>
       </c>
     </row>
-    <row r="80" spans="1:56">
+    <row r="80" spans="1:38">
       <c r="A80" s="2">
         <v>45850</v>
       </c>
       <c r="B80" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="C80" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D80" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E80" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="F80" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -14712,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L80">
         <v>2.16</v>
@@ -14787,87 +10467,33 @@
         <v>0</v>
       </c>
       <c r="AJ80" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK80" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL80">
-        <v>0</v>
-      </c>
-      <c r="AM80">
-        <v>0</v>
-      </c>
-      <c r="AN80">
-        <v>0</v>
-      </c>
-      <c r="AO80">
-        <v>-1</v>
-      </c>
-      <c r="AP80">
-        <v>0</v>
-      </c>
-      <c r="AQ80">
-        <v>0</v>
-      </c>
-      <c r="AR80">
-        <v>0</v>
-      </c>
-      <c r="AS80">
-        <v>0</v>
-      </c>
-      <c r="AT80">
-        <v>0</v>
-      </c>
-      <c r="AU80">
-        <v>0</v>
-      </c>
-      <c r="AV80">
-        <v>0</v>
-      </c>
-      <c r="AW80">
-        <v>0</v>
-      </c>
-      <c r="AX80">
-        <v>0</v>
-      </c>
-      <c r="AY80">
-        <v>0</v>
-      </c>
-      <c r="AZ80">
-        <v>0</v>
-      </c>
-      <c r="BA80">
-        <v>0</v>
-      </c>
-      <c r="BB80">
-        <v>1.73</v>
-      </c>
-      <c r="BC80">
-        <v>2.5</v>
-      </c>
-      <c r="BD80" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL80" s="3">
         <v>45850.875</v>
       </c>
     </row>
-    <row r="81" spans="1:56">
+    <row r="81" spans="1:38">
       <c r="A81" s="2">
         <v>45850</v>
       </c>
       <c r="B81" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C81" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D81" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E81" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="F81" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -14882,7 +10508,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L81">
         <v>2.86</v>
@@ -14957,87 +10583,33 @@
         <v>1.2</v>
       </c>
       <c r="AJ81" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK81" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL81">
-        <v>1.66</v>
-      </c>
-      <c r="AM81">
-        <v>1.26</v>
-      </c>
-      <c r="AN81">
-        <v>1.37</v>
-      </c>
-      <c r="AO81">
-        <v>-1</v>
-      </c>
-      <c r="AP81">
-        <v>1.23</v>
-      </c>
-      <c r="AQ81">
-        <v>1.41</v>
-      </c>
-      <c r="AR81">
-        <v>1.66</v>
-      </c>
-      <c r="AS81">
-        <v>2.04</v>
-      </c>
-      <c r="AT81">
-        <v>2.55</v>
-      </c>
-      <c r="AU81">
-        <v>3.65</v>
-      </c>
-      <c r="AV81">
-        <v>2.65</v>
-      </c>
-      <c r="AW81">
-        <v>2.06</v>
-      </c>
-      <c r="AX81">
-        <v>1.68</v>
-      </c>
-      <c r="AY81">
-        <v>1.44</v>
-      </c>
-      <c r="AZ81">
-        <v>0</v>
-      </c>
-      <c r="BA81">
-        <v>0</v>
-      </c>
-      <c r="BB81">
-        <v>2.2</v>
-      </c>
-      <c r="BC81">
-        <v>1.67</v>
-      </c>
-      <c r="BD81" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL81" s="3">
         <v>45850.89583333334</v>
       </c>
     </row>
-    <row r="82" spans="1:56">
+    <row r="82" spans="1:38">
       <c r="A82" s="2">
         <v>45850</v>
       </c>
       <c r="B82" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C82" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D82" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E82" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="F82" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -15052,7 +10624,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L82">
         <v>2.34</v>
@@ -15127,87 +10699,33 @@
         <v>0</v>
       </c>
       <c r="AJ82" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK82" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL82">
-        <v>0</v>
-      </c>
-      <c r="AM82">
-        <v>0</v>
-      </c>
-      <c r="AN82">
-        <v>0</v>
-      </c>
-      <c r="AO82">
-        <v>-1</v>
-      </c>
-      <c r="AP82">
-        <v>0</v>
-      </c>
-      <c r="AQ82">
-        <v>0</v>
-      </c>
-      <c r="AR82">
-        <v>0</v>
-      </c>
-      <c r="AS82">
-        <v>0</v>
-      </c>
-      <c r="AT82">
-        <v>0</v>
-      </c>
-      <c r="AU82">
-        <v>0</v>
-      </c>
-      <c r="AV82">
-        <v>0</v>
-      </c>
-      <c r="AW82">
-        <v>0</v>
-      </c>
-      <c r="AX82">
-        <v>0</v>
-      </c>
-      <c r="AY82">
-        <v>0</v>
-      </c>
-      <c r="AZ82">
-        <v>0</v>
-      </c>
-      <c r="BA82">
-        <v>0</v>
-      </c>
-      <c r="BB82">
-        <v>0</v>
-      </c>
-      <c r="BC82">
-        <v>0</v>
-      </c>
-      <c r="BD82" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL82" s="3">
         <v>45850.89583333334</v>
       </c>
     </row>
-    <row r="83" spans="1:56">
+    <row r="83" spans="1:38">
       <c r="A83" s="2">
         <v>45850</v>
       </c>
       <c r="B83" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C83" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D83" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E83" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="F83" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -15222,7 +10740,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L83">
         <v>1.77</v>
@@ -15297,87 +10815,33 @@
         <v>1.25</v>
       </c>
       <c r="AJ83" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK83" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL83">
-        <v>1.27</v>
-      </c>
-      <c r="AM83">
-        <v>1.24</v>
-      </c>
-      <c r="AN83">
-        <v>1.88</v>
-      </c>
-      <c r="AO83">
-        <v>-1</v>
-      </c>
-      <c r="AP83">
-        <v>1.23</v>
-      </c>
-      <c r="AQ83">
-        <v>1.41</v>
-      </c>
-      <c r="AR83">
-        <v>1.67</v>
-      </c>
-      <c r="AS83">
-        <v>2.05</v>
-      </c>
-      <c r="AT83">
-        <v>2.55</v>
-      </c>
-      <c r="AU83">
-        <v>3.65</v>
-      </c>
-      <c r="AV83">
-        <v>2.65</v>
-      </c>
-      <c r="AW83">
-        <v>2.05</v>
-      </c>
-      <c r="AX83">
-        <v>1.67</v>
-      </c>
-      <c r="AY83">
-        <v>1.43</v>
-      </c>
-      <c r="AZ83">
-        <v>0</v>
-      </c>
-      <c r="BA83">
-        <v>0</v>
-      </c>
-      <c r="BB83">
-        <v>1.57</v>
-      </c>
-      <c r="BC83">
-        <v>2.38</v>
-      </c>
-      <c r="BD83" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL83" s="3">
         <v>45850.89583333334</v>
       </c>
     </row>
-    <row r="84" spans="1:56">
+    <row r="84" spans="1:38">
       <c r="A84" s="2">
         <v>45850</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C84" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="D84" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E84" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="F84" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -15392,7 +10856,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L84">
         <v>1.86</v>
@@ -15467,87 +10931,33 @@
         <v>1.08</v>
       </c>
       <c r="AJ84" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK84" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL84">
-        <v>1.27</v>
-      </c>
-      <c r="AM84">
-        <v>1.27</v>
-      </c>
-      <c r="AN84">
-        <v>1.83</v>
-      </c>
-      <c r="AO84">
-        <v>-1</v>
-      </c>
-      <c r="AP84">
-        <v>0</v>
-      </c>
-      <c r="AQ84">
-        <v>0</v>
-      </c>
-      <c r="AR84">
-        <v>0</v>
-      </c>
-      <c r="AS84">
-        <v>0</v>
-      </c>
-      <c r="AT84">
-        <v>0</v>
-      </c>
-      <c r="AU84">
-        <v>0</v>
-      </c>
-      <c r="AV84">
-        <v>0</v>
-      </c>
-      <c r="AW84">
-        <v>0</v>
-      </c>
-      <c r="AX84">
-        <v>0</v>
-      </c>
-      <c r="AY84">
-        <v>0</v>
-      </c>
-      <c r="AZ84">
-        <v>0</v>
-      </c>
-      <c r="BA84">
-        <v>0</v>
-      </c>
-      <c r="BB84">
-        <v>1.61</v>
-      </c>
-      <c r="BC84">
-        <v>2.71</v>
-      </c>
-      <c r="BD84" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL84" s="3">
         <v>45850.89583333334</v>
       </c>
     </row>
-    <row r="85" spans="1:56">
+    <row r="85" spans="1:38">
       <c r="A85" s="2">
         <v>45850</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C85" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D85" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E85" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F85" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -15562,7 +10972,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L85">
         <v>2.06</v>
@@ -15637,87 +11047,33 @@
         <v>1.11</v>
       </c>
       <c r="AJ85" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK85" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL85">
-        <v>1.35</v>
-      </c>
-      <c r="AM85">
-        <v>1.28</v>
-      </c>
-      <c r="AN85">
-        <v>1.66</v>
-      </c>
-      <c r="AO85">
-        <v>-1</v>
-      </c>
-      <c r="AP85">
-        <v>1.25</v>
-      </c>
-      <c r="AQ85">
-        <v>1.44</v>
-      </c>
-      <c r="AR85">
-        <v>1.72</v>
-      </c>
-      <c r="AS85">
-        <v>2.12</v>
-      </c>
-      <c r="AT85">
-        <v>2.7</v>
-      </c>
-      <c r="AU85">
-        <v>3.4</v>
-      </c>
-      <c r="AV85">
-        <v>2.55</v>
-      </c>
-      <c r="AW85">
-        <v>1.98</v>
-      </c>
-      <c r="AX85">
-        <v>1.63</v>
-      </c>
-      <c r="AY85">
-        <v>1.4</v>
-      </c>
-      <c r="AZ85">
-        <v>0</v>
-      </c>
-      <c r="BA85">
-        <v>0</v>
-      </c>
-      <c r="BB85">
-        <v>1.67</v>
-      </c>
-      <c r="BC85">
-        <v>2.3</v>
-      </c>
-      <c r="BD85" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL85" s="3">
         <v>45850.89583333334</v>
       </c>
     </row>
-    <row r="86" spans="1:56">
+    <row r="86" spans="1:38">
       <c r="A86" s="2">
         <v>45850</v>
       </c>
       <c r="B86" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C86" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="D86" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E86" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="F86" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -15732,7 +11088,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L86">
         <v>2.46</v>
@@ -15807,87 +11163,33 @@
         <v>1.1</v>
       </c>
       <c r="AJ86" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK86" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL86">
-        <v>1.22</v>
-      </c>
-      <c r="AM86">
-        <v>0</v>
-      </c>
-      <c r="AN86">
-        <v>1.37</v>
-      </c>
-      <c r="AO86">
-        <v>-1</v>
-      </c>
-      <c r="AP86">
-        <v>0</v>
-      </c>
-      <c r="AQ86">
-        <v>0</v>
-      </c>
-      <c r="AR86">
-        <v>0</v>
-      </c>
-      <c r="AS86">
-        <v>0</v>
-      </c>
-      <c r="AT86">
-        <v>0</v>
-      </c>
-      <c r="AU86">
-        <v>0</v>
-      </c>
-      <c r="AV86">
-        <v>0</v>
-      </c>
-      <c r="AW86">
-        <v>0</v>
-      </c>
-      <c r="AX86">
-        <v>0</v>
-      </c>
-      <c r="AY86">
-        <v>0</v>
-      </c>
-      <c r="AZ86">
-        <v>0</v>
-      </c>
-      <c r="BA86">
-        <v>0</v>
-      </c>
-      <c r="BB86">
-        <v>2.3</v>
-      </c>
-      <c r="BC86">
-        <v>1.73</v>
-      </c>
-      <c r="BD86" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL86" s="3">
         <v>45850.91666666666</v>
       </c>
     </row>
-    <row r="87" spans="1:56">
+    <row r="87" spans="1:38">
       <c r="A87" s="2">
         <v>45850</v>
       </c>
       <c r="B87" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C87" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="D87" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E87" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="F87" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -15902,7 +11204,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L87">
         <v>1.59</v>
@@ -15977,87 +11279,33 @@
         <v>1.14</v>
       </c>
       <c r="AJ87" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK87" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL87">
-        <v>1.25</v>
-      </c>
-      <c r="AM87">
-        <v>0</v>
-      </c>
-      <c r="AN87">
-        <v>1.9</v>
-      </c>
-      <c r="AO87">
-        <v>-1</v>
-      </c>
-      <c r="AP87">
-        <v>0</v>
-      </c>
-      <c r="AQ87">
-        <v>0</v>
-      </c>
-      <c r="AR87">
-        <v>0</v>
-      </c>
-      <c r="AS87">
-        <v>0</v>
-      </c>
-      <c r="AT87">
-        <v>0</v>
-      </c>
-      <c r="AU87">
-        <v>0</v>
-      </c>
-      <c r="AV87">
-        <v>0</v>
-      </c>
-      <c r="AW87">
-        <v>0</v>
-      </c>
-      <c r="AX87">
-        <v>0</v>
-      </c>
-      <c r="AY87">
-        <v>0</v>
-      </c>
-      <c r="AZ87">
-        <v>0</v>
-      </c>
-      <c r="BA87">
-        <v>0</v>
-      </c>
-      <c r="BB87">
-        <v>1.53</v>
-      </c>
-      <c r="BC87">
-        <v>2.63</v>
-      </c>
-      <c r="BD87" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL87" s="3">
         <v>45850.91666666666</v>
       </c>
     </row>
-    <row r="88" spans="1:56">
+    <row r="88" spans="1:38">
       <c r="A88" s="2">
         <v>45850</v>
       </c>
       <c r="B88" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C88" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D88" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E88" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="F88" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -16072,7 +11320,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L88">
         <v>1.92</v>
@@ -16147,87 +11395,33 @@
         <v>1.15</v>
       </c>
       <c r="AJ88" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK88" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL88">
-        <v>1.3</v>
-      </c>
-      <c r="AM88">
-        <v>1.27</v>
-      </c>
-      <c r="AN88">
-        <v>1.75</v>
-      </c>
-      <c r="AO88">
-        <v>-1</v>
-      </c>
-      <c r="AP88">
-        <v>1.25</v>
-      </c>
-      <c r="AQ88">
-        <v>1.44</v>
-      </c>
-      <c r="AR88">
-        <v>1.7</v>
-      </c>
-      <c r="AS88">
-        <v>2.15</v>
-      </c>
-      <c r="AT88">
-        <v>2.7</v>
-      </c>
-      <c r="AU88">
-        <v>3.45</v>
-      </c>
-      <c r="AV88">
-        <v>2.55</v>
-      </c>
-      <c r="AW88">
-        <v>2.05</v>
-      </c>
-      <c r="AX88">
-        <v>1.61</v>
-      </c>
-      <c r="AY88">
-        <v>1.38</v>
-      </c>
-      <c r="AZ88">
-        <v>0</v>
-      </c>
-      <c r="BA88">
-        <v>0</v>
-      </c>
-      <c r="BB88">
-        <v>1.62</v>
-      </c>
-      <c r="BC88">
-        <v>2.4</v>
-      </c>
-      <c r="BD88" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL88" s="3">
         <v>45850.9375</v>
       </c>
     </row>
-    <row r="89" spans="1:56">
+    <row r="89" spans="1:38">
       <c r="A89" s="2">
         <v>45850</v>
       </c>
       <c r="B89" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C89" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D89" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E89" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="F89" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -16242,7 +11436,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L89">
         <v>2.2</v>
@@ -16317,87 +11511,33 @@
         <v>1.2</v>
       </c>
       <c r="AJ89" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK89" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL89">
-        <v>1.39</v>
-      </c>
-      <c r="AM89">
-        <v>1.29</v>
-      </c>
-      <c r="AN89">
-        <v>1.58</v>
-      </c>
-      <c r="AO89">
-        <v>-1</v>
-      </c>
-      <c r="AP89">
-        <v>1.25</v>
-      </c>
-      <c r="AQ89">
-        <v>1.44</v>
-      </c>
-      <c r="AR89">
-        <v>1.83</v>
-      </c>
-      <c r="AS89">
-        <v>2.14</v>
-      </c>
-      <c r="AT89">
-        <v>2.7</v>
-      </c>
-      <c r="AU89">
-        <v>3.45</v>
-      </c>
-      <c r="AV89">
-        <v>2.55</v>
-      </c>
-      <c r="AW89">
-        <v>1.85</v>
-      </c>
-      <c r="AX89">
-        <v>1.62</v>
-      </c>
-      <c r="AY89">
-        <v>1.4</v>
-      </c>
-      <c r="AZ89">
-        <v>0</v>
-      </c>
-      <c r="BA89">
-        <v>0</v>
-      </c>
-      <c r="BB89">
-        <v>1.73</v>
-      </c>
-      <c r="BC89">
-        <v>2.1</v>
-      </c>
-      <c r="BD89" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL89" s="3">
         <v>45850.9375</v>
       </c>
     </row>
-    <row r="90" spans="1:56">
+    <row r="90" spans="1:38">
       <c r="A90" s="2">
         <v>45850</v>
       </c>
       <c r="B90" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="C90" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="D90" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E90" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="F90" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -16412,7 +11552,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L90">
         <v>2.43</v>
@@ -16487,87 +11627,33 @@
         <v>1.13</v>
       </c>
       <c r="AJ90" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK90" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL90">
-        <v>1.25</v>
-      </c>
-      <c r="AM90">
-        <v>1.26</v>
-      </c>
-      <c r="AN90">
-        <v>1.42</v>
-      </c>
-      <c r="AO90">
-        <v>-1</v>
-      </c>
-      <c r="AP90">
-        <v>0</v>
-      </c>
-      <c r="AQ90">
-        <v>0</v>
-      </c>
-      <c r="AR90">
-        <v>0</v>
-      </c>
-      <c r="AS90">
-        <v>0</v>
-      </c>
-      <c r="AT90">
-        <v>0</v>
-      </c>
-      <c r="AU90">
-        <v>0</v>
-      </c>
-      <c r="AV90">
-        <v>0</v>
-      </c>
-      <c r="AW90">
-        <v>0</v>
-      </c>
-      <c r="AX90">
-        <v>0</v>
-      </c>
-      <c r="AY90">
-        <v>0</v>
-      </c>
-      <c r="AZ90">
-        <v>0</v>
-      </c>
-      <c r="BA90">
-        <v>0</v>
-      </c>
-      <c r="BB90">
-        <v>1.92</v>
-      </c>
-      <c r="BC90">
-        <v>1.94</v>
-      </c>
-      <c r="BD90" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL90" s="3">
         <v>45850.95833333334</v>
       </c>
     </row>
-    <row r="91" spans="1:56">
+    <row r="91" spans="1:38">
       <c r="A91" s="2">
         <v>45850</v>
       </c>
       <c r="B91" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C91" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D91" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E91" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="F91" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -16582,7 +11668,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L91">
         <v>1.62</v>
@@ -16657,87 +11743,33 @@
         <v>1.14</v>
       </c>
       <c r="AJ91" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK91" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL91">
-        <v>1.18</v>
-      </c>
-      <c r="AM91">
-        <v>1.24</v>
-      </c>
-      <c r="AN91">
-        <v>2.15</v>
-      </c>
-      <c r="AO91">
-        <v>-1</v>
-      </c>
-      <c r="AP91">
-        <v>1.3</v>
-      </c>
-      <c r="AQ91">
-        <v>1.53</v>
-      </c>
-      <c r="AR91">
-        <v>1.85</v>
-      </c>
-      <c r="AS91">
-        <v>2.32</v>
-      </c>
-      <c r="AT91">
-        <v>3.05</v>
-      </c>
-      <c r="AU91">
-        <v>3.05</v>
-      </c>
-      <c r="AV91">
-        <v>2.32</v>
-      </c>
-      <c r="AW91">
-        <v>1.85</v>
-      </c>
-      <c r="AX91">
-        <v>1.53</v>
-      </c>
-      <c r="AY91">
-        <v>1.32</v>
-      </c>
-      <c r="AZ91">
-        <v>0</v>
-      </c>
-      <c r="BA91">
-        <v>0</v>
-      </c>
-      <c r="BB91">
-        <v>1.44</v>
-      </c>
-      <c r="BC91">
-        <v>2.88</v>
-      </c>
-      <c r="BD91" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL91" s="3">
         <v>45850.97916666666</v>
       </c>
     </row>
-    <row r="92" spans="1:56">
+    <row r="92" spans="1:38">
       <c r="A92" s="2">
         <v>45850</v>
       </c>
       <c r="B92" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C92" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D92" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E92" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="F92" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -16752,7 +11784,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="L92">
         <v>1.4</v>
@@ -16827,66 +11859,12 @@
         <v>1.25</v>
       </c>
       <c r="AJ92" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="AK92" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL92">
-        <v>1.12</v>
-      </c>
-      <c r="AM92">
-        <v>1.18</v>
-      </c>
-      <c r="AN92">
-        <v>2.7</v>
-      </c>
-      <c r="AO92">
-        <v>-1</v>
-      </c>
-      <c r="AP92">
-        <v>1.26</v>
-      </c>
-      <c r="AQ92">
-        <v>1.46</v>
-      </c>
-      <c r="AR92">
-        <v>1.73</v>
-      </c>
-      <c r="AS92">
-        <v>2.17</v>
-      </c>
-      <c r="AT92">
-        <v>2.7</v>
-      </c>
-      <c r="AU92">
-        <v>3.4</v>
-      </c>
-      <c r="AV92">
-        <v>2.5</v>
-      </c>
-      <c r="AW92">
-        <v>1.96</v>
-      </c>
-      <c r="AX92">
-        <v>1.6</v>
-      </c>
-      <c r="AY92">
-        <v>1.38</v>
-      </c>
-      <c r="AZ92">
-        <v>0</v>
-      </c>
-      <c r="BA92">
-        <v>0</v>
-      </c>
-      <c r="BB92">
-        <v>1.3</v>
-      </c>
-      <c r="BC92">
-        <v>3.4</v>
-      </c>
-      <c r="BD92" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL92" s="3">
         <v>45850.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-07-12.xlsx
+++ b/jogos_2025-07-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="328">
   <si>
     <t>Date</t>
   </si>
@@ -244,15 +244,15 @@
     <t>Japan J2 League</t>
   </si>
   <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
+    <t>China China League One</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
-    <t>China China League One</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
@@ -283,12 +283,12 @@
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
+    <t>Chile Primera División</t>
+  </si>
+  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
-    <t>Chile Primera División</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -313,72 +313,72 @@
     <t>Mt Druitt Town</t>
   </si>
   <si>
+    <t>Western Sydney W. II</t>
+  </si>
+  <si>
+    <t>Iwaki</t>
+  </si>
+  <si>
     <t>Mito Hollyhock</t>
   </si>
   <si>
     <t>Blaublitz Akita</t>
   </si>
   <si>
-    <t>Iwaki</t>
-  </si>
-  <si>
-    <t>Western Sydney W. II</t>
-  </si>
-  <si>
     <t>Imabari</t>
   </si>
   <si>
     <t>Ventforet Kofu</t>
   </si>
   <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Busan I'Park</t>
+  </si>
+  <si>
+    <t>Fujieda MYFC</t>
+  </si>
+  <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
+    <t>Renofa Yamaguchi</t>
+  </si>
+  <si>
+    <t>Montedio Yamagata</t>
+  </si>
+  <si>
     <t>Ulsan</t>
   </si>
   <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
-    <t>Cheonan City</t>
-  </si>
-  <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Renofa Yamaguchi</t>
-  </si>
-  <si>
     <t>Sagan Tosu</t>
   </si>
   <si>
-    <t>Fujieda MYFC</t>
-  </si>
-  <si>
-    <t>Montedio Yamagata</t>
-  </si>
-  <si>
-    <t>Yanbian Longding</t>
-  </si>
-  <si>
     <t>Jubilo Iwata</t>
   </si>
   <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
     <t>Shaanxi Union</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
+    <t>Qingdao Red Lions</t>
+  </si>
+  <si>
+    <t>Vaprus</t>
   </si>
   <si>
     <t>Dongguan United</t>
   </si>
   <si>
-    <t>Vaprus</t>
-  </si>
-  <si>
-    <t>Qingdao Red Lions</t>
-  </si>
-  <si>
     <t>Ulytau</t>
   </si>
   <si>
@@ -406,24 +406,24 @@
     <t>Malmö FF</t>
   </si>
   <si>
+    <t>Unión San Felipe</t>
+  </si>
+  <si>
+    <t>All Boys</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
     <t>Curicó Unido</t>
   </si>
   <si>
-    <t>All Boys</t>
-  </si>
-  <si>
-    <t>Unión San Felipe</t>
-  </si>
-  <si>
-    <t>Fredrikstad</t>
+    <t>Talleres Remedios</t>
   </si>
   <si>
     <t>Tristán Suárez</t>
   </si>
   <si>
-    <t>Talleres Remedios</t>
-  </si>
-  <si>
     <t>Colegiales</t>
   </si>
   <si>
@@ -442,25 +442,28 @@
     <t>Sligo Rovers</t>
   </si>
   <si>
+    <t>Universidad Chile</t>
+  </si>
+  <si>
     <t>Rosario Central</t>
   </si>
   <si>
+    <t>Atlético Ottawa</t>
+  </si>
+  <si>
     <t>Rangers</t>
   </si>
   <si>
-    <t>Universidad Chile</t>
-  </si>
-  <si>
-    <t>Atlético Ottawa</t>
-  </si>
-  <si>
     <t>Novorizontino</t>
   </si>
   <si>
+    <t>Internacional</t>
+  </si>
+  <si>
     <t>Flamengo</t>
   </si>
   <si>
-    <t>Internacional</t>
+    <t>San Miguel</t>
   </si>
   <si>
     <t>São Bernardo</t>
@@ -469,45 +472,42 @@
     <t>Itabaiana</t>
   </si>
   <si>
+    <t>Los Andes</t>
+  </si>
+  <si>
+    <t>Racing Córdoba</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
+    <t>Patronato</t>
+  </si>
+  <si>
     <t>Almagro</t>
   </si>
   <si>
-    <t>Patronato</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
-    <t>Gimnasia Mendoza</t>
+    <t>Quilmes</t>
   </si>
   <si>
     <t>Ferro Carril Oeste</t>
   </si>
   <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
     <t>Estudiantes Caseros</t>
   </si>
   <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Gimnasia La Plata</t>
+  </si>
+  <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
     <t>Huracán</t>
   </si>
   <si>
-    <t>Gimnasia La Plata</t>
-  </si>
-  <si>
     <t>San Martín Tucumán</t>
   </si>
   <si>
@@ -520,60 +520,60 @@
     <t>Floresta</t>
   </si>
   <si>
+    <t>Univ. Concepción</t>
+  </si>
+  <si>
+    <t>Detroit City FC</t>
+  </si>
+  <si>
     <t>Indy Eleven</t>
   </si>
   <si>
-    <t>Detroit City FC</t>
-  </si>
-  <si>
-    <t>Univ. Concepción</t>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
   </si>
   <si>
     <t>Inter Miami</t>
   </si>
   <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>Atlético PR</t>
+  </si>
+  <si>
     <t>Miami FC II</t>
   </si>
   <si>
-    <t>Atlético PR</t>
-  </si>
-  <si>
     <t>Philadelphia Union</t>
   </si>
   <si>
-    <t>Orlando City</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
     <t>Racing Club</t>
   </si>
   <si>
     <t>Bahia</t>
   </si>
   <si>
+    <t>Sporting KC</t>
+  </si>
+  <si>
+    <t>Austin</t>
+  </si>
+  <si>
+    <t>Minnesota United</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
     <t>Tulsa Roughnecks</t>
   </si>
   <si>
-    <t>Austin</t>
-  </si>
-  <si>
-    <t>Minnesota United</t>
-  </si>
-  <si>
-    <t>Sporting KC</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -589,84 +589,84 @@
     <t>Oakland Roots</t>
   </si>
   <si>
+    <t>Los Angeles FC</t>
+  </si>
+  <si>
     <t>LA Galaxy</t>
   </si>
   <si>
-    <t>Los Angeles FC</t>
-  </si>
-  <si>
     <t>NWS Spirit</t>
   </si>
   <si>
     <t>Sydney II</t>
   </si>
   <si>
+    <t>Marconi Stallions</t>
+  </si>
+  <si>
+    <t>V-Varen Nagasaki</t>
+  </si>
+  <si>
     <t>Kataller Toyama</t>
   </si>
   <si>
     <t>Roasso Kumamoto</t>
   </si>
   <si>
-    <t>V-Varen Nagasaki</t>
-  </si>
-  <si>
-    <t>Marconi Stallions</t>
-  </si>
-  <si>
     <t>Ehime</t>
   </si>
   <si>
     <t>Omiya Ardija</t>
   </si>
   <si>
+    <t>Gyeongnam</t>
+  </si>
+  <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
+    <t>Vegalta Sendai</t>
+  </si>
+  <si>
+    <t>Guangzhou E-Power</t>
+  </si>
+  <si>
+    <t>Tokushima Vortis</t>
+  </si>
+  <si>
+    <t>JEF United</t>
+  </si>
+  <si>
     <t>Daegu</t>
   </si>
   <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
-    <t>Seongnam</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
-    <t>Tokushima Vortis</t>
-  </si>
-  <si>
     <t>Oita Trinita</t>
   </si>
   <si>
-    <t>Vegalta Sendai</t>
-  </si>
-  <si>
-    <t>JEF United</t>
-  </si>
-  <si>
-    <t>Guangzhou E-Power</t>
-  </si>
-  <si>
     <t>Consadole Sapporo</t>
   </si>
   <si>
+    <t>Guangxi Baoyun</t>
+  </si>
+  <si>
     <t>Suzhou Dongwu</t>
   </si>
   <si>
-    <t>Guangxi Baoyun</t>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
+    <t>Trans</t>
   </si>
   <si>
     <t>Shenzhen Juniors</t>
   </si>
   <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
     <t>Yelimay Semey</t>
   </si>
   <si>
@@ -694,21 +694,21 @@
     <t>Norrköping</t>
   </si>
   <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
     <t>San Marcos</t>
   </si>
   <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>Molde</t>
+    <t>San Telmo</t>
   </si>
   <si>
     <t>Club Atlético Güemes</t>
   </si>
   <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
     <t>Atlanta</t>
   </si>
   <si>
@@ -724,60 +724,60 @@
     <t>Derry City</t>
   </si>
   <si>
+    <t>Colo-Colo</t>
+  </si>
+  <si>
     <t>Godoy Cruz</t>
   </si>
   <si>
+    <t>Forge FC</t>
+  </si>
+  <si>
     <t>Deportes Santa Cruz</t>
   </si>
   <si>
-    <t>Colo-Colo</t>
-  </si>
-  <si>
-    <t>Forge FC</t>
-  </si>
-  <si>
     <t>América Mineiro</t>
   </si>
   <si>
+    <t>Vitória</t>
+  </si>
+  <si>
     <t>São Paulo</t>
   </si>
   <si>
-    <t>Vitória</t>
-  </si>
-  <si>
     <t>Ponte Preta</t>
   </si>
   <si>
     <t>Confiança</t>
   </si>
   <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
     <t>Alvarado</t>
   </si>
   <si>
-    <t>Deportivo Maipú</t>
+    <t>Arsenal de Sarandí</t>
   </si>
   <si>
     <t>Deportivo Madryn</t>
   </si>
   <si>
-    <t>Arsenal de Sarandí</t>
-  </si>
-  <si>
     <t>Gimnasia Jujuy</t>
   </si>
   <si>
+    <t>Atlético GO</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
     <t>Botafogo</t>
   </si>
   <si>
-    <t>Atlético GO</t>
-  </si>
-  <si>
     <t>Belgrano</t>
   </si>
   <si>
-    <t>Instituto</t>
-  </si>
-  <si>
     <t>HFX Wanderers FC</t>
   </si>
   <si>
@@ -787,60 +787,60 @@
     <t>Ypiranga Erechim</t>
   </si>
   <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
     <t>Rhode Island</t>
   </si>
   <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>Montreal Impact</t>
+  </si>
+  <si>
+    <t>New York City</t>
   </si>
   <si>
     <t>Nashville SC</t>
   </si>
   <si>
+    <t>Columbus Crew</t>
+  </si>
+  <si>
+    <t>Goiás</t>
+  </si>
+  <si>
     <t>Lexington</t>
   </si>
   <si>
-    <t>Goiás</t>
-  </si>
-  <si>
     <t>New York RB</t>
   </si>
   <si>
-    <t>Montreal Impact</t>
-  </si>
-  <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
-    <t>New York City</t>
-  </si>
-  <si>
-    <t>Columbus Crew</t>
-  </si>
-  <si>
     <t>Barracas Central</t>
   </si>
   <si>
     <t>Atlético Mineiro</t>
   </si>
   <si>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
+    <t>San Diego</t>
+  </si>
+  <si>
     <t>Las Vegas Lights</t>
   </si>
   <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>SJ Earthquakes</t>
-  </si>
-  <si>
-    <t>Seattle Sounders</t>
-  </si>
-  <si>
-    <t>San Diego</t>
-  </si>
-  <si>
     <t>Charleston Battery</t>
   </si>
   <si>
@@ -856,28 +856,148 @@
     <t>Phoenix Rising</t>
   </si>
   <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
     <t>DC United</t>
   </si>
   <si>
-    <t>FC Dallas</t>
-  </si>
-  <si>
     <t>complete</t>
   </si>
   <si>
+    <t>suspended</t>
+  </si>
+  <si>
     <t>incomplete</t>
   </si>
   <si>
-    <t>suspended</t>
-  </si>
-  <si>
     <t>['90+3']</t>
   </si>
   <si>
     <t>[]</t>
   </si>
   <si>
+    <t>['69']</t>
+  </si>
+  <si>
+    <t>['56', '64', '79']</t>
+  </si>
+  <si>
+    <t>['25', '45+1', '45+4']</t>
+  </si>
+  <si>
+    <t>['85']</t>
+  </si>
+  <si>
+    <t>['47']</t>
+  </si>
+  <si>
+    <t>['14']</t>
+  </si>
+  <si>
+    <t>['78', '90+1']</t>
+  </si>
+  <si>
+    <t>['87']</t>
+  </si>
+  <si>
+    <t>['31']</t>
+  </si>
+  <si>
+    <t>['69', '51']</t>
+  </si>
+  <si>
+    <t>['64', '79']</t>
+  </si>
+  <si>
+    <t>['18', '59']</t>
+  </si>
+  <si>
+    <t>['6', '29', '31', '68', '90+3']</t>
+  </si>
+  <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['64']</t>
+  </si>
+  <si>
+    <t>['28', '37', '79']</t>
+  </si>
+  <si>
+    <t>['10', '35']</t>
+  </si>
+  <si>
+    <t>['39']</t>
+  </si>
+  <si>
+    <t>['26']</t>
+  </si>
+  <si>
+    <t>['59', '68']</t>
+  </si>
+  <si>
+    <t>['40', '21', '45+1']</t>
+  </si>
+  <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['32', '49', '81']</t>
+  </si>
+  <si>
+    <t>['81', '85', '88', '90+9']</t>
+  </si>
+  <si>
     <t>['56', '85', '18']</t>
+  </si>
+  <si>
+    <t>['37']</t>
+  </si>
+  <si>
+    <t>['88']</t>
+  </si>
+  <si>
+    <t>['43', '51']</t>
+  </si>
+  <si>
+    <t>['24', '46', '54']</t>
+  </si>
+  <si>
+    <t>['46']</t>
+  </si>
+  <si>
+    <t>['81']</t>
+  </si>
+  <si>
+    <t>['33', '87']</t>
+  </si>
+  <si>
+    <t>['38']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
+  </si>
+  <si>
+    <t>['81', '17', '26']</t>
+  </si>
+  <si>
+    <t>['45+3', '25', '89', '90+3']</t>
+  </si>
+  <si>
+    <t>['45+3']</t>
+  </si>
+  <si>
+    <t>['40', '45']</t>
+  </si>
+  <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>['70', '87']</t>
+  </si>
+  <si>
+    <t>['4', '63']</t>
   </si>
 </sst>
 </file>
@@ -1470,7 +1590,7 @@
         <v>285</v>
       </c>
       <c r="AK2" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="AL2" s="3">
         <v>45850.125</v>
@@ -1600,7 +1720,7 @@
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
         <v>96</v>
@@ -1615,94 +1735,94 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L4">
-        <v>1.61</v>
+        <v>6.07</v>
       </c>
       <c r="M4">
-        <v>3.45</v>
+        <v>4.75</v>
       </c>
       <c r="N4">
-        <v>4.8</v>
+        <v>1.44</v>
       </c>
       <c r="O4">
-        <v>1.53</v>
+        <v>2.71</v>
       </c>
       <c r="P4">
-        <v>8.5</v>
+        <v>28</v>
       </c>
       <c r="Q4">
-        <v>3</v>
+        <v>1.41</v>
       </c>
       <c r="R4">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="S4">
-        <v>2.83</v>
+        <v>4.05</v>
       </c>
       <c r="T4">
-        <v>3.12</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="V4">
-        <v>7.4</v>
+        <v>4.25</v>
       </c>
       <c r="W4">
+        <v>1.15</v>
+      </c>
+      <c r="X4">
+        <v>1.02</v>
+      </c>
+      <c r="Y4">
+        <v>18.5</v>
+      </c>
+      <c r="Z4">
         <v>1.06</v>
       </c>
-      <c r="X4">
-        <v>1.03</v>
-      </c>
-      <c r="Y4">
-        <v>9</v>
-      </c>
-      <c r="Z4">
-        <v>1.29</v>
-      </c>
       <c r="AA4">
-        <v>3.3</v>
+        <v>6.05</v>
       </c>
       <c r="AB4">
-        <v>1.97</v>
+        <v>1.38</v>
       </c>
       <c r="AC4">
-        <v>1.73</v>
+        <v>2.74</v>
       </c>
       <c r="AD4">
-        <v>3.8</v>
+        <v>2.01</v>
       </c>
       <c r="AE4">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="AF4">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AG4">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AH4">
-        <v>7.5</v>
+        <v>3.25</v>
       </c>
       <c r="AI4">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AJ4" t="s">
         <v>286</v>
       </c>
       <c r="AK4" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="AL4" s="3">
         <v>45850.25</v>
@@ -1728,10 +1848,10 @@
         <v>196</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1740,85 +1860,85 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L5">
-        <v>2.61</v>
+        <v>3.34</v>
       </c>
       <c r="M5">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="N5">
-        <v>2.55</v>
+        <v>1.89</v>
       </c>
       <c r="O5">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="P5">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="Q5">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="R5">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S5">
-        <v>2.57</v>
+        <v>3.29</v>
       </c>
       <c r="T5">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="U5">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="V5">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z5">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AA5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB5">
-        <v>1.94</v>
+        <v>1.54</v>
       </c>
       <c r="AC5">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AD5">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="AE5">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AF5">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG5">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AH5">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AI5">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AJ5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AK5" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="AL5" s="3">
         <v>45850.25</v>
@@ -1844,7 +1964,7 @@
         <v>197</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1856,82 +1976,82 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L6">
-        <v>3.34</v>
+        <v>1.61</v>
       </c>
       <c r="M6">
         <v>3.45</v>
       </c>
       <c r="N6">
-        <v>1.89</v>
+        <v>4.8</v>
       </c>
       <c r="O6">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="P6">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Q6">
-        <v>1.78</v>
+        <v>3</v>
       </c>
       <c r="R6">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S6">
-        <v>3.29</v>
+        <v>2.83</v>
       </c>
       <c r="T6">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="U6">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="V6">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z6">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AA6">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AB6">
-        <v>1.54</v>
+        <v>1.97</v>
       </c>
       <c r="AC6">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AD6">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="AE6">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AF6">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AG6">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AH6">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AI6">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AJ6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AK6" t="s">
         <v>286</v>
@@ -1948,7 +2068,7 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
         <v>96</v>
@@ -1960,97 +2080,97 @@
         <v>198</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L7">
-        <v>6.07</v>
+        <v>2.61</v>
       </c>
       <c r="M7">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="N7">
+        <v>2.55</v>
+      </c>
+      <c r="O7">
+        <v>2.13</v>
+      </c>
+      <c r="P7">
+        <v>7.4</v>
+      </c>
+      <c r="Q7">
+        <v>1.95</v>
+      </c>
+      <c r="R7">
         <v>1.44</v>
       </c>
-      <c r="O7">
-        <v>2.71</v>
-      </c>
-      <c r="P7">
-        <v>28</v>
-      </c>
-      <c r="Q7">
-        <v>1.41</v>
-      </c>
-      <c r="R7">
-        <v>1.17</v>
-      </c>
       <c r="S7">
-        <v>4.05</v>
+        <v>2.57</v>
       </c>
       <c r="T7">
-        <v>2</v>
+        <v>3.04</v>
       </c>
       <c r="U7">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="V7">
-        <v>4.25</v>
+        <v>7.9</v>
       </c>
       <c r="W7">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="Z7">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AA7">
-        <v>6.05</v>
+        <v>3</v>
       </c>
       <c r="AB7">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>2.74</v>
+        <v>1.76</v>
       </c>
       <c r="AD7">
-        <v>2.01</v>
+        <v>4</v>
       </c>
       <c r="AE7">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AF7">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AG7">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AH7">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="AI7">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AJ7" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AK7" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="AL7" s="3">
         <v>45850.25</v>
@@ -2076,7 +2196,7 @@
         <v>199</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -2088,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L8">
         <v>1.54</v>
@@ -2163,7 +2283,7 @@
         <v>1.08</v>
       </c>
       <c r="AJ8" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AK8" t="s">
         <v>286</v>
@@ -2192,7 +2312,7 @@
         <v>200</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -2204,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L9">
         <v>2.95</v>
@@ -2279,7 +2399,7 @@
         <v>1.05</v>
       </c>
       <c r="AJ9" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AK9" t="s">
         <v>286</v>
@@ -2308,94 +2428,94 @@
         <v>201</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L10">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="M10">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="N10">
-        <v>5.2</v>
+        <v>3.96</v>
       </c>
       <c r="O10">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="P10">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q10">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="R10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S10">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="T10">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="U10">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="W10">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
         <v>11</v>
       </c>
       <c r="Z10">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AA10">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AB10">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AC10">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AD10">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AE10">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AF10">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH10">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="AI10">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ10" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AK10" t="s">
         <v>286</v>
@@ -2412,7 +2532,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
         <v>96</v>
@@ -2424,97 +2544,97 @@
         <v>202</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L11">
-        <v>1.68</v>
+        <v>2.64</v>
       </c>
       <c r="M11">
-        <v>3.68</v>
+        <v>3.06</v>
       </c>
       <c r="N11">
-        <v>3.96</v>
+        <v>2.42</v>
       </c>
       <c r="O11">
-        <v>1.51</v>
+        <v>2.05</v>
       </c>
       <c r="P11">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>2.58</v>
+        <v>2.05</v>
       </c>
       <c r="R11">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="S11">
-        <v>3.26</v>
+        <v>2.76</v>
       </c>
       <c r="T11">
-        <v>2.46</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="V11">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Z11">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AA11">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB11">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AC11">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AD11">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="AE11">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AF11">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="AH11">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="AI11">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AJ11" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="AK11" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="AL11" s="3">
         <v>45850.29166666666</v>
@@ -2528,7 +2648,7 @@
         <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
         <v>96</v>
@@ -2540,7 +2660,7 @@
         <v>203</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2552,82 +2672,82 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L12">
-        <v>1.82</v>
+        <v>1.34</v>
       </c>
       <c r="M12">
-        <v>3.33</v>
+        <v>4.33</v>
       </c>
       <c r="N12">
-        <v>3.69</v>
+        <v>7.1</v>
       </c>
       <c r="O12">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="P12">
-        <v>8.5</v>
+        <v>15.75</v>
       </c>
       <c r="Q12">
-        <v>2.6</v>
+        <v>3.32</v>
       </c>
       <c r="R12">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="S12">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="T12">
-        <v>3.18</v>
+        <v>2.29</v>
       </c>
       <c r="U12">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="V12">
-        <v>7.2</v>
+        <v>4.95</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z12">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AA12">
-        <v>3</v>
+        <v>4.45</v>
       </c>
       <c r="AB12">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AC12">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AD12">
-        <v>4</v>
+        <v>2.26</v>
       </c>
       <c r="AE12">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="AF12">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AH12">
-        <v>8</v>
+        <v>3.85</v>
       </c>
       <c r="AI12">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AJ12" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="AK12" t="s">
         <v>286</v>
@@ -2644,7 +2764,7 @@
         <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
         <v>96</v>
@@ -2668,43 +2788,43 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L13">
-        <v>2.64</v>
+        <v>1.82</v>
       </c>
       <c r="M13">
-        <v>3.06</v>
+        <v>3.33</v>
       </c>
       <c r="N13">
-        <v>2.42</v>
+        <v>3.69</v>
       </c>
       <c r="O13">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="P13">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Q13">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="R13">
         <v>1.43</v>
       </c>
       <c r="S13">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T13">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U13">
         <v>1.34</v>
       </c>
       <c r="V13">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
         <v>1.05</v>
@@ -2713,16 +2833,16 @@
         <v>8</v>
       </c>
       <c r="Z13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA13">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AB13">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC13">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AD13">
         <v>4</v>
@@ -2731,10 +2851,10 @@
         <v>1.2</v>
       </c>
       <c r="AF13">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG13">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH13">
         <v>8</v>
@@ -2760,7 +2880,7 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
         <v>96</v>
@@ -2772,97 +2892,97 @@
         <v>205</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L14">
-        <v>1.34</v>
+        <v>3.15</v>
       </c>
       <c r="M14">
-        <v>4.33</v>
+        <v>3.14</v>
       </c>
       <c r="N14">
+        <v>2.06</v>
+      </c>
+      <c r="O14">
+        <v>2.25</v>
+      </c>
+      <c r="P14">
+        <v>9</v>
+      </c>
+      <c r="Q14">
+        <v>1.83</v>
+      </c>
+      <c r="R14">
+        <v>1.39</v>
+      </c>
+      <c r="S14">
+        <v>2.95</v>
+      </c>
+      <c r="T14">
+        <v>2.96</v>
+      </c>
+      <c r="U14">
+        <v>1.39</v>
+      </c>
+      <c r="V14">
         <v>7.1</v>
       </c>
-      <c r="O14">
-        <v>1.33</v>
-      </c>
-      <c r="P14">
-        <v>15.75</v>
-      </c>
-      <c r="Q14">
-        <v>3.32</v>
-      </c>
-      <c r="R14">
-        <v>1.27</v>
-      </c>
-      <c r="S14">
-        <v>3.28</v>
-      </c>
-      <c r="T14">
-        <v>2.29</v>
-      </c>
-      <c r="U14">
-        <v>1.58</v>
-      </c>
-      <c r="V14">
-        <v>4.95</v>
-      </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Z14">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AA14">
-        <v>4.45</v>
+        <v>3.3</v>
       </c>
       <c r="AB14">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="AC14">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AD14">
-        <v>2.26</v>
+        <v>3.6</v>
       </c>
       <c r="AE14">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AF14">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG14">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH14">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="AI14">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AJ14" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="AK14" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="AL14" s="3">
         <v>45850.29166666666</v>
@@ -2876,7 +2996,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
         <v>96</v>
@@ -2888,7 +3008,7 @@
         <v>206</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2900,82 +3020,82 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L15">
-        <v>3.16</v>
+        <v>3.33</v>
       </c>
       <c r="M15">
-        <v>2.82</v>
+        <v>3.22</v>
       </c>
       <c r="N15">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="O15">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="P15">
-        <v>5.75</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q15">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="R15">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="S15">
-        <v>2.23</v>
+        <v>2.75</v>
       </c>
       <c r="T15">
-        <v>3.74</v>
+        <v>3</v>
       </c>
       <c r="U15">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="V15">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
         <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Z15">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AA15">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AB15">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="AC15">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AD15">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AE15">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AG15">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AH15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AI15">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AJ15" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="AK15" t="s">
         <v>286</v>
@@ -3016,31 +3136,31 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L16">
-        <v>2.13</v>
+        <v>3.16</v>
       </c>
       <c r="M16">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="N16">
-        <v>3.29</v>
+        <v>2.23</v>
       </c>
       <c r="O16">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="P16">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q16">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="R16">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="S16">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="T16">
         <v>3.74</v>
@@ -3049,28 +3169,28 @@
         <v>1.21</v>
       </c>
       <c r="V16">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Z16">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA16">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB16">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="AC16">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AD16">
         <v>5.5</v>
@@ -3079,10 +3199,10 @@
         <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG16">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH16">
         <v>11</v>
@@ -3123,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -3132,85 +3252,85 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L17">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="M17">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="N17">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="O17">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="P17">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q17">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="R17">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S17">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="T17">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="U17">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="V17">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AA17">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AB17">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AC17">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AD17">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AE17">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF17">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH17">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AI17">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AJ17" t="s">
         <v>286</v>
       </c>
       <c r="AK17" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="AL17" s="3">
         <v>45850.29166666666</v>
@@ -3224,7 +3344,7 @@
         <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
         <v>96</v>
@@ -3236,97 +3356,97 @@
         <v>209</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L18">
-        <v>2.86</v>
+        <v>1.45</v>
       </c>
       <c r="M18">
-        <v>3.23</v>
+        <v>4.2</v>
       </c>
       <c r="N18">
-        <v>2.17</v>
+        <v>5.2</v>
       </c>
       <c r="O18">
-        <v>2.03</v>
+        <v>1.36</v>
       </c>
       <c r="P18">
-        <v>8.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="Q18">
-        <v>1.97</v>
+        <v>3.25</v>
       </c>
       <c r="R18">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S18">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="T18">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="U18">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="V18">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z18">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AA18">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AB18">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AC18">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="AD18">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="AE18">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AF18">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG18">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH18">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI18">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AJ18" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="AK18" t="s">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="AL18" s="3">
         <v>45850.29166666666</v>
@@ -3340,7 +3460,7 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
         <v>96</v>
@@ -3352,97 +3472,97 @@
         <v>210</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L19">
-        <v>2.9</v>
+        <v>2.13</v>
       </c>
       <c r="M19">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="N19">
-        <v>2.22</v>
+        <v>3.29</v>
       </c>
       <c r="O19">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="P19">
-        <v>8.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="Q19">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="R19">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="S19">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="U19">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="V19">
-        <v>7.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z19">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AA19">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AB19">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="AC19">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AD19">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AE19">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AF19">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AH19">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AI19">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AJ19" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="AK19" t="s">
-        <v>286</v>
+        <v>319</v>
       </c>
       <c r="AL19" s="3">
         <v>45850.29166666666</v>
@@ -3468,19 +3588,19 @@
         <v>211</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L20">
         <v>1.82</v>
@@ -3555,10 +3675,10 @@
         <v>1.13</v>
       </c>
       <c r="AJ20" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="AK20" t="s">
-        <v>286</v>
+        <v>320</v>
       </c>
       <c r="AL20" s="3">
         <v>45850.3125</v>
@@ -3572,7 +3692,7 @@
         <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
         <v>96</v>
@@ -3584,7 +3704,7 @@
         <v>212</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -3596,82 +3716,82 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L21">
-        <v>2.28</v>
+        <v>1.1</v>
       </c>
       <c r="M21">
-        <v>3.15</v>
+        <v>6.5</v>
       </c>
       <c r="N21">
-        <v>2.85</v>
+        <v>21</v>
       </c>
       <c r="O21">
-        <v>1.8</v>
+        <v>1.12</v>
       </c>
       <c r="P21">
-        <v>8.699999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="Q21">
+        <v>6.3</v>
+      </c>
+      <c r="R21">
+        <v>1.25</v>
+      </c>
+      <c r="S21">
+        <v>3.75</v>
+      </c>
+      <c r="T21">
+        <v>2.15</v>
+      </c>
+      <c r="U21">
+        <v>1.65</v>
+      </c>
+      <c r="V21">
+        <v>4.8</v>
+      </c>
+      <c r="W21">
+        <v>1.17</v>
+      </c>
+      <c r="X21">
+        <v>1.03</v>
+      </c>
+      <c r="Y21">
+        <v>13</v>
+      </c>
+      <c r="Z21">
+        <v>1.15</v>
+      </c>
+      <c r="AA21">
+        <v>4.8</v>
+      </c>
+      <c r="AB21">
+        <v>1.5</v>
+      </c>
+      <c r="AC21">
         <v>2.3</v>
       </c>
-      <c r="R21">
-        <v>1.4</v>
-      </c>
-      <c r="S21">
-        <v>2.7</v>
-      </c>
-      <c r="T21">
-        <v>2.9</v>
-      </c>
-      <c r="U21">
-        <v>1.36</v>
-      </c>
-      <c r="V21">
-        <v>7</v>
-      </c>
-      <c r="W21">
-        <v>1.06</v>
-      </c>
-      <c r="X21">
-        <v>1</v>
-      </c>
-      <c r="Y21">
-        <v>8.5</v>
-      </c>
-      <c r="Z21">
-        <v>1.28</v>
-      </c>
-      <c r="AA21">
-        <v>3.1</v>
-      </c>
-      <c r="AB21">
-        <v>1.91</v>
-      </c>
-      <c r="AC21">
-        <v>1.73</v>
-      </c>
       <c r="AD21">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="AE21">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AF21">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="AG21">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AH21">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AI21">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AJ21" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="AK21" t="s">
         <v>286</v>
@@ -3688,7 +3808,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
         <v>96</v>
@@ -3700,97 +3820,97 @@
         <v>213</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L22">
-        <v>1.1</v>
+        <v>2.28</v>
       </c>
       <c r="M22">
+        <v>3.15</v>
+      </c>
+      <c r="N22">
+        <v>2.85</v>
+      </c>
+      <c r="O22">
+        <v>1.8</v>
+      </c>
+      <c r="P22">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Q22">
+        <v>2.3</v>
+      </c>
+      <c r="R22">
+        <v>1.4</v>
+      </c>
+      <c r="S22">
+        <v>2.7</v>
+      </c>
+      <c r="T22">
+        <v>2.92</v>
+      </c>
+      <c r="U22">
+        <v>1.33</v>
+      </c>
+      <c r="V22">
+        <v>7.25</v>
+      </c>
+      <c r="W22">
+        <v>1.08</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z22">
+        <v>1.28</v>
+      </c>
+      <c r="AA22">
+        <v>3.08</v>
+      </c>
+      <c r="AB22">
+        <v>2.05</v>
+      </c>
+      <c r="AC22">
+        <v>1.76</v>
+      </c>
+      <c r="AD22">
+        <v>3.48</v>
+      </c>
+      <c r="AE22">
+        <v>1.22</v>
+      </c>
+      <c r="AF22">
+        <v>1.81</v>
+      </c>
+      <c r="AG22">
+        <v>1.83</v>
+      </c>
+      <c r="AH22">
         <v>6.5</v>
       </c>
-      <c r="N22">
-        <v>21</v>
-      </c>
-      <c r="O22">
-        <v>1.12</v>
-      </c>
-      <c r="P22">
-        <v>15.5</v>
-      </c>
-      <c r="Q22">
-        <v>6.3</v>
-      </c>
-      <c r="R22">
-        <v>1.22</v>
-      </c>
-      <c r="S22">
-        <v>4</v>
-      </c>
-      <c r="T22">
-        <v>2.1</v>
-      </c>
-      <c r="U22">
-        <v>1.73</v>
-      </c>
-      <c r="V22">
-        <v>4.5</v>
-      </c>
-      <c r="W22">
-        <v>1.18</v>
-      </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
-      <c r="Y22">
-        <v>19</v>
-      </c>
-      <c r="Z22">
-        <v>1.12</v>
-      </c>
-      <c r="AA22">
-        <v>5.5</v>
-      </c>
-      <c r="AB22">
-        <v>1.43</v>
-      </c>
-      <c r="AC22">
-        <v>2.63</v>
-      </c>
-      <c r="AD22">
-        <v>2.05</v>
-      </c>
-      <c r="AE22">
-        <v>1.65</v>
-      </c>
-      <c r="AF22">
-        <v>2.25</v>
-      </c>
-      <c r="AG22">
-        <v>1.67</v>
-      </c>
-      <c r="AH22">
-        <v>3.6</v>
-      </c>
       <c r="AI22">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AJ22" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="AK22" t="s">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="AL22" s="3">
         <v>45850.33333333334</v>
@@ -3804,7 +3924,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
         <v>96</v>
@@ -3816,97 +3936,97 @@
         <v>214</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L23">
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="N23">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="O23">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>6.95</v>
+        <v>11.5</v>
       </c>
       <c r="Q23">
-        <v>2.04</v>
+        <v>1.4</v>
       </c>
       <c r="R23">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S23">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="T23">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U23">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V23">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Z23">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AA23">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="AB23">
         <v>1.95</v>
       </c>
       <c r="AC23">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AD23">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="AE23">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF23">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AG23">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH23">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="AI23">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AJ23" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="AK23" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="AL23" s="3">
         <v>45850.35416666666</v>
@@ -3944,16 +4064,16 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L24">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="M24">
-        <v>3.69</v>
+        <v>3.3</v>
       </c>
       <c r="N24">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="O24">
         <v>2.5</v>
@@ -3965,58 +4085,58 @@
         <v>1.53</v>
       </c>
       <c r="R24">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S24">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="T24">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U24">
         <v>1.44</v>
       </c>
       <c r="V24">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="Z24">
         <v>1.25</v>
       </c>
       <c r="AA24">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AB24">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC24">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD24">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AE24">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF24">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AH24">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="AI24">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AJ24" t="s">
         <v>286</v>
@@ -4036,7 +4156,7 @@
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
         <v>96</v>
@@ -4048,97 +4168,97 @@
         <v>216</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L25">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="M25">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="N25">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="P25">
-        <v>11.5</v>
+        <v>6.95</v>
       </c>
       <c r="Q25">
+        <v>2.04</v>
+      </c>
+      <c r="R25">
         <v>1.4</v>
       </c>
-      <c r="R25">
-        <v>1.44</v>
-      </c>
       <c r="S25">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="T25">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U25">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V25">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
+        <v>1.08</v>
+      </c>
+      <c r="Y25">
+        <v>8</v>
+      </c>
+      <c r="Z25">
+        <v>1.42</v>
+      </c>
+      <c r="AA25">
+        <v>2.62</v>
+      </c>
+      <c r="AB25">
+        <v>2.2</v>
+      </c>
+      <c r="AC25">
+        <v>1.65</v>
+      </c>
+      <c r="AD25">
+        <v>4.2</v>
+      </c>
+      <c r="AE25">
+        <v>1.2</v>
+      </c>
+      <c r="AF25">
+        <v>1.95</v>
+      </c>
+      <c r="AG25">
+        <v>1.75</v>
+      </c>
+      <c r="AH25">
+        <v>7.8</v>
+      </c>
+      <c r="AI25">
         <v>1.06</v>
       </c>
-      <c r="Y25">
-        <v>8.5</v>
-      </c>
-      <c r="Z25">
-        <v>1.36</v>
-      </c>
-      <c r="AA25">
-        <v>3.1</v>
-      </c>
-      <c r="AB25">
-        <v>1.91</v>
-      </c>
-      <c r="AC25">
-        <v>1.73</v>
-      </c>
-      <c r="AD25">
-        <v>3.8</v>
-      </c>
-      <c r="AE25">
-        <v>1.22</v>
-      </c>
-      <c r="AF25">
-        <v>2</v>
-      </c>
-      <c r="AG25">
-        <v>1.67</v>
-      </c>
-      <c r="AH25">
-        <v>8</v>
-      </c>
-      <c r="AI25">
-        <v>1.02</v>
-      </c>
       <c r="AJ25" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="AK25" t="s">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="AL25" s="3">
         <v>45850.35416666666</v>
@@ -4164,19 +4284,19 @@
         <v>217</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L26">
         <v>4.3</v>
@@ -4206,19 +4326,19 @@
         <v>2.9</v>
       </c>
       <c r="U26">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V26">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="Z26">
         <v>1.34</v>
@@ -4227,34 +4347,34 @@
         <v>3</v>
       </c>
       <c r="AB26">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AD26">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AE26">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF26">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG26">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH26">
         <v>6.5</v>
       </c>
       <c r="AI26">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AJ26" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="AK26" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="AL26" s="3">
         <v>45850.375</v>
@@ -4280,19 +4400,19 @@
         <v>218</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L27">
         <v>2.4</v>
@@ -4367,10 +4487,10 @@
         <v>1.14</v>
       </c>
       <c r="AJ27" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="AK27" t="s">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="AL27" s="3">
         <v>45850.41666666666</v>
@@ -4396,7 +4516,7 @@
         <v>219</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -4408,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L28">
         <v>1.26</v>
@@ -4483,7 +4603,7 @@
         <v>1.44</v>
       </c>
       <c r="AJ28" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="AK28" t="s">
         <v>286</v>
@@ -4524,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L29">
         <v>3.44</v>
@@ -4640,7 +4760,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4744,19 +4864,19 @@
         <v>222</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L31">
         <v>1.2</v>
@@ -4777,22 +4897,22 @@
         <v>4.33</v>
       </c>
       <c r="R31">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S31">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T31">
         <v>2.2</v>
       </c>
       <c r="U31">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V31">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="W31">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X31">
         <v>1.03</v>
@@ -4801,7 +4921,7 @@
         <v>10</v>
       </c>
       <c r="Z31">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AA31">
         <v>5</v>
@@ -4819,22 +4939,22 @@
         <v>1.7</v>
       </c>
       <c r="AF31">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AG31">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH31">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="AI31">
         <v>1.22</v>
       </c>
       <c r="AJ31" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="AK31" t="s">
-        <v>286</v>
+        <v>325</v>
       </c>
       <c r="AL31" s="3">
         <v>45850.45833333334</v>
@@ -4872,16 +4992,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L32">
-        <v>2.81</v>
+        <v>2.57</v>
       </c>
       <c r="M32">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="N32">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="O32">
         <v>2.05</v>
@@ -4923,10 +5043,10 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AC32">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AD32">
         <v>0</v>
@@ -4976,28 +5096,28 @@
         <v>224</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L33">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="M33">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N33">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="O33">
         <v>3.18</v>
@@ -5009,64 +5129,64 @@
         <v>1.47</v>
       </c>
       <c r="R33">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S33">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="T33">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="U33">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V33">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
         <v>1</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z33">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AA33">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AB33">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AC33">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AD33">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="AE33">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF33">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AG33">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AH33">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AI33">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AJ33" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="AK33" t="s">
-        <v>286</v>
+        <v>326</v>
       </c>
       <c r="AL33" s="3">
         <v>45850.5</v>
@@ -5092,19 +5212,19 @@
         <v>225</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L34">
         <v>1.46</v>
@@ -5179,10 +5299,10 @@
         <v>1.3</v>
       </c>
       <c r="AJ34" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="AK34" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="AL34" s="3">
         <v>45850.52083333334</v>
@@ -5220,79 +5340,79 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L35">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="M35">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="N35">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="O35">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="P35">
+        <v>7.9</v>
+      </c>
+      <c r="Q35">
+        <v>2.02</v>
+      </c>
+      <c r="R35">
+        <v>1.46</v>
+      </c>
+      <c r="S35">
+        <v>2.52</v>
+      </c>
+      <c r="T35">
+        <v>3.3</v>
+      </c>
+      <c r="U35">
+        <v>1.3</v>
+      </c>
+      <c r="V35">
+        <v>10</v>
+      </c>
+      <c r="W35">
+        <v>1.06</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
         <v>7.5</v>
       </c>
-      <c r="Q35">
-        <v>2.18</v>
-      </c>
-      <c r="R35">
-        <v>1.4</v>
-      </c>
-      <c r="S35">
-        <v>2.8</v>
-      </c>
-      <c r="T35">
-        <v>3</v>
-      </c>
-      <c r="U35">
-        <v>1.33</v>
-      </c>
-      <c r="V35">
-        <v>7.5</v>
-      </c>
-      <c r="W35">
+      <c r="Z35">
+        <v>1.36</v>
+      </c>
+      <c r="AA35">
+        <v>2.7</v>
+      </c>
+      <c r="AB35">
+        <v>2.2</v>
+      </c>
+      <c r="AC35">
+        <v>1.59</v>
+      </c>
+      <c r="AD35">
+        <v>4</v>
+      </c>
+      <c r="AE35">
+        <v>1.21</v>
+      </c>
+      <c r="AF35">
+        <v>1.85</v>
+      </c>
+      <c r="AG35">
+        <v>1.85</v>
+      </c>
+      <c r="AH35">
+        <v>8</v>
+      </c>
+      <c r="AI35">
         <v>1.05</v>
-      </c>
-      <c r="X35">
-        <v>1.05</v>
-      </c>
-      <c r="Y35">
-        <v>8</v>
-      </c>
-      <c r="Z35">
-        <v>1.33</v>
-      </c>
-      <c r="AA35">
-        <v>2.83</v>
-      </c>
-      <c r="AB35">
-        <v>2.1</v>
-      </c>
-      <c r="AC35">
-        <v>1.61</v>
-      </c>
-      <c r="AD35">
-        <v>3.58</v>
-      </c>
-      <c r="AE35">
-        <v>1.25</v>
-      </c>
-      <c r="AF35">
-        <v>1.9</v>
-      </c>
-      <c r="AG35">
-        <v>1.91</v>
-      </c>
-      <c r="AH35">
-        <v>6.95</v>
-      </c>
-      <c r="AI35">
-        <v>1.04</v>
       </c>
       <c r="AJ35" t="s">
         <v>286</v>
@@ -5321,7 +5441,7 @@
         <v>131</v>
       </c>
       <c r="F36" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -5336,16 +5456,16 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L36">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="M36">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="N36">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O36">
         <v>1.83</v>
@@ -5357,19 +5477,19 @@
         <v>2.6</v>
       </c>
       <c r="R36">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="S36">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="T36">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="U36">
         <v>1.18</v>
       </c>
       <c r="V36">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="W36">
         <v>1</v>
@@ -5378,31 +5498,31 @@
         <v>1.15</v>
       </c>
       <c r="Y36">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="Z36">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AA36">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB36">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="AC36">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AD36">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="AE36">
         <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG36">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AH36">
         <v>15.5</v>
@@ -5428,7 +5548,7 @@
         <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
         <v>96</v>
@@ -5440,97 +5560,97 @@
         <v>227</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L37">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="M37">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="N37">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="O37">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="P37">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="Q37">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S37">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T37">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U37">
+        <v>1.4</v>
+      </c>
+      <c r="V37">
+        <v>8</v>
+      </c>
+      <c r="W37">
+        <v>1.08</v>
+      </c>
+      <c r="X37">
+        <v>1.06</v>
+      </c>
+      <c r="Y37">
+        <v>8.5</v>
+      </c>
+      <c r="Z37">
         <v>1.33</v>
       </c>
-      <c r="V37">
-        <v>9.5</v>
-      </c>
-      <c r="W37">
-        <v>1.06</v>
-      </c>
-      <c r="X37">
-        <v>1.03</v>
-      </c>
-      <c r="Y37">
-        <v>7.5</v>
-      </c>
-      <c r="Z37">
-        <v>1.36</v>
-      </c>
       <c r="AA37">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AB37">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC37">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AD37">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="AE37">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AF37">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH37">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AI37">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AJ37" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="AK37" t="s">
-        <v>286</v>
+        <v>327</v>
       </c>
       <c r="AL37" s="3">
         <v>45850.54166666666</v>
@@ -5544,7 +5664,7 @@
         <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D38" t="s">
         <v>96</v>
@@ -5568,79 +5688,79 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L38">
+        <v>2.05</v>
+      </c>
+      <c r="M38">
+        <v>3.2</v>
+      </c>
+      <c r="N38">
+        <v>3.15</v>
+      </c>
+      <c r="O38">
+        <v>1.91</v>
+      </c>
+      <c r="P38">
+        <v>7.5</v>
+      </c>
+      <c r="Q38">
+        <v>2.18</v>
+      </c>
+      <c r="R38">
+        <v>1.42</v>
+      </c>
+      <c r="S38">
         <v>2.62</v>
       </c>
-      <c r="M38">
-        <v>3.1</v>
-      </c>
-      <c r="N38">
-        <v>2.41</v>
-      </c>
-      <c r="O38">
-        <v>1.83</v>
-      </c>
-      <c r="P38">
-        <v>8.5</v>
-      </c>
-      <c r="Q38">
-        <v>2.1</v>
-      </c>
-      <c r="R38">
-        <v>1.4</v>
-      </c>
-      <c r="S38">
-        <v>2.75</v>
-      </c>
       <c r="T38">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U38">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z38">
         <v>1.33</v>
       </c>
       <c r="AA38">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AB38">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AC38">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AD38">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AE38">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG38">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH38">
-        <v>6.5</v>
+        <v>6.85</v>
       </c>
       <c r="AI38">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AJ38" t="s">
         <v>286</v>
@@ -5684,73 +5804,73 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L39">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="M39">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="N39">
-        <v>5.2</v>
+        <v>2.45</v>
       </c>
       <c r="O39">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="P39">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="Q39">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="S39">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="T39">
         <v>3.5</v>
       </c>
       <c r="U39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V39">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="W39">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y39">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="Z39">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AA39">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AB39">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="AC39">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AD39">
         <v>5</v>
       </c>
       <c r="AE39">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG39">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH39">
         <v>10</v>
@@ -5800,79 +5920,79 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L40">
-        <v>3.27</v>
+        <v>2.25</v>
       </c>
       <c r="M40">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="N40">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="O40">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="P40">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q40">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="R40">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="S40">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="T40">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="U40">
         <v>1.25</v>
       </c>
       <c r="V40">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W40">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X40">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y40">
-        <v>6.2</v>
+        <v>5.75</v>
       </c>
       <c r="Z40">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA40">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AB40">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AC40">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AD40">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AE40">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF40">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG40">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH40">
-        <v>11</v>
+        <v>8.9</v>
       </c>
       <c r="AI40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ40" t="s">
         <v>286</v>
@@ -5916,16 +6036,16 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L41">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="M41">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="N41">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="O41">
         <v>2.25</v>
@@ -5937,52 +6057,52 @@
         <v>2.05</v>
       </c>
       <c r="R41">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="S41">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="T41">
         <v>4.33</v>
       </c>
       <c r="U41">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V41">
         <v>13</v>
       </c>
       <c r="W41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X41">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Y41">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="Z41">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AA41">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AB41">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AC41">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AD41">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AE41">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="AG41">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AH41">
         <v>12</v>
@@ -6032,16 +6152,16 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L42">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="M42">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N42">
-        <v>3.84</v>
+        <v>4.6</v>
       </c>
       <c r="O42">
         <v>1.62</v>
@@ -6059,7 +6179,7 @@
         <v>2.25</v>
       </c>
       <c r="T42">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U42">
         <v>1.25</v>
@@ -6068,40 +6188,40 @@
         <v>11</v>
       </c>
       <c r="W42">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X42">
+        <v>1.07</v>
+      </c>
+      <c r="Y42">
+        <v>5.75</v>
+      </c>
+      <c r="Z42">
+        <v>1.54</v>
+      </c>
+      <c r="AA42">
+        <v>2.33</v>
+      </c>
+      <c r="AB42">
+        <v>2.45</v>
+      </c>
+      <c r="AC42">
+        <v>1.44</v>
+      </c>
+      <c r="AD42">
+        <v>5.05</v>
+      </c>
+      <c r="AE42">
         <v>1.1</v>
       </c>
-      <c r="Y42">
-        <v>5.5</v>
-      </c>
-      <c r="Z42">
-        <v>1.5</v>
-      </c>
-      <c r="AA42">
+      <c r="AF42">
         <v>2.3</v>
       </c>
-      <c r="AB42">
-        <v>2.73</v>
-      </c>
-      <c r="AC42">
-        <v>1.4</v>
-      </c>
-      <c r="AD42">
-        <v>5.2</v>
-      </c>
-      <c r="AE42">
-        <v>1.12</v>
-      </c>
-      <c r="AF42">
-        <v>2.32</v>
-      </c>
       <c r="AG42">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AH42">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AI42">
         <v>1.02</v>
@@ -6148,16 +6268,16 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L43">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="M43">
-        <v>3.31</v>
+        <v>3.56</v>
       </c>
       <c r="N43">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
       <c r="O43">
         <v>2.1</v>
@@ -6169,34 +6289,34 @@
         <v>1.95</v>
       </c>
       <c r="R43">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S43">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="T43">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="U43">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="V43">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z43">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AA43">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AB43">
         <v>1.77</v>
@@ -6205,22 +6325,22 @@
         <v>1.93</v>
       </c>
       <c r="AD43">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AE43">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AF43">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG43">
         <v>2.1</v>
       </c>
       <c r="AH43">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AI43">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AJ43" t="s">
         <v>286</v>
@@ -6264,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L44">
-        <v>3.58</v>
+        <v>4.9</v>
       </c>
       <c r="M44">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="N44">
-        <v>2.03</v>
+        <v>1.73</v>
       </c>
       <c r="O44">
         <v>3.6</v>
@@ -6291,43 +6411,43 @@
         <v>2.25</v>
       </c>
       <c r="T44">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U44">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V44">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="W44">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X44">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y44">
         <v>5.75</v>
       </c>
       <c r="Z44">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AA44">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AB44">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="AC44">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AD44">
-        <v>5.85</v>
+        <v>5</v>
       </c>
       <c r="AE44">
         <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AG44">
         <v>1.44</v>
@@ -6380,16 +6500,16 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L45">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="M45">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="N45">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="O45">
         <v>1.57</v>
@@ -6401,16 +6521,16 @@
         <v>3.4</v>
       </c>
       <c r="R45">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="S45">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="T45">
         <v>4.2</v>
       </c>
       <c r="U45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V45">
         <v>11.5</v>
@@ -6419,34 +6539,34 @@
         <v>1.03</v>
       </c>
       <c r="X45">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Y45">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
       <c r="Z45">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AA45">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AB45">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AC45">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AD45">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="AE45">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF45">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AG45">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AH45">
         <v>13.5</v>
@@ -6496,16 +6616,16 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L46">
-        <v>4.6</v>
+        <v>4.92</v>
       </c>
       <c r="M46">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="N46">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="O46">
         <v>3</v>
@@ -6517,16 +6637,16 @@
         <v>1.57</v>
       </c>
       <c r="R46">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S46">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="T46">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U46">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V46">
         <v>8.5</v>
@@ -6535,37 +6655,37 @@
         <v>1.06</v>
       </c>
       <c r="X46">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y46">
         <v>7.5</v>
       </c>
       <c r="Z46">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AA46">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AB46">
         <v>2.15</v>
       </c>
       <c r="AC46">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AD46">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="AE46">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF46">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="AG46">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH46">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AI46">
         <v>1.06</v>
@@ -6612,79 +6732,79 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L47">
+        <v>2.3</v>
+      </c>
+      <c r="M47">
+        <v>3.3</v>
+      </c>
+      <c r="N47">
+        <v>2.95</v>
+      </c>
+      <c r="O47">
+        <v>1.87</v>
+      </c>
+      <c r="P47">
+        <v>8</v>
+      </c>
+      <c r="Q47">
+        <v>2.2</v>
+      </c>
+      <c r="R47">
+        <v>1.44</v>
+      </c>
+      <c r="S47">
+        <v>2.6</v>
+      </c>
+      <c r="T47">
+        <v>3</v>
+      </c>
+      <c r="U47">
+        <v>1.33</v>
+      </c>
+      <c r="V47">
+        <v>8.25</v>
+      </c>
+      <c r="W47">
+        <v>1.06</v>
+      </c>
+      <c r="X47">
+        <v>1.07</v>
+      </c>
+      <c r="Y47">
+        <v>8</v>
+      </c>
+      <c r="Z47">
+        <v>1.36</v>
+      </c>
+      <c r="AA47">
+        <v>2.87</v>
+      </c>
+      <c r="AB47">
+        <v>2.05</v>
+      </c>
+      <c r="AC47">
+        <v>1.65</v>
+      </c>
+      <c r="AD47">
+        <v>3.7</v>
+      </c>
+      <c r="AE47">
+        <v>1.24</v>
+      </c>
+      <c r="AF47">
+        <v>1.87</v>
+      </c>
+      <c r="AG47">
         <v>1.8</v>
       </c>
-      <c r="M47">
-        <v>3.5</v>
-      </c>
-      <c r="N47">
-        <v>5</v>
-      </c>
-      <c r="O47">
-        <v>1.53</v>
-      </c>
-      <c r="P47">
-        <v>5.75</v>
-      </c>
-      <c r="Q47">
-        <v>3.4</v>
-      </c>
-      <c r="R47">
-        <v>1.57</v>
-      </c>
-      <c r="S47">
-        <v>2.25</v>
-      </c>
-      <c r="T47">
-        <v>3.75</v>
-      </c>
-      <c r="U47">
-        <v>1.25</v>
-      </c>
-      <c r="V47">
-        <v>13</v>
-      </c>
-      <c r="W47">
-        <v>1.04</v>
-      </c>
-      <c r="X47">
-        <v>1.11</v>
-      </c>
-      <c r="Y47">
-        <v>6.25</v>
-      </c>
-      <c r="Z47">
-        <v>1.55</v>
-      </c>
-      <c r="AA47">
-        <v>2.3</v>
-      </c>
-      <c r="AB47">
-        <v>2.7</v>
-      </c>
-      <c r="AC47">
-        <v>1.44</v>
-      </c>
-      <c r="AD47">
-        <v>5.5</v>
-      </c>
-      <c r="AE47">
-        <v>1.14</v>
-      </c>
-      <c r="AF47">
-        <v>2.5</v>
-      </c>
-      <c r="AG47">
-        <v>1.5</v>
-      </c>
       <c r="AH47">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="AI47">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AJ47" t="s">
         <v>286</v>
@@ -6704,7 +6824,7 @@
         <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D48" t="s">
         <v>96</v>
@@ -6728,79 +6848,79 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L48">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="M48">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="N48">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="O48">
         <v>1.53</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q48">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB48">
-        <v>1.76</v>
+        <v>2.7</v>
       </c>
       <c r="AC48">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="AD48">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="AE48">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH48">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI48">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ48" t="s">
         <v>286</v>
@@ -6820,7 +6940,7 @@
         <v>58</v>
       </c>
       <c r="C49" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D49" t="s">
         <v>96</v>
@@ -6844,76 +6964,76 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L49">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="M49">
+        <v>3.1</v>
+      </c>
+      <c r="N49">
+        <v>2.5</v>
+      </c>
+      <c r="O49">
+        <v>1.67</v>
+      </c>
+      <c r="P49">
+        <v>6.75</v>
+      </c>
+      <c r="Q49">
+        <v>2.38</v>
+      </c>
+      <c r="R49">
+        <v>1.33</v>
+      </c>
+      <c r="S49">
+        <v>2.9</v>
+      </c>
+      <c r="T49">
+        <v>2.68</v>
+      </c>
+      <c r="U49">
+        <v>1.4</v>
+      </c>
+      <c r="V49">
+        <v>7</v>
+      </c>
+      <c r="W49">
+        <v>1.08</v>
+      </c>
+      <c r="X49">
+        <v>1.05</v>
+      </c>
+      <c r="Y49">
+        <v>10</v>
+      </c>
+      <c r="Z49">
+        <v>1.29</v>
+      </c>
+      <c r="AA49">
         <v>3.3</v>
       </c>
-      <c r="N49">
-        <v>2.95</v>
-      </c>
-      <c r="O49">
-        <v>1.87</v>
-      </c>
-      <c r="P49">
-        <v>8</v>
-      </c>
-      <c r="Q49">
-        <v>2.2</v>
-      </c>
-      <c r="R49">
-        <v>1.44</v>
-      </c>
-      <c r="S49">
-        <v>2.6</v>
-      </c>
-      <c r="T49">
+      <c r="AB49">
+        <v>1.83</v>
+      </c>
+      <c r="AC49">
+        <v>1.8</v>
+      </c>
+      <c r="AD49">
         <v>3</v>
       </c>
-      <c r="U49">
-        <v>1.33</v>
-      </c>
-      <c r="V49">
-        <v>8.25</v>
-      </c>
-      <c r="W49">
-        <v>1.06</v>
-      </c>
-      <c r="X49">
-        <v>1.07</v>
-      </c>
-      <c r="Y49">
-        <v>8</v>
-      </c>
-      <c r="Z49">
-        <v>1.36</v>
-      </c>
-      <c r="AA49">
-        <v>2.87</v>
-      </c>
-      <c r="AB49">
-        <v>2.05</v>
-      </c>
-      <c r="AC49">
-        <v>1.65</v>
-      </c>
-      <c r="AD49">
-        <v>3.7</v>
-      </c>
       <c r="AE49">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AF49">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AG49">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AH49">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="AI49">
         <v>1.08</v>
@@ -6936,7 +7056,7 @@
         <v>58</v>
       </c>
       <c r="C50" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D50" t="s">
         <v>96</v>
@@ -6960,79 +7080,79 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L50">
-        <v>2.24</v>
+        <v>1.75</v>
       </c>
       <c r="M50">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="N50">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="O50">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P50">
-        <v>6.75</v>
+        <v>10</v>
       </c>
       <c r="Q50">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="R50">
+        <v>1.35</v>
+      </c>
+      <c r="S50">
+        <v>2.9</v>
+      </c>
+      <c r="T50">
+        <v>2.6</v>
+      </c>
+      <c r="U50">
+        <v>1.44</v>
+      </c>
+      <c r="V50">
+        <v>6.4</v>
+      </c>
+      <c r="W50">
+        <v>1.08</v>
+      </c>
+      <c r="X50">
+        <v>1.02</v>
+      </c>
+      <c r="Y50">
+        <v>10</v>
+      </c>
+      <c r="Z50">
+        <v>1.25</v>
+      </c>
+      <c r="AA50">
+        <v>3.6</v>
+      </c>
+      <c r="AB50">
+        <v>1.8</v>
+      </c>
+      <c r="AC50">
+        <v>1.91</v>
+      </c>
+      <c r="AD50">
+        <v>2.9</v>
+      </c>
+      <c r="AE50">
         <v>1.36</v>
       </c>
-      <c r="S50">
-        <v>2.8</v>
-      </c>
-      <c r="T50">
-        <v>2.9</v>
-      </c>
-      <c r="U50">
-        <v>1.36</v>
-      </c>
-      <c r="V50">
-        <v>7.5</v>
-      </c>
-      <c r="W50">
-        <v>1.07</v>
-      </c>
-      <c r="X50">
-        <v>1.04</v>
-      </c>
-      <c r="Y50">
-        <v>8.5</v>
-      </c>
-      <c r="Z50">
-        <v>1.3</v>
-      </c>
-      <c r="AA50">
-        <v>3.2</v>
-      </c>
-      <c r="AB50">
+      <c r="AF50">
+        <v>1.7</v>
+      </c>
+      <c r="AG50">
         <v>2.1</v>
       </c>
-      <c r="AC50">
-        <v>1.61</v>
-      </c>
-      <c r="AD50">
-        <v>3.4</v>
-      </c>
-      <c r="AE50">
-        <v>1.27</v>
-      </c>
-      <c r="AF50">
-        <v>1.73</v>
-      </c>
-      <c r="AG50">
-        <v>1.93</v>
-      </c>
       <c r="AH50">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="AI50">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AJ50" t="s">
         <v>286</v>
@@ -7076,16 +7196,16 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L51">
-        <v>1.74</v>
+        <v>2.13</v>
       </c>
       <c r="M51">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="N51">
-        <v>4.5</v>
+        <v>3.79</v>
       </c>
       <c r="O51">
         <v>1.67</v>
@@ -7097,46 +7217,46 @@
         <v>2.88</v>
       </c>
       <c r="R51">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S51">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="T51">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U51">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="V51">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W51">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X51">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y51">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Z51">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AA51">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="AB51">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AC51">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AD51">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AE51">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
         <v>2.2</v>
@@ -7145,10 +7265,10 @@
         <v>1.62</v>
       </c>
       <c r="AH51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI51">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ51" t="s">
         <v>286</v>
@@ -7192,49 +7312,49 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L52">
+        <v>1.66</v>
+      </c>
+      <c r="M52">
+        <v>3.6</v>
+      </c>
+      <c r="N52">
+        <v>6</v>
+      </c>
+      <c r="O52">
         <v>1.44</v>
       </c>
-      <c r="M52">
-        <v>4.1</v>
-      </c>
-      <c r="N52">
-        <v>8</v>
-      </c>
-      <c r="O52">
-        <v>1.37</v>
-      </c>
       <c r="P52">
-        <v>8.25</v>
+        <v>7.5</v>
       </c>
       <c r="Q52">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="R52">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S52">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T52">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="U52">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V52">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="Z52">
         <v>1.33</v>
@@ -7243,28 +7363,28 @@
         <v>3</v>
       </c>
       <c r="AB52">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC52">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AD52">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AE52">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF52">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG52">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH52">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="AI52">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AJ52" t="s">
         <v>286</v>
@@ -7308,79 +7428,79 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L53">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="M53">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="N53">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="O53">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="P53">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="Q53">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="R53">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S53">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="T53">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U53">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="V53">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W53">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X53">
         <v>1.06</v>
       </c>
       <c r="Y53">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Z53">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AA53">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AB53">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="AC53">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AD53">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AE53">
         <v>1.22</v>
       </c>
       <c r="AF53">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AG53">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AH53">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AI53">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ53" t="s">
         <v>286</v>
@@ -7400,7 +7520,7 @@
         <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D54" t="s">
         <v>96</v>
@@ -7409,7 +7529,7 @@
         <v>149</v>
       </c>
       <c r="F54" t="s">
-        <v>243</v>
+        <v>131</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -7427,76 +7547,76 @@
         <v>283</v>
       </c>
       <c r="L54">
-        <v>2.09</v>
+        <v>1.5</v>
       </c>
       <c r="M54">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="N54">
-        <v>3.89</v>
+        <v>6.75</v>
       </c>
       <c r="O54">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>0</v>
+      </c>
+      <c r="AB54">
         <v>2.5</v>
       </c>
-      <c r="R54">
-        <v>1.63</v>
-      </c>
-      <c r="S54">
-        <v>2.15</v>
-      </c>
-      <c r="T54">
-        <v>3.7</v>
-      </c>
-      <c r="U54">
-        <v>1.25</v>
-      </c>
-      <c r="V54">
-        <v>10</v>
-      </c>
-      <c r="W54">
-        <v>1.04</v>
-      </c>
-      <c r="X54">
-        <v>1.11</v>
-      </c>
-      <c r="Y54">
-        <v>5.5</v>
-      </c>
-      <c r="Z54">
+      <c r="AC54">
         <v>1.5</v>
       </c>
-      <c r="AA54">
-        <v>2.3</v>
-      </c>
-      <c r="AB54">
-        <v>2.94</v>
-      </c>
-      <c r="AC54">
-        <v>1.35</v>
-      </c>
       <c r="AD54">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AE54">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF54">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG54">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH54">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AI54">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="s">
         <v>286</v>
@@ -7525,7 +7645,7 @@
         <v>150</v>
       </c>
       <c r="F55" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -7540,79 +7660,79 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L55">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="M55">
-        <v>2.79</v>
+        <v>2.96</v>
       </c>
       <c r="N55">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="O55">
         <v>1.8</v>
       </c>
       <c r="P55">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="Q55">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R55">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="S55">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="T55">
-        <v>3</v>
+        <v>3.94</v>
       </c>
       <c r="U55">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="V55">
-        <v>8.25</v>
+        <v>11.5</v>
       </c>
       <c r="W55">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X55">
+        <v>1.11</v>
+      </c>
+      <c r="Y55">
+        <v>5.5</v>
+      </c>
+      <c r="Z55">
+        <v>1.6</v>
+      </c>
+      <c r="AA55">
+        <v>2.25</v>
+      </c>
+      <c r="AB55">
+        <v>2.78</v>
+      </c>
+      <c r="AC55">
+        <v>1.38</v>
+      </c>
+      <c r="AD55">
+        <v>5.8</v>
+      </c>
+      <c r="AE55">
+        <v>1.11</v>
+      </c>
+      <c r="AF55">
+        <v>2.2</v>
+      </c>
+      <c r="AG55">
+        <v>1.6</v>
+      </c>
+      <c r="AH55">
+        <v>13</v>
+      </c>
+      <c r="AI55">
         <v>1.02</v>
-      </c>
-      <c r="Y55">
-        <v>8.1</v>
-      </c>
-      <c r="Z55">
-        <v>1.36</v>
-      </c>
-      <c r="AA55">
-        <v>2.9</v>
-      </c>
-      <c r="AB55">
-        <v>2.25</v>
-      </c>
-      <c r="AC55">
-        <v>1.5</v>
-      </c>
-      <c r="AD55">
-        <v>3.78</v>
-      </c>
-      <c r="AE55">
-        <v>1.22</v>
-      </c>
-      <c r="AF55">
-        <v>1.83</v>
-      </c>
-      <c r="AG55">
-        <v>1.83</v>
-      </c>
-      <c r="AH55">
-        <v>7.5</v>
-      </c>
-      <c r="AI55">
-        <v>1.03</v>
       </c>
       <c r="AJ55" t="s">
         <v>286</v>
@@ -7632,7 +7752,7 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D56" t="s">
         <v>96</v>
@@ -7641,7 +7761,7 @@
         <v>151</v>
       </c>
       <c r="F56" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -7659,76 +7779,76 @@
         <v>284</v>
       </c>
       <c r="L56">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="M56">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N56">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Z56">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA56">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH56">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AI56">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ56" t="s">
         <v>286</v>
@@ -7757,7 +7877,7 @@
         <v>152</v>
       </c>
       <c r="F57" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -7772,16 +7892,16 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L57">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="M57">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N57">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -7811,16 +7931,16 @@
         <v>0</v>
       </c>
       <c r="X57">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y57">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Z57">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AA57">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AB57">
         <v>0</v>
@@ -7888,7 +8008,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -8004,7 +8124,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L59">
         <v>1.87</v>
@@ -8105,7 +8225,7 @@
         <v>155</v>
       </c>
       <c r="F60" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -8120,16 +8240,16 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -8159,16 +8279,16 @@
         <v>0</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB60">
         <v>0</v>
@@ -8221,7 +8341,7 @@
         <v>156</v>
       </c>
       <c r="F61" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -8236,16 +8356,16 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L61">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="M61">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N61">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -8281,7 +8401,7 @@
         <v>0</v>
       </c>
       <c r="Z61">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA61">
         <v>2.38</v>
@@ -8337,7 +8457,7 @@
         <v>157</v>
       </c>
       <c r="F62" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -8352,16 +8472,16 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L62">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="M62">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N62">
-        <v>4.02</v>
+        <v>4.15</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -8397,10 +8517,10 @@
         <v>0</v>
       </c>
       <c r="Z62">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AA62">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB62">
         <v>0</v>
@@ -8453,7 +8573,7 @@
         <v>158</v>
       </c>
       <c r="F63" t="s">
-        <v>131</v>
+        <v>248</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -8468,16 +8588,16 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L63">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M63">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N63">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -8519,10 +8639,10 @@
         <v>0</v>
       </c>
       <c r="AB63">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC63">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD63">
         <v>0</v>
@@ -8584,16 +8704,16 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L64">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="M64">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="N64">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="O64">
         <v>1.95</v>
@@ -8605,58 +8725,58 @@
         <v>2.5</v>
       </c>
       <c r="R64">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="S64">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T64">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U64">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V64">
         <v>9</v>
       </c>
       <c r="W64">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X64">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Y64">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="Z64">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AA64">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB64">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="AC64">
         <v>1.3</v>
       </c>
       <c r="AD64">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AE64">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF64">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="AG64">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH64">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI64">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ64" t="s">
         <v>286</v>
@@ -8676,7 +8796,7 @@
         <v>62</v>
       </c>
       <c r="C65" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D65" t="s">
         <v>96</v>
@@ -8700,79 +8820,79 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L65">
-        <v>3.3</v>
+        <v>2.49</v>
       </c>
       <c r="M65">
-        <v>3.16</v>
+        <v>2.83</v>
       </c>
       <c r="N65">
-        <v>2.25</v>
+        <v>3.09</v>
       </c>
       <c r="O65">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="P65">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="Q65">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="R65">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="S65">
-        <v>2.51</v>
+        <v>2.23</v>
       </c>
       <c r="T65">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="U65">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="V65">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="W65">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X65">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y65">
-        <v>7.8</v>
+        <v>5.75</v>
       </c>
       <c r="Z65">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AA65">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="AB65">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="AC65">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AD65">
-        <v>4.47</v>
+        <v>5</v>
       </c>
       <c r="AE65">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF65">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG65">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AH65">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AI65">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ65" t="s">
         <v>286</v>
@@ -8792,7 +8912,7 @@
         <v>62</v>
       </c>
       <c r="C66" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D66" t="s">
         <v>96</v>
@@ -8816,25 +8936,25 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L66">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="M66">
+        <v>2.9</v>
+      </c>
+      <c r="N66">
+        <v>3.8</v>
+      </c>
+      <c r="O66">
+        <v>1.73</v>
+      </c>
+      <c r="P66">
+        <v>5.75</v>
+      </c>
+      <c r="Q66">
         <v>2.75</v>
-      </c>
-      <c r="N66">
-        <v>3.05</v>
-      </c>
-      <c r="O66">
-        <v>1.91</v>
-      </c>
-      <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>2.4</v>
       </c>
       <c r="R66">
         <v>1.57</v>
@@ -8855,28 +8975,28 @@
         <v>1.04</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Z66">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AA66">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB66">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AC66">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF66">
         <v>2.2</v>
@@ -8885,10 +9005,10 @@
         <v>1.62</v>
       </c>
       <c r="AH66">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI66">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ66" t="s">
         <v>286</v>
@@ -8908,7 +9028,7 @@
         <v>62</v>
       </c>
       <c r="C67" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D67" t="s">
         <v>96</v>
@@ -8932,79 +9052,79 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L67">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="M67">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N67">
-        <v>4.5</v>
+        <v>2.14</v>
       </c>
       <c r="O67">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="P67">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="Q67">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="R67">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="S67">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="T67">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="U67">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="V67">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="W67">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X67">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y67">
-        <v>5.75</v>
+        <v>7.99</v>
       </c>
       <c r="Z67">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AA67">
-        <v>2.25</v>
+        <v>2.78</v>
       </c>
       <c r="AB67">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="AC67">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AD67">
-        <v>6</v>
+        <v>4.62</v>
       </c>
       <c r="AE67">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF67">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AG67">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AH67">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="AI67">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ67" t="s">
         <v>286</v>
@@ -9024,7 +9144,7 @@
         <v>62</v>
       </c>
       <c r="C68" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D68" t="s">
         <v>96</v>
@@ -9048,37 +9168,37 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L68">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M68">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N68">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="O68">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="P68">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q68">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R68">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S68">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T68">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U68">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V68">
         <v>13</v>
@@ -9093,34 +9213,34 @@
         <v>5.75</v>
       </c>
       <c r="Z68">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AA68">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB68">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC68">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AD68">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AE68">
         <v>1.12</v>
       </c>
       <c r="AF68">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AG68">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AH68">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI68">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ68" t="s">
         <v>286</v>
@@ -9149,7 +9269,7 @@
         <v>164</v>
       </c>
       <c r="F69" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -9164,16 +9284,16 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L69">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="M69">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N69">
-        <v>4.6</v>
+        <v>5.58</v>
       </c>
       <c r="O69">
         <v>1.6</v>
@@ -9185,55 +9305,55 @@
         <v>3.25</v>
       </c>
       <c r="R69">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="S69">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="T69">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="U69">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V69">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W69">
         <v>1</v>
       </c>
       <c r="X69">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Y69">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="Z69">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AA69">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB69">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="AC69">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AD69">
-        <v>6</v>
+        <v>6.95</v>
       </c>
       <c r="AE69">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF69">
         <v>2.75</v>
       </c>
       <c r="AG69">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH69">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI69">
         <v>1</v>
@@ -9280,7 +9400,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L70">
         <v>2.95</v>
@@ -9301,58 +9421,58 @@
         <v>1.73</v>
       </c>
       <c r="R70">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S70">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="T70">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="U70">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V70">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W70">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X70">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>12.3</v>
+        <v>9.5</v>
       </c>
       <c r="Z70">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AA70">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="AB70">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC70">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AD70">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="AE70">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AF70">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG70">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AH70">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AI70">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AJ70" t="s">
         <v>286</v>
@@ -9396,16 +9516,16 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L71">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="M71">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="N71">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="O71">
         <v>1.73</v>
@@ -9417,40 +9537,40 @@
         <v>2.75</v>
       </c>
       <c r="R71">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="S71">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="T71">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="U71">
         <v>1.22</v>
       </c>
       <c r="V71">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W71">
         <v>1.03</v>
       </c>
       <c r="X71">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y71">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="Z71">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AA71">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AB71">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="AC71">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AD71">
         <v>6</v>
@@ -9459,10 +9579,10 @@
         <v>1.08</v>
       </c>
       <c r="AF71">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG71">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AH71">
         <v>13</v>
@@ -9512,7 +9632,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L72">
         <v>2.34</v>
@@ -9533,55 +9653,55 @@
         <v>2.5</v>
       </c>
       <c r="R72">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="S72">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="T72">
         <v>3.8</v>
       </c>
       <c r="U72">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="V72">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="W72">
         <v>1.02</v>
       </c>
       <c r="X72">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Y72">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Z72">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AA72">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AB72">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="AC72">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AD72">
-        <v>6.05</v>
+        <v>6.55</v>
       </c>
       <c r="AE72">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF72">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG72">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH72">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AI72">
         <v>1.01</v>
@@ -9604,7 +9724,7 @@
         <v>65</v>
       </c>
       <c r="C73" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D73" t="s">
         <v>96</v>
@@ -9628,79 +9748,79 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L73">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="M73">
+        <v>2.9</v>
+      </c>
+      <c r="N73">
         <v>3.25</v>
       </c>
-      <c r="N73">
-        <v>2.75</v>
-      </c>
       <c r="O73">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="P73">
-        <v>11.75</v>
+        <v>7.7</v>
       </c>
       <c r="Q73">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R73">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="S73">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T73">
-        <v>2.75</v>
+        <v>3.48</v>
       </c>
       <c r="U73">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V73">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W73">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y73">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z73">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AA73">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="AB73">
-        <v>1.89</v>
+        <v>2.49</v>
       </c>
       <c r="AC73">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AD73">
-        <v>3.28</v>
+        <v>4.5</v>
       </c>
       <c r="AE73">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AF73">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AG73">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AH73">
-        <v>6.75</v>
+        <v>10</v>
       </c>
       <c r="AI73">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ73" t="s">
         <v>286</v>
@@ -9744,16 +9864,16 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L74">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="M74">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N74">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="O74">
         <v>1.47</v>
@@ -9765,58 +9885,58 @@
         <v>2.88</v>
       </c>
       <c r="R74">
+        <v>1.43</v>
+      </c>
+      <c r="S74">
+        <v>2.82</v>
+      </c>
+      <c r="T74">
+        <v>2.93</v>
+      </c>
+      <c r="U74">
         <v>1.36</v>
       </c>
-      <c r="S74">
-        <v>2.75</v>
-      </c>
-      <c r="T74">
-        <v>2.8</v>
-      </c>
-      <c r="U74">
-        <v>1.4</v>
-      </c>
       <c r="V74">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W74">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y74">
-        <v>9</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Z74">
         <v>1.3</v>
       </c>
       <c r="AA74">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AB74">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AC74">
         <v>1.75</v>
       </c>
       <c r="AD74">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AE74">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF74">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG74">
         <v>1.9</v>
       </c>
       <c r="AH74">
-        <v>6</v>
+        <v>7.05</v>
       </c>
       <c r="AI74">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AJ74" t="s">
         <v>286</v>
@@ -9836,7 +9956,7 @@
         <v>65</v>
       </c>
       <c r="C75" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D75" t="s">
         <v>96</v>
@@ -9860,40 +9980,40 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L75">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="M75">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="N75">
-        <v>3.02</v>
+        <v>2.84</v>
       </c>
       <c r="O75">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="P75">
-        <v>7.7</v>
+        <v>11.75</v>
       </c>
       <c r="Q75">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R75">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S75">
-        <v>2.8</v>
+        <v>3.01</v>
       </c>
       <c r="T75">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U75">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V75">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W75">
         <v>1.06</v>
@@ -9902,37 +10022,37 @@
         <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z75">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AA75">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB75">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AC75">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AD75">
         <v>3.4</v>
       </c>
       <c r="AE75">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF75">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG75">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="AH75">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AI75">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ75" t="s">
         <v>286</v>
@@ -9976,79 +10096,79 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L76">
-        <v>1.92</v>
+        <v>2.46</v>
       </c>
       <c r="M76">
-        <v>3.75</v>
+        <v>3.33</v>
       </c>
       <c r="N76">
-        <v>3.02</v>
+        <v>2.42</v>
       </c>
       <c r="O76">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="P76">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="Q76">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R76">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S76">
-        <v>3.75</v>
+        <v>3.18</v>
       </c>
       <c r="T76">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="U76">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="V76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W76">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X76">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y76">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="Z76">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AA76">
-        <v>5.75</v>
+        <v>3.94</v>
       </c>
       <c r="AB76">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AC76">
-        <v>2.74</v>
+        <v>1.95</v>
       </c>
       <c r="AD76">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="AE76">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AF76">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AG76">
-        <v>2.9</v>
+        <v>2.21</v>
       </c>
       <c r="AH76">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="AI76">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AJ76" t="s">
         <v>286</v>
@@ -10068,7 +10188,7 @@
         <v>66</v>
       </c>
       <c r="C77" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D77" t="s">
         <v>96</v>
@@ -10092,79 +10212,79 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L77">
-        <v>2.48</v>
+        <v>1.39</v>
       </c>
       <c r="M77">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="N77">
-        <v>2.44</v>
+        <v>5.8</v>
       </c>
       <c r="O77">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="P77">
-        <v>9.300000000000001</v>
+        <v>17.75</v>
       </c>
       <c r="Q77">
-        <v>2.14</v>
+        <v>3.4</v>
       </c>
       <c r="R77">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="S77">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="T77">
-        <v>2.46</v>
+        <v>2.21</v>
       </c>
       <c r="U77">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="V77">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="W77">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X77">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z77">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AA77">
-        <v>3.94</v>
+        <v>4.6</v>
       </c>
       <c r="AB77">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AC77">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="AD77">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="AE77">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AF77">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG77">
-        <v>2.36</v>
+        <v>1.96</v>
       </c>
       <c r="AH77">
-        <v>5.06</v>
+        <v>3.88</v>
       </c>
       <c r="AI77">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AJ77" t="s">
         <v>286</v>
@@ -10184,7 +10304,7 @@
         <v>66</v>
       </c>
       <c r="C78" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D78" t="s">
         <v>96</v>
@@ -10208,79 +10328,79 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L78">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="M78">
-        <v>3.06</v>
+        <v>3.45</v>
       </c>
       <c r="N78">
-        <v>4.4</v>
+        <v>3.31</v>
       </c>
       <c r="O78">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="P78">
-        <v>6.25</v>
+        <v>10</v>
       </c>
       <c r="Q78">
+        <v>2.25</v>
+      </c>
+      <c r="R78">
+        <v>1.28</v>
+      </c>
+      <c r="S78">
         <v>3.4</v>
       </c>
-      <c r="R78">
-        <v>1.53</v>
-      </c>
-      <c r="S78">
+      <c r="T78">
+        <v>2.2</v>
+      </c>
+      <c r="U78">
+        <v>1.6</v>
+      </c>
+      <c r="V78">
+        <v>4.75</v>
+      </c>
+      <c r="W78">
+        <v>1.15</v>
+      </c>
+      <c r="X78">
+        <v>1.04</v>
+      </c>
+      <c r="Y78">
+        <v>10</v>
+      </c>
+      <c r="Z78">
+        <v>1.18</v>
+      </c>
+      <c r="AA78">
+        <v>4.75</v>
+      </c>
+      <c r="AB78">
+        <v>1.48</v>
+      </c>
+      <c r="AC78">
+        <v>2.54</v>
+      </c>
+      <c r="AD78">
+        <v>2.25</v>
+      </c>
+      <c r="AE78">
+        <v>1.57</v>
+      </c>
+      <c r="AF78">
+        <v>1.48</v>
+      </c>
+      <c r="AG78">
         <v>2.5</v>
       </c>
-      <c r="T78">
-        <v>3.45</v>
-      </c>
-      <c r="U78">
-        <v>1.29</v>
-      </c>
-      <c r="V78">
-        <v>10</v>
-      </c>
-      <c r="W78">
-        <v>1.03</v>
-      </c>
-      <c r="X78">
-        <v>1.05</v>
-      </c>
-      <c r="Y78">
-        <v>6</v>
-      </c>
-      <c r="Z78">
-        <v>1.48</v>
-      </c>
-      <c r="AA78">
-        <v>2.35</v>
-      </c>
-      <c r="AB78">
-        <v>2.37</v>
-      </c>
-      <c r="AC78">
-        <v>1.48</v>
-      </c>
-      <c r="AD78">
-        <v>4.8</v>
-      </c>
-      <c r="AE78">
-        <v>1.17</v>
-      </c>
-      <c r="AF78">
-        <v>2.25</v>
-      </c>
-      <c r="AG78">
-        <v>1.62</v>
-      </c>
       <c r="AH78">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AI78">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AJ78" t="s">
         <v>286</v>
@@ -10324,79 +10444,79 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L79">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="M79">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N79">
-        <v>3.73</v>
+        <v>3.02</v>
       </c>
       <c r="O79">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="P79">
-        <v>9.300000000000001</v>
+        <v>21</v>
       </c>
       <c r="Q79">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="R79">
+        <v>1.22</v>
+      </c>
+      <c r="S79">
+        <v>3.75</v>
+      </c>
+      <c r="T79">
+        <v>2</v>
+      </c>
+      <c r="U79">
+        <v>1.73</v>
+      </c>
+      <c r="V79">
+        <v>4</v>
+      </c>
+      <c r="W79">
+        <v>1.2</v>
+      </c>
+      <c r="X79">
+        <v>1.01</v>
+      </c>
+      <c r="Y79">
+        <v>17</v>
+      </c>
+      <c r="Z79">
+        <v>1.12</v>
+      </c>
+      <c r="AA79">
+        <v>5.75</v>
+      </c>
+      <c r="AB79">
+        <v>1.42</v>
+      </c>
+      <c r="AC79">
+        <v>2.74</v>
+      </c>
+      <c r="AD79">
+        <v>2</v>
+      </c>
+      <c r="AE79">
+        <v>1.72</v>
+      </c>
+      <c r="AF79">
+        <v>1.36</v>
+      </c>
+      <c r="AG79">
+        <v>2.9</v>
+      </c>
+      <c r="AH79">
+        <v>3.2</v>
+      </c>
+      <c r="AI79">
         <v>1.33</v>
-      </c>
-      <c r="S79">
-        <v>2.93</v>
-      </c>
-      <c r="T79">
-        <v>2.51</v>
-      </c>
-      <c r="U79">
-        <v>1.44</v>
-      </c>
-      <c r="V79">
-        <v>5.75</v>
-      </c>
-      <c r="W79">
-        <v>1.07</v>
-      </c>
-      <c r="X79">
-        <v>1</v>
-      </c>
-      <c r="Y79">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Z79">
-        <v>1.22</v>
-      </c>
-      <c r="AA79">
-        <v>3.64</v>
-      </c>
-      <c r="AB79">
-        <v>1.76</v>
-      </c>
-      <c r="AC79">
-        <v>1.94</v>
-      </c>
-      <c r="AD79">
-        <v>2.83</v>
-      </c>
-      <c r="AE79">
-        <v>1.35</v>
-      </c>
-      <c r="AF79">
-        <v>1.69</v>
-      </c>
-      <c r="AG79">
-        <v>2.04</v>
-      </c>
-      <c r="AH79">
-        <v>5.1</v>
-      </c>
-      <c r="AI79">
-        <v>1.1</v>
       </c>
       <c r="AJ79" t="s">
         <v>286</v>
@@ -10440,43 +10560,43 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L80">
-        <v>1.39</v>
+        <v>2.02</v>
       </c>
       <c r="M80">
-        <v>4.33</v>
+        <v>3.69</v>
       </c>
       <c r="N80">
-        <v>5.8</v>
+        <v>2.84</v>
       </c>
       <c r="O80">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="P80">
-        <v>17.75</v>
+        <v>11</v>
       </c>
       <c r="Q80">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="R80">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S80">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="T80">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="U80">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="V80">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="W80">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X80">
         <v>1.03</v>
@@ -10485,34 +10605,34 @@
         <v>11</v>
       </c>
       <c r="Z80">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AA80">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AB80">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC80">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AD80">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AE80">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AF80">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AG80">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="AH80">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="AI80">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ80" t="s">
         <v>286</v>
@@ -10532,7 +10652,7 @@
         <v>66</v>
       </c>
       <c r="C81" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D81" t="s">
         <v>96</v>
@@ -10556,79 +10676,79 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L81">
-        <v>2.46</v>
+        <v>1.84</v>
       </c>
       <c r="M81">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="N81">
-        <v>2.42</v>
+        <v>4.8</v>
       </c>
       <c r="O81">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="P81">
-        <v>14.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q81">
-        <v>1.98</v>
+        <v>3.4</v>
       </c>
       <c r="R81">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="S81">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="T81">
-        <v>2.48</v>
+        <v>3.56</v>
       </c>
       <c r="U81">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="V81">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="W81">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X81">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y81">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z81">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="AA81">
-        <v>3.94</v>
+        <v>2.5</v>
       </c>
       <c r="AB81">
-        <v>1.75</v>
+        <v>2.44</v>
       </c>
       <c r="AC81">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AD81">
-        <v>2.78</v>
+        <v>4.75</v>
       </c>
       <c r="AE81">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AF81">
-        <v>1.59</v>
+        <v>2.25</v>
       </c>
       <c r="AG81">
-        <v>2.21</v>
+        <v>1.6</v>
       </c>
       <c r="AH81">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="AI81">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AJ81" t="s">
         <v>286</v>
@@ -10648,7 +10768,7 @@
         <v>66</v>
       </c>
       <c r="C82" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D82" t="s">
         <v>96</v>
@@ -10672,79 +10792,79 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L82">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M82">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N82">
-        <v>3.31</v>
+        <v>2.81</v>
       </c>
       <c r="O82">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="P82">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q82">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="R82">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S82">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T82">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="U82">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="V82">
-        <v>4.75</v>
+        <v>5.95</v>
       </c>
       <c r="W82">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X82">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y82">
         <v>10</v>
       </c>
       <c r="Z82">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AA82">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="AB82">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AC82">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="AD82">
+        <v>2.6</v>
+      </c>
+      <c r="AE82">
+        <v>1.42</v>
+      </c>
+      <c r="AF82">
+        <v>1.6</v>
+      </c>
+      <c r="AG82">
         <v>2.25</v>
       </c>
-      <c r="AE82">
-        <v>1.57</v>
-      </c>
-      <c r="AF82">
-        <v>1.48</v>
-      </c>
-      <c r="AG82">
-        <v>2.5</v>
-      </c>
       <c r="AH82">
-        <v>4.2</v>
+        <v>5.21</v>
       </c>
       <c r="AI82">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AJ82" t="s">
         <v>286</v>
@@ -10788,79 +10908,79 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L83">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="M83">
-        <v>3.69</v>
+        <v>3.45</v>
       </c>
       <c r="N83">
-        <v>2.84</v>
+        <v>3.73</v>
       </c>
       <c r="O83">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="P83">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q83">
-        <v>2.2</v>
+        <v>2.57</v>
       </c>
       <c r="R83">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S83">
-        <v>3.75</v>
+        <v>2.93</v>
       </c>
       <c r="T83">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="U83">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="V83">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W83">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X83">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y83">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z83">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AA83">
-        <v>5</v>
+        <v>3.64</v>
       </c>
       <c r="AB83">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AC83">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="AD83">
-        <v>2.22</v>
+        <v>2.83</v>
       </c>
       <c r="AE83">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AF83">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AG83">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="AH83">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="AI83">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AJ83" t="s">
         <v>286</v>
@@ -10880,7 +11000,7 @@
         <v>67</v>
       </c>
       <c r="C84" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D84" t="s">
         <v>96</v>
@@ -10904,7 +11024,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L84">
         <v>1.48</v>
@@ -11020,16 +11140,16 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L85">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="M85">
         <v>3</v>
       </c>
       <c r="N85">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="O85">
         <v>1.73</v>
@@ -11044,43 +11164,43 @@
         <v>1.53</v>
       </c>
       <c r="S85">
-        <v>2.28</v>
+        <v>2.58</v>
       </c>
       <c r="T85">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U85">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V85">
-        <v>7.8</v>
+        <v>9.5</v>
       </c>
       <c r="W85">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X85">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y85">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="Z85">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AA85">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AB85">
         <v>2.25</v>
       </c>
       <c r="AC85">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AD85">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE85">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF85">
         <v>1.9</v>
@@ -11089,7 +11209,7 @@
         <v>1.75</v>
       </c>
       <c r="AH85">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AI85">
         <v>1.03</v>
@@ -11112,7 +11232,7 @@
         <v>69</v>
       </c>
       <c r="C86" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D86" t="s">
         <v>96</v>
@@ -11136,79 +11256,79 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L86">
-        <v>1.86</v>
+        <v>2.86</v>
       </c>
       <c r="M86">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="N86">
-        <v>3.85</v>
+        <v>2.04</v>
       </c>
       <c r="O86">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="P86">
-        <v>7.9</v>
+        <v>12.5</v>
       </c>
       <c r="Q86">
-        <v>2.71</v>
+        <v>1.67</v>
       </c>
       <c r="R86">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S86">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T86">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="U86">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V86">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W86">
+        <v>1.14</v>
+      </c>
+      <c r="X86">
         <v>1.04</v>
       </c>
-      <c r="X86">
-        <v>1.03</v>
-      </c>
       <c r="Y86">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z86">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AA86">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AB86">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AC86">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="AD86">
-        <v>3.42</v>
+        <v>2.55</v>
       </c>
       <c r="AE86">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AF86">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AG86">
-        <v>1.76</v>
+        <v>2.38</v>
       </c>
       <c r="AH86">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="AI86">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AJ86" t="s">
         <v>286</v>
@@ -11252,7 +11372,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L87">
         <v>2.06</v>
@@ -11368,7 +11488,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L88">
         <v>1.77</v>
@@ -11484,79 +11604,79 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L89">
-        <v>2.86</v>
+        <v>2.34</v>
       </c>
       <c r="M89">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="N89">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="O89">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P89">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S89">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T89">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U89">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V89">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W89">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X89">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y89">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z89">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA89">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB89">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AC89">
-        <v>2.07</v>
+        <v>2.82</v>
       </c>
       <c r="AD89">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AE89">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AF89">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG89">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH89">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI89">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ89" t="s">
         <v>286</v>
@@ -11576,7 +11696,7 @@
         <v>69</v>
       </c>
       <c r="C90" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D90" t="s">
         <v>96</v>
@@ -11600,79 +11720,79 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L90">
-        <v>2.34</v>
+        <v>1.62</v>
       </c>
       <c r="M90">
+        <v>3.76</v>
+      </c>
+      <c r="N90">
+        <v>5.25</v>
+      </c>
+      <c r="O90">
+        <v>1.61</v>
+      </c>
+      <c r="P90">
+        <v>7.9</v>
+      </c>
+      <c r="Q90">
+        <v>2.71</v>
+      </c>
+      <c r="R90">
+        <v>1.36</v>
+      </c>
+      <c r="S90">
+        <v>2.9</v>
+      </c>
+      <c r="T90">
+        <v>2.7</v>
+      </c>
+      <c r="U90">
+        <v>1.4</v>
+      </c>
+      <c r="V90">
+        <v>6.85</v>
+      </c>
+      <c r="W90">
+        <v>1.08</v>
+      </c>
+      <c r="X90">
+        <v>1</v>
+      </c>
+      <c r="Y90">
+        <v>9</v>
+      </c>
+      <c r="Z90">
+        <v>1.3</v>
+      </c>
+      <c r="AA90">
+        <v>3.14</v>
+      </c>
+      <c r="AB90">
+        <v>1.94</v>
+      </c>
+      <c r="AC90">
+        <v>1.8</v>
+      </c>
+      <c r="AD90">
         <v>3.45</v>
       </c>
-      <c r="N90">
-        <v>2.48</v>
-      </c>
-      <c r="O90">
-        <v>0</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
-        <v>0</v>
-      </c>
-      <c r="R90">
-        <v>0</v>
-      </c>
-      <c r="S90">
-        <v>0</v>
-      </c>
-      <c r="T90">
-        <v>0</v>
-      </c>
-      <c r="U90">
-        <v>0</v>
-      </c>
-      <c r="V90">
-        <v>0</v>
-      </c>
-      <c r="W90">
-        <v>0</v>
-      </c>
-      <c r="X90">
-        <v>0</v>
-      </c>
-      <c r="Y90">
-        <v>0</v>
-      </c>
-      <c r="Z90">
-        <v>0</v>
-      </c>
-      <c r="AA90">
-        <v>0</v>
-      </c>
-      <c r="AB90">
-        <v>1.4</v>
-      </c>
-      <c r="AC90">
-        <v>2.82</v>
-      </c>
-      <c r="AD90">
-        <v>2.05</v>
-      </c>
       <c r="AE90">
-        <v>1.68</v>
+        <v>1.29</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH90">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AI90">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ90" t="s">
         <v>286</v>
@@ -11716,16 +11836,16 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L91">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="M91">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N91">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="O91">
         <v>2.3</v>
@@ -11737,55 +11857,55 @@
         <v>1.73</v>
       </c>
       <c r="R91">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S91">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T91">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U91">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="V91">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W91">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y91">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z91">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA91">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AB91">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC91">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD91">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="AE91">
         <v>1.36</v>
       </c>
       <c r="AF91">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG91">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AH91">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AI91">
         <v>1.11</v>
@@ -11832,16 +11952,16 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L92">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="M92">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N92">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="O92">
         <v>1.53</v>
@@ -11853,19 +11973,19 @@
         <v>2.63</v>
       </c>
       <c r="R92">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S92">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="T92">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U92">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V92">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W92">
         <v>1.09</v>
@@ -11877,22 +11997,22 @@
         <v>10</v>
       </c>
       <c r="Z92">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AA92">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB92">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC92">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AD92">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AE92">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF92">
         <v>1.7</v>
@@ -11901,10 +12021,10 @@
         <v>2.1</v>
       </c>
       <c r="AH92">
-        <v>6.2</v>
+        <v>6.15</v>
       </c>
       <c r="AI92">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AJ92" t="s">
         <v>286</v>
@@ -11948,7 +12068,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L93">
         <v>1.92</v>
@@ -12064,7 +12184,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L94">
         <v>2.2</v>
@@ -12180,16 +12300,16 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L95">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="M95">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N95">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O95">
         <v>1.92</v>
@@ -12201,58 +12321,58 @@
         <v>1.94</v>
       </c>
       <c r="R95">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S95">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T95">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="U95">
         <v>1.36</v>
       </c>
       <c r="V95">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W95">
         <v>1.08</v>
       </c>
       <c r="X95">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y95">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="Z95">
+        <v>1.33</v>
+      </c>
+      <c r="AA95">
+        <v>3.2</v>
+      </c>
+      <c r="AB95">
+        <v>2</v>
+      </c>
+      <c r="AC95">
+        <v>1.73</v>
+      </c>
+      <c r="AD95">
+        <v>3.7</v>
+      </c>
+      <c r="AE95">
         <v>1.25</v>
       </c>
-      <c r="AA95">
-        <v>3.1</v>
-      </c>
-      <c r="AB95">
-        <v>1.95</v>
-      </c>
-      <c r="AC95">
-        <v>1.7</v>
-      </c>
-      <c r="AD95">
-        <v>3.4</v>
-      </c>
-      <c r="AE95">
-        <v>1.27</v>
-      </c>
       <c r="AF95">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG95">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH95">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI95">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AJ95" t="s">
         <v>286</v>
@@ -12296,79 +12416,79 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L96">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="M96">
-        <v>3.66</v>
+        <v>4.2</v>
       </c>
       <c r="N96">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="O96">
+        <v>1.3</v>
+      </c>
+      <c r="P96">
+        <v>15</v>
+      </c>
+      <c r="Q96">
+        <v>3.4</v>
+      </c>
+      <c r="R96">
+        <v>1.25</v>
+      </c>
+      <c r="S96">
+        <v>3.75</v>
+      </c>
+      <c r="T96">
+        <v>2.1</v>
+      </c>
+      <c r="U96">
+        <v>1.67</v>
+      </c>
+      <c r="V96">
+        <v>4.5</v>
+      </c>
+      <c r="W96">
+        <v>1.18</v>
+      </c>
+      <c r="X96">
+        <v>1.01</v>
+      </c>
+      <c r="Y96">
+        <v>17</v>
+      </c>
+      <c r="Z96">
+        <v>1.15</v>
+      </c>
+      <c r="AA96">
+        <v>5.25</v>
+      </c>
+      <c r="AB96">
         <v>1.44</v>
       </c>
-      <c r="P96">
-        <v>11</v>
-      </c>
-      <c r="Q96">
-        <v>2.88</v>
-      </c>
-      <c r="R96">
-        <v>1.33</v>
-      </c>
-      <c r="S96">
-        <v>3.25</v>
-      </c>
-      <c r="T96">
-        <v>2.5</v>
-      </c>
-      <c r="U96">
-        <v>1.5</v>
-      </c>
-      <c r="V96">
-        <v>6.5</v>
-      </c>
-      <c r="W96">
-        <v>1.11</v>
-      </c>
-      <c r="X96">
-        <v>1.05</v>
-      </c>
-      <c r="Y96">
-        <v>9.5</v>
-      </c>
-      <c r="Z96">
+      <c r="AC96">
+        <v>2.67</v>
+      </c>
+      <c r="AD96">
+        <v>2.12</v>
+      </c>
+      <c r="AE96">
+        <v>1.64</v>
+      </c>
+      <c r="AF96">
+        <v>1.67</v>
+      </c>
+      <c r="AG96">
+        <v>2.1</v>
+      </c>
+      <c r="AH96">
+        <v>3.85</v>
+      </c>
+      <c r="AI96">
         <v>1.25</v>
-      </c>
-      <c r="AA96">
-        <v>3.8</v>
-      </c>
-      <c r="AB96">
-        <v>1.57</v>
-      </c>
-      <c r="AC96">
-        <v>2.25</v>
-      </c>
-      <c r="AD96">
-        <v>2.3</v>
-      </c>
-      <c r="AE96">
-        <v>1.55</v>
-      </c>
-      <c r="AF96">
-        <v>1.75</v>
-      </c>
-      <c r="AG96">
-        <v>2</v>
-      </c>
-      <c r="AH96">
-        <v>5.5</v>
-      </c>
-      <c r="AI96">
-        <v>1.14</v>
       </c>
       <c r="AJ96" t="s">
         <v>286</v>
@@ -12412,79 +12532,79 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L97">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="M97">
-        <v>4.2</v>
+        <v>3.66</v>
       </c>
       <c r="N97">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="O97">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="P97">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q97">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R97">
+        <v>1.33</v>
+      </c>
+      <c r="S97">
+        <v>3.25</v>
+      </c>
+      <c r="T97">
+        <v>2.5</v>
+      </c>
+      <c r="U97">
+        <v>1.5</v>
+      </c>
+      <c r="V97">
+        <v>6.5</v>
+      </c>
+      <c r="W97">
+        <v>1.11</v>
+      </c>
+      <c r="X97">
+        <v>1.05</v>
+      </c>
+      <c r="Y97">
+        <v>9.5</v>
+      </c>
+      <c r="Z97">
         <v>1.25</v>
       </c>
-      <c r="S97">
-        <v>3.75</v>
-      </c>
-      <c r="T97">
-        <v>2.1</v>
-      </c>
-      <c r="U97">
-        <v>1.67</v>
-      </c>
-      <c r="V97">
-        <v>4.5</v>
-      </c>
-      <c r="W97">
-        <v>1.18</v>
-      </c>
-      <c r="X97">
-        <v>1.01</v>
-      </c>
-      <c r="Y97">
-        <v>17</v>
-      </c>
-      <c r="Z97">
-        <v>1.15</v>
-      </c>
       <c r="AA97">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="AB97">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC97">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AD97">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="AE97">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AF97">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG97">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH97">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="AI97">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AJ97" t="s">
         <v>286</v>

--- a/jogos_2025-07-12.xlsx
+++ b/jogos_2025-07-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="337">
   <si>
     <t>Date</t>
   </si>
@@ -244,15 +244,15 @@
     <t>Japan J2 League</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
     <t>China China League One</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
@@ -262,27 +262,30 @@
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
-    <t>Finland Veikkausliiga</t>
+    <t>Argentina Prim B Nacional</t>
   </si>
   <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Chile Primera División</t>
   </si>
   <si>
@@ -292,9 +295,6 @@
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
@@ -313,54 +313,54 @@
     <t>Mt Druitt Town</t>
   </si>
   <si>
+    <t>Blaublitz Akita</t>
+  </si>
+  <si>
+    <t>Iwaki</t>
+  </si>
+  <si>
+    <t>Mito Hollyhock</t>
+  </si>
+  <si>
     <t>Western Sydney W. II</t>
   </si>
   <si>
-    <t>Iwaki</t>
-  </si>
-  <si>
-    <t>Mito Hollyhock</t>
-  </si>
-  <si>
-    <t>Blaublitz Akita</t>
-  </si>
-  <si>
     <t>Imabari</t>
   </si>
   <si>
     <t>Ventforet Kofu</t>
   </si>
   <si>
+    <t>Renofa Yamaguchi</t>
+  </si>
+  <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
+    <t>Montedio Yamagata</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Sagan Tosu</t>
+  </si>
+  <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
+    <t>Busan I'Park</t>
+  </si>
+  <si>
+    <t>Fujieda MYFC</t>
+  </si>
+  <si>
     <t>Jeonnam Dragons</t>
   </si>
   <si>
-    <t>Cheonan City</t>
-  </si>
-  <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
-    <t>Fujieda MYFC</t>
-  </si>
-  <si>
-    <t>Yanbian Longding</t>
-  </si>
-  <si>
-    <t>Renofa Yamaguchi</t>
-  </si>
-  <si>
-    <t>Montedio Yamagata</t>
-  </si>
-  <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
-    <t>Sagan Tosu</t>
-  </si>
-  <si>
     <t>Jubilo Iwata</t>
   </si>
   <si>
@@ -370,33 +370,33 @@
     <t>Shaanxi Union</t>
   </si>
   <si>
+    <t>Vaprus</t>
+  </si>
+  <si>
+    <t>Dongguan United</t>
+  </si>
+  <si>
     <t>Qingdao Red Lions</t>
   </si>
   <si>
-    <t>Vaprus</t>
-  </si>
-  <si>
-    <t>Dongguan United</t>
-  </si>
-  <si>
     <t>Ulytau</t>
   </si>
   <si>
     <t>IFK Göteborg</t>
   </si>
   <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Inter Turku</t>
+  </si>
+  <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
-    <t>Santos</t>
-  </si>
-  <si>
     <t>Ilves</t>
   </si>
   <si>
-    <t>Inter Turku</t>
-  </si>
-  <si>
     <t>Mirassol</t>
   </si>
   <si>
@@ -406,12 +406,12 @@
     <t>Malmö FF</t>
   </si>
   <si>
+    <t>All Boys</t>
+  </si>
+  <si>
     <t>Unión San Felipe</t>
   </si>
   <si>
-    <t>All Boys</t>
-  </si>
-  <si>
     <t>Fredrikstad</t>
   </si>
   <si>
@@ -430,18 +430,21 @@
     <t>Deportivo Morón</t>
   </si>
   <si>
+    <t>Defensores Unidos</t>
+  </si>
+  <si>
     <t>Longford Town</t>
   </si>
   <si>
-    <t>Defensores Unidos</t>
-  </si>
-  <si>
     <t>Temperley</t>
   </si>
   <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
+    <t>Novorizontino</t>
+  </si>
+  <si>
     <t>Universidad Chile</t>
   </si>
   <si>
@@ -454,132 +457,129 @@
     <t>Rangers</t>
   </si>
   <si>
-    <t>Novorizontino</t>
-  </si>
-  <si>
     <t>Internacional</t>
   </si>
   <si>
     <t>Flamengo</t>
   </si>
   <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Patronato</t>
+  </si>
+  <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
+    <t>Racing Córdoba</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
+  </si>
+  <si>
+    <t>São Bernardo</t>
+  </si>
+  <si>
     <t>San Miguel</t>
   </si>
   <si>
-    <t>São Bernardo</t>
-  </si>
-  <si>
-    <t>Itabaiana</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
-    <t>Gimnasia Mendoza</t>
-  </si>
-  <si>
-    <t>Patronato</t>
-  </si>
-  <si>
     <t>Almagro</t>
   </si>
   <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
     <t>Estudiantes Caseros</t>
   </si>
   <si>
+    <t>Huracán</t>
+  </si>
+  <si>
+    <t>Gimnasia La Plata</t>
+  </si>
+  <si>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
     <t>Paysandu</t>
   </si>
   <si>
-    <t>Gimnasia La Plata</t>
-  </si>
-  <si>
-    <t>Vasco da Gama</t>
-  </si>
-  <si>
-    <t>Huracán</t>
+    <t>Pacific FC</t>
   </si>
   <si>
     <t>San Martín Tucumán</t>
   </si>
   <si>
-    <t>Pacific FC</t>
-  </si>
-  <si>
     <t>Tombense</t>
   </si>
   <si>
     <t>Floresta</t>
   </si>
   <si>
+    <t>Indy Eleven</t>
+  </si>
+  <si>
     <t>Univ. Concepción</t>
   </si>
   <si>
     <t>Detroit City FC</t>
   </si>
   <si>
-    <t>Indy Eleven</t>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
+    <t>Atlético PR</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
   </si>
   <si>
     <t>Toronto</t>
   </si>
   <si>
-    <t>Orlando City</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
-    <t>Atlético PR</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
     <t>Racing Club</t>
   </si>
   <si>
     <t>Bahia</t>
   </si>
   <si>
+    <t>Tulsa Roughnecks</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
     <t>Sporting KC</t>
   </si>
   <si>
+    <t>Minnesota United</t>
+  </si>
+  <si>
     <t>Austin</t>
   </si>
   <si>
-    <t>Minnesota United</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>Tulsa Roughnecks</t>
+    <t>San Antonio</t>
   </si>
   <si>
     <t>New Mexico United</t>
   </si>
   <si>
-    <t>San Antonio</t>
-  </si>
-  <si>
     <t>Real Salt Lake</t>
   </si>
   <si>
@@ -601,54 +601,54 @@
     <t>Sydney II</t>
   </si>
   <si>
+    <t>Roasso Kumamoto</t>
+  </si>
+  <si>
+    <t>V-Varen Nagasaki</t>
+  </si>
+  <si>
+    <t>Kataller Toyama</t>
+  </si>
+  <si>
     <t>Marconi Stallions</t>
   </si>
   <si>
-    <t>V-Varen Nagasaki</t>
-  </si>
-  <si>
-    <t>Kataller Toyama</t>
-  </si>
-  <si>
-    <t>Roasso Kumamoto</t>
-  </si>
-  <si>
     <t>Ehime</t>
   </si>
   <si>
     <t>Omiya Ardija</t>
   </si>
   <si>
+    <t>Tokushima Vortis</t>
+  </si>
+  <si>
+    <t>Daegu</t>
+  </si>
+  <si>
+    <t>JEF United</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
+    <t>Oita Trinita</t>
+  </si>
+  <si>
+    <t>Guangzhou E-Power</t>
+  </si>
+  <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
+    <t>Vegalta Sendai</t>
+  </si>
+  <si>
     <t>Gyeongnam</t>
   </si>
   <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
-    <t>Seongnam</t>
-  </si>
-  <si>
-    <t>Vegalta Sendai</t>
-  </si>
-  <si>
-    <t>Guangzhou E-Power</t>
-  </si>
-  <si>
-    <t>Tokushima Vortis</t>
-  </si>
-  <si>
-    <t>JEF United</t>
-  </si>
-  <si>
-    <t>Daegu</t>
-  </si>
-  <si>
-    <t>Oita Trinita</t>
-  </si>
-  <si>
     <t>Consadole Sapporo</t>
   </si>
   <si>
@@ -658,33 +658,33 @@
     <t>Suzhou Dongwu</t>
   </si>
   <si>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>Shenzhen Juniors</t>
+  </si>
+  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Shenzhen Juniors</t>
-  </si>
-  <si>
     <t>Yelimay Semey</t>
   </si>
   <si>
     <t>Elfsborg</t>
   </si>
   <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
+    <t>Jaro</t>
+  </si>
+  <si>
     <t>Sandefjord</t>
   </si>
   <si>
-    <t>Palmeiras</t>
-  </si>
-  <si>
     <t>VPS</t>
   </si>
   <si>
-    <t>Jaro</t>
-  </si>
-  <si>
     <t>Fluminense</t>
   </si>
   <si>
@@ -724,6 +724,9 @@
     <t>Derry City</t>
   </si>
   <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
     <t>Colo-Colo</t>
   </si>
   <si>
@@ -736,48 +739,45 @@
     <t>Deportes Santa Cruz</t>
   </si>
   <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
     <t>Vitória</t>
   </si>
   <si>
     <t>São Paulo</t>
   </si>
   <si>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Confiança</t>
+  </si>
+  <si>
+    <t>Arsenal de Sarandí</t>
+  </si>
+  <si>
     <t>Ponte Preta</t>
   </si>
   <si>
-    <t>Confiança</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
     <t>Alvarado</t>
   </si>
   <si>
-    <t>Arsenal de Sarandí</t>
-  </si>
-  <si>
-    <t>Deportivo Madryn</t>
-  </si>
-  <si>
     <t>Gimnasia Jujuy</t>
   </si>
   <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
     <t>Atlético GO</t>
   </si>
   <si>
-    <t>Instituto</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
     <t>HFX Wanderers FC</t>
   </si>
   <si>
@@ -787,66 +787,66 @@
     <t>Ypiranga Erechim</t>
   </si>
   <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
     <t>Santiago Wanderers</t>
   </si>
   <si>
     <t>Hartford Athletic</t>
   </si>
   <si>
-    <t>Rhode Island</t>
+    <t>Montreal Impact</t>
+  </si>
+  <si>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>Goiás</t>
+  </si>
+  <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
+    <t>Columbus Crew</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
+    <t>Lexington</t>
   </si>
   <si>
     <t>Atlanta United FC</t>
   </si>
   <si>
-    <t>Montreal Impact</t>
-  </si>
-  <si>
-    <t>New York City</t>
-  </si>
-  <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
-    <t>Columbus Crew</t>
-  </si>
-  <si>
-    <t>Goiás</t>
-  </si>
-  <si>
-    <t>Lexington</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
     <t>Barracas Central</t>
   </si>
   <si>
     <t>Atlético Mineiro</t>
   </si>
   <si>
+    <t>Las Vegas Lights</t>
+  </si>
+  <si>
+    <t>San Diego</t>
+  </si>
+  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
     <t>New England Revolution</t>
   </si>
   <si>
-    <t>SJ Earthquakes</t>
-  </si>
-  <si>
-    <t>San Diego</t>
-  </si>
-  <si>
-    <t>Las Vegas Lights</t>
+    <t>Tampa Bay Rowdies</t>
   </si>
   <si>
     <t>Charleston Battery</t>
   </si>
   <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
     <t>Houston Dynamo</t>
   </si>
   <si>
@@ -877,42 +877,42 @@
     <t>[]</t>
   </si>
   <si>
+    <t>['25', '45+1', '45+4']</t>
+  </si>
+  <si>
     <t>['69']</t>
   </si>
   <si>
     <t>['56', '64', '79']</t>
   </si>
   <si>
-    <t>['25', '45+1', '45+4']</t>
-  </si>
-  <si>
     <t>['85']</t>
   </si>
   <si>
     <t>['47']</t>
   </si>
   <si>
+    <t>['64', '79']</t>
+  </si>
+  <si>
+    <t>['87']</t>
+  </si>
+  <si>
+    <t>['18', '59']</t>
+  </si>
+  <si>
+    <t>['69', '51']</t>
+  </si>
+  <si>
+    <t>['78', '90+1']</t>
+  </si>
+  <si>
+    <t>['31']</t>
+  </si>
+  <si>
     <t>['14']</t>
   </si>
   <si>
-    <t>['78', '90+1']</t>
-  </si>
-  <si>
-    <t>['87']</t>
-  </si>
-  <si>
-    <t>['31']</t>
-  </si>
-  <si>
-    <t>['69', '51']</t>
-  </si>
-  <si>
-    <t>['64', '79']</t>
-  </si>
-  <si>
-    <t>['18', '59']</t>
-  </si>
-  <si>
     <t>['6', '29', '31', '68', '90+3']</t>
   </si>
   <si>
@@ -922,43 +922,67 @@
     <t>['64']</t>
   </si>
   <si>
+    <t>['10', '35']</t>
+  </si>
+  <si>
     <t>['28', '37', '79']</t>
   </si>
   <si>
-    <t>['10', '35']</t>
-  </si>
-  <si>
     <t>['39']</t>
   </si>
   <si>
     <t>['26']</t>
   </si>
   <si>
+    <t>['40', '21', '45+1']</t>
+  </si>
+  <si>
     <t>['59', '68']</t>
   </si>
   <si>
-    <t>['40', '21', '45+1']</t>
-  </si>
-  <si>
     <t>['11']</t>
   </si>
   <si>
     <t>['32', '49', '81']</t>
   </si>
   <si>
+    <t>['38', '83', '78']</t>
+  </si>
+  <si>
     <t>['81', '85', '88', '90+9']</t>
   </si>
   <si>
+    <t>['3', '53', '83', '76', '89']</t>
+  </si>
+  <si>
+    <t>['30', '5']</t>
+  </si>
+  <si>
+    <t>['89']</t>
+  </si>
+  <si>
+    <t>['3', '11', '58']</t>
+  </si>
+  <si>
+    <t>['88']</t>
+  </si>
+  <si>
     <t>['56', '85', '18']</t>
   </si>
   <si>
+    <t>['43', '51']</t>
+  </si>
+  <si>
     <t>['37']</t>
   </si>
   <si>
-    <t>['88']</t>
-  </si>
-  <si>
-    <t>['43', '51']</t>
+    <t>['33', '87']</t>
+  </si>
+  <si>
+    <t>['81']</t>
+  </si>
+  <si>
+    <t>['38']</t>
   </si>
   <si>
     <t>['24', '46', '54']</t>
@@ -967,27 +991,18 @@
     <t>['46']</t>
   </si>
   <si>
-    <t>['81']</t>
-  </si>
-  <si>
-    <t>['33', '87']</t>
-  </si>
-  <si>
-    <t>['38']</t>
-  </si>
-  <si>
     <t>['45+2']</t>
   </si>
   <si>
     <t>['81', '17', '26']</t>
   </si>
   <si>
+    <t>['45+3']</t>
+  </si>
+  <si>
     <t>['45+3', '25', '89', '90+3']</t>
   </si>
   <si>
-    <t>['45+3']</t>
-  </si>
-  <si>
     <t>['40', '45']</t>
   </si>
   <si>
@@ -998,6 +1013,18 @@
   </si>
   <si>
     <t>['4', '63']</t>
+  </si>
+  <si>
+    <t>['36', '25', '90+6']</t>
+  </si>
+  <si>
+    <t>['84']</t>
+  </si>
+  <si>
+    <t>['63']</t>
+  </si>
+  <si>
+    <t>['51']</t>
   </si>
 </sst>
 </file>
@@ -1590,7 +1617,7 @@
         <v>285</v>
       </c>
       <c r="AK2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="AL2" s="3">
         <v>45850.125</v>
@@ -1720,7 +1747,7 @@
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
         <v>96</v>
@@ -1732,13 +1759,13 @@
         <v>195</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1747,82 +1774,82 @@
         <v>282</v>
       </c>
       <c r="L4">
-        <v>6.07</v>
+        <v>2.61</v>
       </c>
       <c r="M4">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="N4">
+        <v>2.55</v>
+      </c>
+      <c r="O4">
+        <v>2.13</v>
+      </c>
+      <c r="P4">
+        <v>7.4</v>
+      </c>
+      <c r="Q4">
+        <v>1.95</v>
+      </c>
+      <c r="R4">
         <v>1.44</v>
       </c>
-      <c r="O4">
-        <v>2.71</v>
-      </c>
-      <c r="P4">
-        <v>28</v>
-      </c>
-      <c r="Q4">
-        <v>1.41</v>
-      </c>
-      <c r="R4">
-        <v>1.17</v>
-      </c>
       <c r="S4">
-        <v>4.05</v>
+        <v>2.57</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>3.04</v>
       </c>
       <c r="U4">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="V4">
-        <v>4.25</v>
+        <v>7.9</v>
       </c>
       <c r="W4">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="Z4">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AA4">
-        <v>6.05</v>
+        <v>3</v>
       </c>
       <c r="AB4">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="AC4">
-        <v>2.74</v>
+        <v>1.76</v>
       </c>
       <c r="AD4">
-        <v>2.01</v>
+        <v>4</v>
       </c>
       <c r="AE4">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AF4">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AH4">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="AI4">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AJ4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AK4" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="AL4" s="3">
         <v>45850.25</v>
@@ -1935,10 +1962,10 @@
         <v>1.11</v>
       </c>
       <c r="AJ5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AK5" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AL5" s="3">
         <v>45850.25</v>
@@ -2051,7 +2078,7 @@
         <v>1.06</v>
       </c>
       <c r="AJ6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AK6" t="s">
         <v>286</v>
@@ -2068,7 +2095,7 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
         <v>96</v>
@@ -2080,13 +2107,13 @@
         <v>198</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -2095,82 +2122,82 @@
         <v>282</v>
       </c>
       <c r="L7">
-        <v>2.61</v>
+        <v>6.07</v>
       </c>
       <c r="M7">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="N7">
-        <v>2.55</v>
+        <v>1.44</v>
       </c>
       <c r="O7">
-        <v>2.13</v>
+        <v>2.71</v>
       </c>
       <c r="P7">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="Q7">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="R7">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="S7">
-        <v>2.57</v>
+        <v>4.05</v>
       </c>
       <c r="T7">
-        <v>3.04</v>
+        <v>2</v>
       </c>
       <c r="U7">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="V7">
-        <v>7.9</v>
+        <v>4.25</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>18.5</v>
       </c>
       <c r="Z7">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AA7">
-        <v>3</v>
+        <v>6.05</v>
       </c>
       <c r="AB7">
-        <v>1.94</v>
+        <v>1.38</v>
       </c>
       <c r="AC7">
+        <v>2.74</v>
+      </c>
+      <c r="AD7">
+        <v>2.01</v>
+      </c>
+      <c r="AE7">
         <v>1.76</v>
       </c>
-      <c r="AD7">
-        <v>4</v>
-      </c>
-      <c r="AE7">
-        <v>1.2</v>
-      </c>
       <c r="AF7">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AG7">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AH7">
-        <v>8</v>
+        <v>3.25</v>
       </c>
       <c r="AI7">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AJ7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AK7" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AL7" s="3">
         <v>45850.25</v>
@@ -2416,7 +2443,7 @@
         <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
         <v>96</v>
@@ -2428,13 +2455,13 @@
         <v>201</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2443,79 +2470,79 @@
         <v>282</v>
       </c>
       <c r="L10">
-        <v>1.68</v>
+        <v>3.16</v>
       </c>
       <c r="M10">
-        <v>3.68</v>
+        <v>2.82</v>
       </c>
       <c r="N10">
-        <v>3.96</v>
+        <v>2.23</v>
       </c>
       <c r="O10">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="P10">
-        <v>15</v>
+        <v>5.75</v>
       </c>
       <c r="Q10">
-        <v>2.58</v>
+        <v>1.95</v>
       </c>
       <c r="R10">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="S10">
-        <v>3.26</v>
+        <v>2.23</v>
       </c>
       <c r="T10">
-        <v>2.46</v>
+        <v>3.74</v>
       </c>
       <c r="U10">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="V10">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
+        <v>1.08</v>
+      </c>
+      <c r="Y10">
+        <v>6.5</v>
+      </c>
+      <c r="Z10">
+        <v>1.55</v>
+      </c>
+      <c r="AA10">
+        <v>2.2</v>
+      </c>
+      <c r="AB10">
+        <v>2.62</v>
+      </c>
+      <c r="AC10">
+        <v>1.42</v>
+      </c>
+      <c r="AD10">
+        <v>5.5</v>
+      </c>
+      <c r="AE10">
+        <v>1.11</v>
+      </c>
+      <c r="AF10">
+        <v>2.25</v>
+      </c>
+      <c r="AG10">
+        <v>1.57</v>
+      </c>
+      <c r="AH10">
+        <v>11</v>
+      </c>
+      <c r="AI10">
         <v>1.01</v>
       </c>
-      <c r="Y10">
-        <v>11</v>
-      </c>
-      <c r="Z10">
-        <v>1.16</v>
-      </c>
-      <c r="AA10">
-        <v>4.1</v>
-      </c>
-      <c r="AB10">
-        <v>1.67</v>
-      </c>
-      <c r="AC10">
-        <v>2</v>
-      </c>
-      <c r="AD10">
-        <v>2.62</v>
-      </c>
-      <c r="AE10">
-        <v>1.38</v>
-      </c>
-      <c r="AF10">
-        <v>1.63</v>
-      </c>
-      <c r="AG10">
-        <v>2.09</v>
-      </c>
-      <c r="AH10">
-        <v>4.9</v>
-      </c>
-      <c r="AI10">
-        <v>1.11</v>
-      </c>
       <c r="AJ10" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AK10" t="s">
         <v>286</v>
@@ -2547,7 +2574,7 @@
         <v>2</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2559,82 +2586,82 @@
         <v>282</v>
       </c>
       <c r="L11">
-        <v>2.64</v>
+        <v>1.45</v>
       </c>
       <c r="M11">
-        <v>3.06</v>
+        <v>4.2</v>
       </c>
       <c r="N11">
-        <v>2.42</v>
+        <v>5.2</v>
       </c>
       <c r="O11">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="P11">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q11">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="R11">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="S11">
-        <v>2.76</v>
+        <v>3.4</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="U11">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="V11">
-        <v>7.9</v>
+        <v>6</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z11">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AA11">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="AB11">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AC11">
-        <v>1.61</v>
+        <v>2.22</v>
       </c>
       <c r="AD11">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="AE11">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH11">
-        <v>8</v>
+        <v>4.75</v>
       </c>
       <c r="AI11">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AJ11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AK11" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AL11" s="3">
         <v>45850.29166666666</v>
@@ -2648,7 +2675,7 @@
         <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
         <v>96</v>
@@ -2660,10 +2687,10 @@
         <v>203</v>
       </c>
       <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>1</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2675,82 +2702,82 @@
         <v>282</v>
       </c>
       <c r="L12">
-        <v>1.34</v>
+        <v>2.86</v>
       </c>
       <c r="M12">
-        <v>4.33</v>
+        <v>3.23</v>
       </c>
       <c r="N12">
-        <v>7.1</v>
+        <v>2.17</v>
       </c>
       <c r="O12">
-        <v>1.33</v>
+        <v>2.03</v>
       </c>
       <c r="P12">
-        <v>15.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q12">
-        <v>3.32</v>
+        <v>1.97</v>
       </c>
       <c r="R12">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S12">
-        <v>3.28</v>
+        <v>3.11</v>
       </c>
       <c r="T12">
-        <v>2.29</v>
+        <v>2.78</v>
       </c>
       <c r="U12">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="V12">
-        <v>4.95</v>
+        <v>6.5</v>
       </c>
       <c r="W12">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AA12">
-        <v>4.45</v>
+        <v>3.6</v>
       </c>
       <c r="AB12">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AC12">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AD12">
-        <v>2.26</v>
+        <v>3.2</v>
       </c>
       <c r="AE12">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="AF12">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AH12">
-        <v>3.85</v>
+        <v>6.5</v>
       </c>
       <c r="AI12">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AJ12" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="AK12" t="s">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="AL12" s="3">
         <v>45850.29166666666</v>
@@ -2764,7 +2791,7 @@
         <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
         <v>96</v>
@@ -2776,7 +2803,7 @@
         <v>204</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2791,79 +2818,79 @@
         <v>282</v>
       </c>
       <c r="L13">
-        <v>1.82</v>
+        <v>1.34</v>
       </c>
       <c r="M13">
-        <v>3.33</v>
+        <v>4.33</v>
       </c>
       <c r="N13">
-        <v>3.69</v>
+        <v>7.1</v>
       </c>
       <c r="O13">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="P13">
-        <v>8.5</v>
+        <v>15.75</v>
       </c>
       <c r="Q13">
-        <v>2.6</v>
+        <v>3.32</v>
       </c>
       <c r="R13">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="S13">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="T13">
-        <v>3.18</v>
+        <v>2.29</v>
       </c>
       <c r="U13">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="V13">
-        <v>7.2</v>
+        <v>4.95</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z13">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AA13">
-        <v>3</v>
+        <v>4.45</v>
       </c>
       <c r="AB13">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AC13">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AD13">
-        <v>4</v>
+        <v>2.26</v>
       </c>
       <c r="AE13">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="AF13">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG13">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AH13">
-        <v>8</v>
+        <v>3.85</v>
       </c>
       <c r="AI13">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AJ13" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="AK13" t="s">
         <v>286</v>
@@ -2892,7 +2919,7 @@
         <v>205</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -2901,88 +2928,88 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="s">
         <v>282</v>
       </c>
       <c r="L14">
-        <v>3.15</v>
+        <v>2.13</v>
       </c>
       <c r="M14">
-        <v>3.14</v>
+        <v>2.89</v>
       </c>
       <c r="N14">
-        <v>2.06</v>
+        <v>3.29</v>
       </c>
       <c r="O14">
+        <v>1.88</v>
+      </c>
+      <c r="P14">
+        <v>6.5</v>
+      </c>
+      <c r="Q14">
+        <v>2.4</v>
+      </c>
+      <c r="R14">
+        <v>1.59</v>
+      </c>
+      <c r="S14">
+        <v>2.33</v>
+      </c>
+      <c r="T14">
+        <v>3.74</v>
+      </c>
+      <c r="U14">
+        <v>1.21</v>
+      </c>
+      <c r="V14">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="W14">
+        <v>1.02</v>
+      </c>
+      <c r="X14">
+        <v>1.07</v>
+      </c>
+      <c r="Y14">
+        <v>7</v>
+      </c>
+      <c r="Z14">
+        <v>1.53</v>
+      </c>
+      <c r="AA14">
         <v>2.25</v>
       </c>
-      <c r="P14">
-        <v>9</v>
-      </c>
-      <c r="Q14">
-        <v>1.83</v>
-      </c>
-      <c r="R14">
-        <v>1.39</v>
-      </c>
-      <c r="S14">
-        <v>2.95</v>
-      </c>
-      <c r="T14">
-        <v>2.96</v>
-      </c>
-      <c r="U14">
-        <v>1.39</v>
-      </c>
-      <c r="V14">
-        <v>7.1</v>
-      </c>
-      <c r="W14">
-        <v>1.06</v>
-      </c>
-      <c r="X14">
-        <v>1.03</v>
-      </c>
-      <c r="Y14">
-        <v>9</v>
-      </c>
-      <c r="Z14">
-        <v>1.29</v>
-      </c>
-      <c r="AA14">
-        <v>3.3</v>
-      </c>
       <c r="AB14">
-        <v>1.92</v>
+        <v>2.48</v>
       </c>
       <c r="AC14">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AD14">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AE14">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AH14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AI14">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AJ14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AK14" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="AL14" s="3">
         <v>45850.29166666666</v>
@@ -2996,7 +3023,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
         <v>96</v>
@@ -3095,7 +3122,7 @@
         <v>1.06</v>
       </c>
       <c r="AJ15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AK15" t="s">
         <v>286</v>
@@ -3112,7 +3139,7 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
         <v>96</v>
@@ -3124,97 +3151,97 @@
         <v>207</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="s">
         <v>282</v>
       </c>
       <c r="L16">
-        <v>3.16</v>
+        <v>2.64</v>
       </c>
       <c r="M16">
-        <v>2.82</v>
+        <v>3.06</v>
       </c>
       <c r="N16">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="O16">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="P16">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="R16">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="S16">
-        <v>2.23</v>
+        <v>2.76</v>
       </c>
       <c r="T16">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="U16">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="V16">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
       <c r="W16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Z16">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AA16">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AB16">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="AC16">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AD16">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AE16">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF16">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AG16">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AH16">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AI16">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AJ16" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="AK16" t="s">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="AL16" s="3">
         <v>45850.29166666666</v>
@@ -3228,7 +3255,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
         <v>96</v>
@@ -3243,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -3255,82 +3282,82 @@
         <v>282</v>
       </c>
       <c r="L17">
-        <v>2.86</v>
+        <v>1.82</v>
       </c>
       <c r="M17">
-        <v>3.23</v>
+        <v>3.33</v>
       </c>
       <c r="N17">
-        <v>2.17</v>
+        <v>3.69</v>
       </c>
       <c r="O17">
-        <v>2.03</v>
+        <v>1.67</v>
       </c>
       <c r="P17">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Q17">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="R17">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S17">
-        <v>3.11</v>
+        <v>2.78</v>
       </c>
       <c r="T17">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="U17">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="V17">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z17">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AA17">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AB17">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AC17">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AD17">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AE17">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AH17">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AI17">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AJ17" t="s">
         <v>286</v>
       </c>
       <c r="AK17" t="s">
-        <v>317</v>
+        <v>286</v>
       </c>
       <c r="AL17" s="3">
         <v>45850.29166666666</v>
@@ -3344,7 +3371,7 @@
         <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
         <v>96</v>
@@ -3356,79 +3383,79 @@
         <v>209</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="s">
         <v>282</v>
       </c>
       <c r="L18">
-        <v>1.45</v>
+        <v>3.15</v>
       </c>
       <c r="M18">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="N18">
-        <v>5.2</v>
+        <v>2.06</v>
       </c>
       <c r="O18">
-        <v>1.36</v>
+        <v>2.25</v>
       </c>
       <c r="P18">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="R18">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="S18">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="T18">
-        <v>2.38</v>
+        <v>2.96</v>
       </c>
       <c r="U18">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
         <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z18">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AA18">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AB18">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AC18">
-        <v>2.22</v>
+        <v>1.78</v>
       </c>
       <c r="AD18">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="AE18">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
         <v>1.73</v>
@@ -3437,16 +3464,16 @@
         <v>2</v>
       </c>
       <c r="AH18">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="AI18">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AJ18" t="s">
         <v>297</v>
       </c>
       <c r="AK18" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="AL18" s="3">
         <v>45850.29166666666</v>
@@ -3460,7 +3487,7 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
         <v>96</v>
@@ -3472,97 +3499,97 @@
         <v>210</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="s">
         <v>282</v>
       </c>
       <c r="L19">
-        <v>2.13</v>
+        <v>1.68</v>
       </c>
       <c r="M19">
-        <v>2.89</v>
+        <v>3.68</v>
       </c>
       <c r="N19">
-        <v>3.29</v>
+        <v>3.96</v>
       </c>
       <c r="O19">
-        <v>1.88</v>
+        <v>1.51</v>
       </c>
       <c r="P19">
-        <v>6.5</v>
+        <v>15</v>
       </c>
       <c r="Q19">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="R19">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="S19">
-        <v>2.33</v>
+        <v>3.26</v>
       </c>
       <c r="T19">
-        <v>3.74</v>
+        <v>2.46</v>
       </c>
       <c r="U19">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="V19">
-        <v>9.699999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="W19">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Z19">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="AA19">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="AB19">
-        <v>2.48</v>
+        <v>1.67</v>
       </c>
       <c r="AC19">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AD19">
-        <v>5.5</v>
+        <v>2.62</v>
       </c>
       <c r="AE19">
+        <v>1.38</v>
+      </c>
+      <c r="AF19">
+        <v>1.63</v>
+      </c>
+      <c r="AG19">
+        <v>2.09</v>
+      </c>
+      <c r="AH19">
+        <v>4.9</v>
+      </c>
+      <c r="AI19">
         <v>1.11</v>
-      </c>
-      <c r="AF19">
-        <v>2.2</v>
-      </c>
-      <c r="AG19">
-        <v>1.62</v>
-      </c>
-      <c r="AH19">
-        <v>11</v>
-      </c>
-      <c r="AI19">
-        <v>1.01</v>
       </c>
       <c r="AJ19" t="s">
         <v>298</v>
       </c>
       <c r="AK19" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="AL19" s="3">
         <v>45850.29166666666</v>
@@ -3678,7 +3705,7 @@
         <v>299</v>
       </c>
       <c r="AK20" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AL20" s="3">
         <v>45850.3125</v>
@@ -3692,7 +3719,7 @@
         <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
         <v>96</v>
@@ -3808,7 +3835,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
         <v>96</v>
@@ -3910,7 +3937,7 @@
         <v>301</v>
       </c>
       <c r="AK22" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AL22" s="3">
         <v>45850.33333333334</v>
@@ -3924,7 +3951,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
         <v>96</v>
@@ -3936,97 +3963,97 @@
         <v>214</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" t="s">
         <v>282</v>
       </c>
       <c r="L23">
-        <v>7</v>
+        <v>3.55</v>
       </c>
       <c r="M23">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N23">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="P23">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="Q23">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="R23">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S23">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T23">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U23">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y23">
-        <v>8.949999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="Z23">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AA23">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="AB23">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC23">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AD23">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AE23">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AF23">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AG23">
-        <v>1.62</v>
+        <v>2.14</v>
       </c>
       <c r="AH23">
-        <v>6.7</v>
+        <v>4.6</v>
       </c>
       <c r="AI23">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AJ23" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="AK23" t="s">
-        <v>322</v>
+        <v>286</v>
       </c>
       <c r="AL23" s="3">
         <v>45850.35416666666</v>
@@ -4040,7 +4067,7 @@
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
         <v>96</v>
@@ -4052,97 +4079,97 @@
         <v>215</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="s">
         <v>282</v>
       </c>
       <c r="L24">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="M24">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N24">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="O24">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="P24">
-        <v>15.5</v>
+        <v>6.95</v>
       </c>
       <c r="Q24">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="R24">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S24">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="T24">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="U24">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V24">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y24">
-        <v>9.9</v>
+        <v>8</v>
       </c>
       <c r="Z24">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AA24">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB24">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AC24">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AD24">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AE24">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AF24">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AG24">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AH24">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AI24">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AJ24" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="AK24" t="s">
-        <v>286</v>
+        <v>327</v>
       </c>
       <c r="AL24" s="3">
         <v>45850.35416666666</v>
@@ -4156,7 +4183,7 @@
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
         <v>96</v>
@@ -4168,97 +4195,97 @@
         <v>216</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I25">
         <v>2</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" t="s">
         <v>282</v>
       </c>
       <c r="L25">
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="M25">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="N25">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="O25">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>6.95</v>
+        <v>11.5</v>
       </c>
       <c r="Q25">
-        <v>2.04</v>
+        <v>1.4</v>
       </c>
       <c r="R25">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S25">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="T25">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U25">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V25">
         <v>7</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Z25">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AA25">
-        <v>2.62</v>
+        <v>3.22</v>
       </c>
       <c r="AB25">
+        <v>1.95</v>
+      </c>
+      <c r="AC25">
+        <v>1.77</v>
+      </c>
+      <c r="AD25">
+        <v>3.34</v>
+      </c>
+      <c r="AE25">
+        <v>1.24</v>
+      </c>
+      <c r="AF25">
         <v>2.2</v>
       </c>
-      <c r="AC25">
-        <v>1.65</v>
-      </c>
-      <c r="AD25">
-        <v>4.2</v>
-      </c>
-      <c r="AE25">
-        <v>1.2</v>
-      </c>
-      <c r="AF25">
-        <v>1.95</v>
-      </c>
       <c r="AG25">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH25">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="AI25">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AJ25" t="s">
         <v>303</v>
       </c>
       <c r="AK25" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AL25" s="3">
         <v>45850.35416666666</v>
@@ -4490,7 +4517,7 @@
         <v>305</v>
       </c>
       <c r="AK27" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AL27" s="3">
         <v>45850.41666666666</v>
@@ -4516,7 +4543,7 @@
         <v>219</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -4528,82 +4555,82 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L28">
-        <v>1.26</v>
+        <v>3.44</v>
       </c>
       <c r="M28">
-        <v>5.1</v>
+        <v>3.13</v>
       </c>
       <c r="N28">
-        <v>7.8</v>
+        <v>2.25</v>
       </c>
       <c r="O28">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC28">
-        <v>3.33</v>
+        <v>1.53</v>
       </c>
       <c r="AD28">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH28">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI28">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AK28" t="s">
         <v>286</v>
@@ -4632,97 +4659,97 @@
         <v>220</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L29">
-        <v>3.44</v>
+        <v>1.2</v>
       </c>
       <c r="M29">
-        <v>3.13</v>
+        <v>5.4</v>
       </c>
       <c r="N29">
-        <v>2.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB29">
-        <v>2.4</v>
+        <v>1.52</v>
       </c>
       <c r="AC29">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ29" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="AK29" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="AL29" s="3">
         <v>45850.45833333334</v>
@@ -4748,7 +4775,7 @@
         <v>221</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -4760,82 +4787,82 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ30" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="AK30" t="s">
         <v>286</v>
@@ -4852,7 +4879,7 @@
         <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D31" t="s">
         <v>96</v>
@@ -4864,97 +4891,97 @@
         <v>222</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L31">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="AK31" t="s">
-        <v>325</v>
+        <v>286</v>
       </c>
       <c r="AL31" s="3">
         <v>45850.45833333334</v>
@@ -4968,7 +4995,7 @@
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D32" t="s">
         <v>96</v>
@@ -5186,7 +5213,7 @@
         <v>308</v>
       </c>
       <c r="AK33" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AL33" s="3">
         <v>45850.5</v>
@@ -5302,7 +5329,7 @@
         <v>309</v>
       </c>
       <c r="AK34" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AL34" s="3">
         <v>45850.52083333334</v>
@@ -5325,7 +5352,7 @@
         <v>130</v>
       </c>
       <c r="F35" t="s">
-        <v>226</v>
+        <v>152</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -5340,79 +5367,79 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L35">
-        <v>2.69</v>
+        <v>2.35</v>
       </c>
       <c r="M35">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="N35">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="O35">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="P35">
-        <v>7.9</v>
+        <v>5.25</v>
       </c>
       <c r="Q35">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="R35">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="S35">
-        <v>2.52</v>
+        <v>2</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="U35">
+        <v>1.18</v>
+      </c>
+      <c r="V35">
+        <v>14.5</v>
+      </c>
+      <c r="W35">
+        <v>1</v>
+      </c>
+      <c r="X35">
+        <v>1.15</v>
+      </c>
+      <c r="Y35">
+        <v>4.75</v>
+      </c>
+      <c r="Z35">
+        <v>1.75</v>
+      </c>
+      <c r="AA35">
+        <v>2</v>
+      </c>
+      <c r="AB35">
+        <v>3.5</v>
+      </c>
+      <c r="AC35">
         <v>1.3</v>
       </c>
-      <c r="V35">
-        <v>10</v>
-      </c>
-      <c r="W35">
-        <v>1.06</v>
-      </c>
-      <c r="X35">
-        <v>1.03</v>
-      </c>
-      <c r="Y35">
-        <v>7.5</v>
-      </c>
-      <c r="Z35">
-        <v>1.36</v>
-      </c>
-      <c r="AA35">
-        <v>2.7</v>
-      </c>
-      <c r="AB35">
-        <v>2.2</v>
-      </c>
-      <c r="AC35">
-        <v>1.59</v>
-      </c>
       <c r="AD35">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AE35">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AG35">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AH35">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="AI35">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AJ35" t="s">
         <v>286</v>
@@ -5441,97 +5468,97 @@
         <v>131</v>
       </c>
       <c r="F36" t="s">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L36">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="M36">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="N36">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="O36">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="P36">
-        <v>5.25</v>
+        <v>7.9</v>
       </c>
       <c r="Q36">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="R36">
-        <v>1.76</v>
+        <v>1.46</v>
       </c>
       <c r="S36">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="T36">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="V36">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="W36">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>4.75</v>
+        <v>7.5</v>
       </c>
       <c r="Z36">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AA36">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AB36">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC36">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="AD36">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AF36">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AG36">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AH36">
-        <v>15.5</v>
+        <v>8</v>
       </c>
       <c r="AI36">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AJ36" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="AK36" t="s">
         <v>286</v>
@@ -5548,7 +5575,7 @@
         <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D37" t="s">
         <v>96</v>
@@ -5647,10 +5674,10 @@
         <v>1.1</v>
       </c>
       <c r="AJ37" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AK37" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="AL37" s="3">
         <v>45850.54166666666</v>
@@ -5664,7 +5691,7 @@
         <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D38" t="s">
         <v>96</v>
@@ -5676,19 +5703,19 @@
         <v>228</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L38">
         <v>2.05</v>
@@ -5763,10 +5790,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ38" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="AK38" t="s">
-        <v>286</v>
+        <v>333</v>
       </c>
       <c r="AL38" s="3">
         <v>45850.54166666666</v>
@@ -5780,7 +5807,7 @@
         <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D39" t="s">
         <v>96</v>
@@ -5804,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L39">
         <v>2.8</v>
@@ -5896,7 +5923,7 @@
         <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D40" t="s">
         <v>96</v>
@@ -5920,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L40">
         <v>2.25</v>
@@ -6012,7 +6039,7 @@
         <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D41" t="s">
         <v>96</v>
@@ -6024,19 +6051,19 @@
         <v>231</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41">
         <v>0</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L41">
         <v>3.35</v>
@@ -6111,7 +6138,7 @@
         <v>1</v>
       </c>
       <c r="AJ41" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="AK41" t="s">
         <v>286</v>
@@ -6128,7 +6155,7 @@
         <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D42" t="s">
         <v>96</v>
@@ -6140,10 +6167,10 @@
         <v>232</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -6152,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L42">
         <v>1.75</v>
@@ -6227,10 +6254,10 @@
         <v>1.02</v>
       </c>
       <c r="AJ42" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="AK42" t="s">
-        <v>286</v>
+        <v>334</v>
       </c>
       <c r="AL42" s="3">
         <v>45850.63541666666</v>
@@ -6244,7 +6271,7 @@
         <v>56</v>
       </c>
       <c r="C43" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D43" t="s">
         <v>96</v>
@@ -6253,13 +6280,13 @@
         <v>138</v>
       </c>
       <c r="F43" t="s">
-        <v>233</v>
+        <v>153</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -6268,85 +6295,85 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L43">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="M43">
-        <v>3.56</v>
+        <v>3.15</v>
       </c>
       <c r="N43">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="O43">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="R43">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="S43">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="T43">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="U43">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="V43">
-        <v>5.75</v>
+        <v>10</v>
       </c>
       <c r="W43">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X43">
         <v>1.05</v>
       </c>
       <c r="Y43">
+        <v>5.75</v>
+      </c>
+      <c r="Z43">
+        <v>1.55</v>
+      </c>
+      <c r="AA43">
+        <v>2.3</v>
+      </c>
+      <c r="AB43">
+        <v>2.62</v>
+      </c>
+      <c r="AC43">
+        <v>1.42</v>
+      </c>
+      <c r="AD43">
+        <v>5</v>
+      </c>
+      <c r="AE43">
+        <v>1.13</v>
+      </c>
+      <c r="AF43">
+        <v>2.45</v>
+      </c>
+      <c r="AG43">
+        <v>1.44</v>
+      </c>
+      <c r="AH43">
         <v>10</v>
       </c>
-      <c r="Z43">
-        <v>1.25</v>
-      </c>
-      <c r="AA43">
-        <v>3.58</v>
-      </c>
-      <c r="AB43">
-        <v>1.77</v>
-      </c>
-      <c r="AC43">
-        <v>1.93</v>
-      </c>
-      <c r="AD43">
-        <v>2.83</v>
-      </c>
-      <c r="AE43">
-        <v>1.36</v>
-      </c>
-      <c r="AF43">
-        <v>1.65</v>
-      </c>
-      <c r="AG43">
-        <v>2.1</v>
-      </c>
-      <c r="AH43">
-        <v>5.25</v>
-      </c>
       <c r="AI43">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AJ43" t="s">
         <v>286</v>
       </c>
       <c r="AK43" t="s">
-        <v>286</v>
+        <v>335</v>
       </c>
       <c r="AL43" s="3">
         <v>45850.64583333334</v>
@@ -6360,7 +6387,7 @@
         <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D44" t="s">
         <v>96</v>
@@ -6369,100 +6396,100 @@
         <v>139</v>
       </c>
       <c r="F44" t="s">
-        <v>154</v>
+        <v>233</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J44">
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L44">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="M44">
-        <v>3.15</v>
+        <v>3.56</v>
       </c>
       <c r="N44">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="O44">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q44">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="R44">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="S44">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="T44">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="U44">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="V44">
-        <v>10</v>
+        <v>5.75</v>
       </c>
       <c r="W44">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X44">
         <v>1.05</v>
       </c>
       <c r="Y44">
-        <v>5.75</v>
+        <v>10</v>
       </c>
       <c r="Z44">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AA44">
-        <v>2.3</v>
+        <v>3.58</v>
       </c>
       <c r="AB44">
-        <v>2.62</v>
+        <v>1.77</v>
       </c>
       <c r="AC44">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="AD44">
-        <v>5</v>
+        <v>2.83</v>
       </c>
       <c r="AE44">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AF44">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="AG44">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AH44">
-        <v>10</v>
+        <v>5.25</v>
       </c>
       <c r="AI44">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AJ44" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="AK44" t="s">
-        <v>286</v>
+        <v>336</v>
       </c>
       <c r="AL44" s="3">
         <v>45850.64583333334</v>
@@ -6476,7 +6503,7 @@
         <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D45" t="s">
         <v>96</v>
@@ -6488,7 +6515,7 @@
         <v>234</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -6500,7 +6527,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L45">
         <v>1.73</v>
@@ -6575,7 +6602,7 @@
         <v>1.02</v>
       </c>
       <c r="AJ45" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="AK45" t="s">
         <v>286</v>
@@ -6735,76 +6762,76 @@
         <v>284</v>
       </c>
       <c r="L47">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="M47">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N47">
-        <v>2.95</v>
+        <v>3.79</v>
       </c>
       <c r="O47">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="P47">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="Q47">
+        <v>2.88</v>
+      </c>
+      <c r="R47">
+        <v>1.57</v>
+      </c>
+      <c r="S47">
+        <v>2.25</v>
+      </c>
+      <c r="T47">
+        <v>4.1</v>
+      </c>
+      <c r="U47">
+        <v>1.21</v>
+      </c>
+      <c r="V47">
+        <v>7.5</v>
+      </c>
+      <c r="W47">
+        <v>1.03</v>
+      </c>
+      <c r="X47">
+        <v>1.09</v>
+      </c>
+      <c r="Y47">
+        <v>6.2</v>
+      </c>
+      <c r="Z47">
+        <v>1.57</v>
+      </c>
+      <c r="AA47">
+        <v>2.24</v>
+      </c>
+      <c r="AB47">
+        <v>2.8</v>
+      </c>
+      <c r="AC47">
+        <v>1.42</v>
+      </c>
+      <c r="AD47">
+        <v>5.25</v>
+      </c>
+      <c r="AE47">
+        <v>1.12</v>
+      </c>
+      <c r="AF47">
         <v>2.2</v>
       </c>
-      <c r="R47">
-        <v>1.44</v>
-      </c>
-      <c r="S47">
-        <v>2.6</v>
-      </c>
-      <c r="T47">
-        <v>3</v>
-      </c>
-      <c r="U47">
-        <v>1.33</v>
-      </c>
-      <c r="V47">
-        <v>8.25</v>
-      </c>
-      <c r="W47">
-        <v>1.06</v>
-      </c>
-      <c r="X47">
-        <v>1.07</v>
-      </c>
-      <c r="Y47">
-        <v>8</v>
-      </c>
-      <c r="Z47">
-        <v>1.36</v>
-      </c>
-      <c r="AA47">
-        <v>2.87</v>
-      </c>
-      <c r="AB47">
-        <v>2.05</v>
-      </c>
-      <c r="AC47">
-        <v>1.65</v>
-      </c>
-      <c r="AD47">
-        <v>3.7</v>
-      </c>
-      <c r="AE47">
-        <v>1.24</v>
-      </c>
-      <c r="AF47">
-        <v>1.87</v>
-      </c>
       <c r="AG47">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AH47">
-        <v>7.5</v>
+        <v>13</v>
       </c>
       <c r="AI47">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AJ47" t="s">
         <v>286</v>
@@ -6851,76 +6878,76 @@
         <v>284</v>
       </c>
       <c r="L48">
+        <v>2.3</v>
+      </c>
+      <c r="M48">
+        <v>3.3</v>
+      </c>
+      <c r="N48">
+        <v>2.95</v>
+      </c>
+      <c r="O48">
+        <v>1.87</v>
+      </c>
+      <c r="P48">
+        <v>8</v>
+      </c>
+      <c r="Q48">
+        <v>2.2</v>
+      </c>
+      <c r="R48">
+        <v>1.44</v>
+      </c>
+      <c r="S48">
+        <v>2.6</v>
+      </c>
+      <c r="T48">
+        <v>3</v>
+      </c>
+      <c r="U48">
+        <v>1.33</v>
+      </c>
+      <c r="V48">
+        <v>8.25</v>
+      </c>
+      <c r="W48">
+        <v>1.06</v>
+      </c>
+      <c r="X48">
+        <v>1.07</v>
+      </c>
+      <c r="Y48">
+        <v>8</v>
+      </c>
+      <c r="Z48">
+        <v>1.36</v>
+      </c>
+      <c r="AA48">
+        <v>2.87</v>
+      </c>
+      <c r="AB48">
+        <v>2.05</v>
+      </c>
+      <c r="AC48">
+        <v>1.65</v>
+      </c>
+      <c r="AD48">
+        <v>3.7</v>
+      </c>
+      <c r="AE48">
+        <v>1.24</v>
+      </c>
+      <c r="AF48">
+        <v>1.87</v>
+      </c>
+      <c r="AG48">
         <v>1.8</v>
       </c>
-      <c r="M48">
-        <v>3.5</v>
-      </c>
-      <c r="N48">
-        <v>5</v>
-      </c>
-      <c r="O48">
-        <v>1.53</v>
-      </c>
-      <c r="P48">
-        <v>5.75</v>
-      </c>
-      <c r="Q48">
-        <v>3.4</v>
-      </c>
-      <c r="R48">
-        <v>1.57</v>
-      </c>
-      <c r="S48">
-        <v>2.25</v>
-      </c>
-      <c r="T48">
-        <v>3.75</v>
-      </c>
-      <c r="U48">
-        <v>1.25</v>
-      </c>
-      <c r="V48">
-        <v>13</v>
-      </c>
-      <c r="W48">
-        <v>1.04</v>
-      </c>
-      <c r="X48">
-        <v>1.11</v>
-      </c>
-      <c r="Y48">
-        <v>6.25</v>
-      </c>
-      <c r="Z48">
-        <v>1.55</v>
-      </c>
-      <c r="AA48">
-        <v>2.3</v>
-      </c>
-      <c r="AB48">
-        <v>2.7</v>
-      </c>
-      <c r="AC48">
-        <v>1.44</v>
-      </c>
-      <c r="AD48">
-        <v>5.5</v>
-      </c>
-      <c r="AE48">
-        <v>1.14</v>
-      </c>
-      <c r="AF48">
-        <v>2.5</v>
-      </c>
-      <c r="AG48">
-        <v>1.5</v>
-      </c>
       <c r="AH48">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="AI48">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AJ48" t="s">
         <v>286</v>
@@ -6967,76 +6994,76 @@
         <v>284</v>
       </c>
       <c r="L49">
-        <v>2.61</v>
+        <v>1.8</v>
       </c>
       <c r="M49">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N49">
+        <v>5</v>
+      </c>
+      <c r="O49">
+        <v>1.53</v>
+      </c>
+      <c r="P49">
+        <v>5.75</v>
+      </c>
+      <c r="Q49">
+        <v>3.4</v>
+      </c>
+      <c r="R49">
+        <v>1.57</v>
+      </c>
+      <c r="S49">
+        <v>2.25</v>
+      </c>
+      <c r="T49">
+        <v>3.75</v>
+      </c>
+      <c r="U49">
+        <v>1.25</v>
+      </c>
+      <c r="V49">
+        <v>13</v>
+      </c>
+      <c r="W49">
+        <v>1.04</v>
+      </c>
+      <c r="X49">
+        <v>1.11</v>
+      </c>
+      <c r="Y49">
+        <v>6.25</v>
+      </c>
+      <c r="Z49">
+        <v>1.55</v>
+      </c>
+      <c r="AA49">
+        <v>2.3</v>
+      </c>
+      <c r="AB49">
+        <v>2.7</v>
+      </c>
+      <c r="AC49">
+        <v>1.44</v>
+      </c>
+      <c r="AD49">
+        <v>5.5</v>
+      </c>
+      <c r="AE49">
+        <v>1.14</v>
+      </c>
+      <c r="AF49">
         <v>2.5</v>
       </c>
-      <c r="O49">
-        <v>1.67</v>
-      </c>
-      <c r="P49">
-        <v>6.75</v>
-      </c>
-      <c r="Q49">
-        <v>2.38</v>
-      </c>
-      <c r="R49">
-        <v>1.33</v>
-      </c>
-      <c r="S49">
-        <v>2.9</v>
-      </c>
-      <c r="T49">
-        <v>2.68</v>
-      </c>
-      <c r="U49">
-        <v>1.4</v>
-      </c>
-      <c r="V49">
-        <v>7</v>
-      </c>
-      <c r="W49">
-        <v>1.08</v>
-      </c>
-      <c r="X49">
-        <v>1.05</v>
-      </c>
-      <c r="Y49">
+      <c r="AG49">
+        <v>1.5</v>
+      </c>
+      <c r="AH49">
         <v>10</v>
       </c>
-      <c r="Z49">
-        <v>1.29</v>
-      </c>
-      <c r="AA49">
-        <v>3.3</v>
-      </c>
-      <c r="AB49">
-        <v>1.83</v>
-      </c>
-      <c r="AC49">
-        <v>1.8</v>
-      </c>
-      <c r="AD49">
-        <v>3</v>
-      </c>
-      <c r="AE49">
-        <v>1.3</v>
-      </c>
-      <c r="AF49">
-        <v>1.73</v>
-      </c>
-      <c r="AG49">
-        <v>2.15</v>
-      </c>
-      <c r="AH49">
-        <v>6.2</v>
-      </c>
       <c r="AI49">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AJ49" t="s">
         <v>286</v>
@@ -7056,7 +7083,7 @@
         <v>58</v>
       </c>
       <c r="C50" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D50" t="s">
         <v>96</v>
@@ -7083,76 +7110,76 @@
         <v>284</v>
       </c>
       <c r="L50">
-        <v>1.75</v>
+        <v>2.61</v>
       </c>
       <c r="M50">
-        <v>3.64</v>
+        <v>3.1</v>
       </c>
       <c r="N50">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="O50">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="P50">
-        <v>10</v>
+        <v>6.75</v>
       </c>
       <c r="Q50">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="R50">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S50">
         <v>2.9</v>
       </c>
       <c r="T50">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="U50">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V50">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="W50">
         <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y50">
         <v>10</v>
       </c>
       <c r="Z50">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AA50">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AB50">
+        <v>1.83</v>
+      </c>
+      <c r="AC50">
         <v>1.8</v>
       </c>
-      <c r="AC50">
-        <v>1.91</v>
-      </c>
       <c r="AD50">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AE50">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF50">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG50">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH50">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="AI50">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AJ50" t="s">
         <v>286</v>
@@ -7172,7 +7199,7 @@
         <v>58</v>
       </c>
       <c r="C51" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D51" t="s">
         <v>96</v>
@@ -7199,76 +7226,76 @@
         <v>284</v>
       </c>
       <c r="L51">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="M51">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="N51">
-        <v>3.79</v>
+        <v>3.7</v>
       </c>
       <c r="O51">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P51">
-        <v>5.75</v>
+        <v>10</v>
       </c>
       <c r="Q51">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="R51">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="S51">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="T51">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="U51">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="V51">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="W51">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="Z51">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AA51">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="AB51">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="AC51">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="AD51">
+        <v>2.9</v>
+      </c>
+      <c r="AE51">
+        <v>1.36</v>
+      </c>
+      <c r="AF51">
+        <v>1.7</v>
+      </c>
+      <c r="AG51">
+        <v>2.1</v>
+      </c>
+      <c r="AH51">
         <v>5.25</v>
       </c>
-      <c r="AE51">
+      <c r="AI51">
         <v>1.12</v>
-      </c>
-      <c r="AF51">
-        <v>2.2</v>
-      </c>
-      <c r="AG51">
-        <v>1.62</v>
-      </c>
-      <c r="AH51">
-        <v>13</v>
-      </c>
-      <c r="AI51">
-        <v>1.02</v>
       </c>
       <c r="AJ51" t="s">
         <v>286</v>
@@ -7288,7 +7315,7 @@
         <v>59</v>
       </c>
       <c r="C52" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D52" t="s">
         <v>96</v>
@@ -7404,7 +7431,7 @@
         <v>59</v>
       </c>
       <c r="C53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D53" t="s">
         <v>96</v>
@@ -7520,7 +7547,7 @@
         <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D54" t="s">
         <v>96</v>
@@ -7529,7 +7556,7 @@
         <v>149</v>
       </c>
       <c r="F54" t="s">
-        <v>131</v>
+        <v>243</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -7547,13 +7574,13 @@
         <v>283</v>
       </c>
       <c r="L54">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M54">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N54">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -7595,10 +7622,10 @@
         <v>0</v>
       </c>
       <c r="AB54">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC54">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD54">
         <v>0</v>
@@ -7636,7 +7663,7 @@
         <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D55" t="s">
         <v>96</v>
@@ -7645,7 +7672,7 @@
         <v>150</v>
       </c>
       <c r="F55" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -7660,79 +7687,79 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L55">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="M55">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="N55">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="O55">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P55">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q55">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R55">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S55">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T55">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="U55">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V55">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="W55">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X55">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y55">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z55">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AA55">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AB55">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AC55">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD55">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AE55">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF55">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG55">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH55">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AI55">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="s">
         <v>286</v>
@@ -7761,7 +7788,7 @@
         <v>151</v>
       </c>
       <c r="F56" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -7868,7 +7895,7 @@
         <v>60</v>
       </c>
       <c r="C57" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D57" t="s">
         <v>96</v>
@@ -7877,7 +7904,7 @@
         <v>152</v>
       </c>
       <c r="F57" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -7895,13 +7922,13 @@
         <v>283</v>
       </c>
       <c r="L57">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="M57">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N57">
-        <v>2.85</v>
+        <v>4.15</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -7937,10 +7964,10 @@
         <v>0</v>
       </c>
       <c r="Z57">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AA57">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB57">
         <v>0</v>
@@ -7984,7 +8011,7 @@
         <v>60</v>
       </c>
       <c r="C58" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D58" t="s">
         <v>96</v>
@@ -7993,7 +8020,7 @@
         <v>153</v>
       </c>
       <c r="F58" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -8008,16 +8035,16 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M58">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="O58">
         <v>0</v>
@@ -8053,10 +8080,10 @@
         <v>0</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB58">
         <v>0</v>
@@ -8100,7 +8127,7 @@
         <v>60</v>
       </c>
       <c r="C59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D59" t="s">
         <v>96</v>
@@ -8109,7 +8136,7 @@
         <v>154</v>
       </c>
       <c r="F59" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -8124,16 +8151,16 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L59">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M59">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N59">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -8169,10 +8196,10 @@
         <v>0</v>
       </c>
       <c r="Z59">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA59">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB59">
         <v>0</v>
@@ -8216,7 +8243,7 @@
         <v>60</v>
       </c>
       <c r="C60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D60" t="s">
         <v>96</v>
@@ -8225,7 +8252,7 @@
         <v>155</v>
       </c>
       <c r="F60" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -8243,13 +8270,13 @@
         <v>283</v>
       </c>
       <c r="L60">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="M60">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N60">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -8279,16 +8306,16 @@
         <v>0</v>
       </c>
       <c r="X60">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y60">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Z60">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AA60">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AB60">
         <v>0</v>
@@ -8332,7 +8359,7 @@
         <v>60</v>
       </c>
       <c r="C61" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D61" t="s">
         <v>96</v>
@@ -8341,7 +8368,7 @@
         <v>156</v>
       </c>
       <c r="F61" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -8356,79 +8383,79 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L61">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="M61">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N61">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Z61">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA61">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH61">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AI61">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ61" t="s">
         <v>286</v>
@@ -8448,7 +8475,7 @@
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D62" t="s">
         <v>96</v>
@@ -8457,7 +8484,7 @@
         <v>157</v>
       </c>
       <c r="F62" t="s">
-        <v>247</v>
+        <v>130</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -8475,13 +8502,13 @@
         <v>283</v>
       </c>
       <c r="L62">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="M62">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N62">
-        <v>4.15</v>
+        <v>6.75</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -8517,16 +8544,16 @@
         <v>0</v>
       </c>
       <c r="Z62">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA62">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD62">
         <v>0</v>
@@ -8564,7 +8591,7 @@
         <v>60</v>
       </c>
       <c r="C63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D63" t="s">
         <v>96</v>
@@ -8591,13 +8618,13 @@
         <v>283</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -8633,10 +8660,10 @@
         <v>0</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB63">
         <v>0</v>
@@ -8680,7 +8707,7 @@
         <v>61</v>
       </c>
       <c r="C64" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D64" t="s">
         <v>96</v>
@@ -8796,7 +8823,7 @@
         <v>62</v>
       </c>
       <c r="C65" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D65" t="s">
         <v>96</v>
@@ -8823,76 +8850,76 @@
         <v>284</v>
       </c>
       <c r="L65">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="M65">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="N65">
-        <v>3.09</v>
+        <v>4.5</v>
       </c>
       <c r="O65">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="P65">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q65">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R65">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S65">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="T65">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="U65">
         <v>1.22</v>
       </c>
       <c r="V65">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W65">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X65">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y65">
         <v>5.75</v>
       </c>
       <c r="Z65">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AA65">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="AB65">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AC65">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AD65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE65">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF65">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AG65">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AH65">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI65">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ65" t="s">
         <v>286</v>
@@ -8912,7 +8939,7 @@
         <v>62</v>
       </c>
       <c r="C66" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D66" t="s">
         <v>96</v>
@@ -9028,7 +9055,7 @@
         <v>62</v>
       </c>
       <c r="C67" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D67" t="s">
         <v>96</v>
@@ -9144,7 +9171,7 @@
         <v>62</v>
       </c>
       <c r="C68" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D68" t="s">
         <v>96</v>
@@ -9171,76 +9198,76 @@
         <v>284</v>
       </c>
       <c r="L68">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="M68">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="N68">
-        <v>4.5</v>
+        <v>3.09</v>
       </c>
       <c r="O68">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="P68">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q68">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R68">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S68">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="T68">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U68">
         <v>1.22</v>
       </c>
       <c r="V68">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="W68">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X68">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y68">
         <v>5.75</v>
       </c>
       <c r="Z68">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AA68">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="AB68">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AC68">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AD68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE68">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF68">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AG68">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AH68">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI68">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ68" t="s">
         <v>286</v>
@@ -9260,7 +9287,7 @@
         <v>63</v>
       </c>
       <c r="C69" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D69" t="s">
         <v>96</v>
@@ -9269,7 +9296,7 @@
         <v>164</v>
       </c>
       <c r="F69" t="s">
-        <v>152</v>
+        <v>254</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -9287,76 +9314,76 @@
         <v>284</v>
       </c>
       <c r="L69">
-        <v>1.76</v>
+        <v>2.95</v>
       </c>
       <c r="M69">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N69">
-        <v>5.58</v>
+        <v>2.23</v>
       </c>
       <c r="O69">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="P69">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q69">
-        <v>3.25</v>
+        <v>1.73</v>
       </c>
       <c r="R69">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="S69">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="T69">
-        <v>4.33</v>
+        <v>2.62</v>
       </c>
       <c r="U69">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="V69">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="W69">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="X69">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>4.7</v>
+        <v>9.5</v>
       </c>
       <c r="Z69">
-        <v>1.83</v>
+        <v>1.21</v>
       </c>
       <c r="AA69">
-        <v>1.95</v>
+        <v>3.58</v>
       </c>
       <c r="AB69">
-        <v>3.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC69">
-        <v>1.29</v>
+        <v>1.87</v>
       </c>
       <c r="AD69">
-        <v>6.95</v>
+        <v>3.08</v>
       </c>
       <c r="AE69">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="AF69">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG69">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH69">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="AI69">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ69" t="s">
         <v>286</v>
@@ -9376,7 +9403,7 @@
         <v>63</v>
       </c>
       <c r="C70" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D70" t="s">
         <v>96</v>
@@ -9385,7 +9412,7 @@
         <v>165</v>
       </c>
       <c r="F70" t="s">
-        <v>254</v>
+        <v>155</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -9403,76 +9430,76 @@
         <v>284</v>
       </c>
       <c r="L70">
-        <v>2.95</v>
+        <v>1.76</v>
       </c>
       <c r="M70">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N70">
-        <v>2.23</v>
+        <v>5.58</v>
       </c>
       <c r="O70">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q70">
+        <v>3.25</v>
+      </c>
+      <c r="R70">
         <v>1.73</v>
       </c>
-      <c r="R70">
-        <v>1.36</v>
-      </c>
       <c r="S70">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="T70">
-        <v>2.62</v>
+        <v>4.33</v>
       </c>
       <c r="U70">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="V70">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="W70">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="Y70">
-        <v>9.5</v>
+        <v>4.7</v>
       </c>
       <c r="Z70">
-        <v>1.21</v>
+        <v>1.83</v>
       </c>
       <c r="AA70">
-        <v>3.58</v>
+        <v>1.95</v>
       </c>
       <c r="AB70">
-        <v>1.85</v>
+        <v>3.6</v>
       </c>
       <c r="AC70">
-        <v>1.87</v>
+        <v>1.29</v>
       </c>
       <c r="AD70">
-        <v>3.08</v>
+        <v>6.95</v>
       </c>
       <c r="AE70">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="AF70">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
       <c r="AG70">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH70">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AI70">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AJ70" t="s">
         <v>286</v>
@@ -9724,7 +9751,7 @@
         <v>65</v>
       </c>
       <c r="C73" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D73" t="s">
         <v>96</v>
@@ -9751,76 +9778,76 @@
         <v>284</v>
       </c>
       <c r="L73">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="M73">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N73">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="O73">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="P73">
-        <v>7.7</v>
+        <v>11.75</v>
       </c>
       <c r="Q73">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R73">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="S73">
-        <v>2.5</v>
+        <v>3.01</v>
       </c>
       <c r="T73">
-        <v>3.48</v>
+        <v>2.81</v>
       </c>
       <c r="U73">
+        <v>1.43</v>
+      </c>
+      <c r="V73">
+        <v>7.4</v>
+      </c>
+      <c r="W73">
+        <v>1.06</v>
+      </c>
+      <c r="X73">
+        <v>1.05</v>
+      </c>
+      <c r="Y73">
+        <v>10</v>
+      </c>
+      <c r="Z73">
+        <v>1.24</v>
+      </c>
+      <c r="AA73">
+        <v>3.4</v>
+      </c>
+      <c r="AB73">
+        <v>1.94</v>
+      </c>
+      <c r="AC73">
+        <v>1.88</v>
+      </c>
+      <c r="AD73">
+        <v>3.4</v>
+      </c>
+      <c r="AE73">
         <v>1.3</v>
       </c>
-      <c r="V73">
-        <v>10</v>
-      </c>
-      <c r="W73">
-        <v>1.05</v>
-      </c>
-      <c r="X73">
-        <v>1.04</v>
-      </c>
-      <c r="Y73">
-        <v>7</v>
-      </c>
-      <c r="Z73">
-        <v>1.44</v>
-      </c>
-      <c r="AA73">
-        <v>2.63</v>
-      </c>
-      <c r="AB73">
-        <v>2.49</v>
-      </c>
-      <c r="AC73">
-        <v>1.53</v>
-      </c>
-      <c r="AD73">
-        <v>4.5</v>
-      </c>
-      <c r="AE73">
-        <v>1.15</v>
-      </c>
       <c r="AF73">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AG73">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AH73">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AI73">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AJ73" t="s">
         <v>286</v>
@@ -9840,7 +9867,7 @@
         <v>65</v>
       </c>
       <c r="C74" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D74" t="s">
         <v>96</v>
@@ -9867,76 +9894,76 @@
         <v>284</v>
       </c>
       <c r="L74">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="M74">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N74">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="O74">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="P74">
-        <v>11.25</v>
+        <v>7.7</v>
       </c>
       <c r="Q74">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="R74">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="S74">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="T74">
-        <v>2.93</v>
+        <v>3.48</v>
       </c>
       <c r="U74">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V74">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W74">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X74">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y74">
-        <v>8.550000000000001</v>
+        <v>7</v>
       </c>
       <c r="Z74">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AA74">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="AB74">
-        <v>2.07</v>
+        <v>2.49</v>
       </c>
       <c r="AC74">
+        <v>1.53</v>
+      </c>
+      <c r="AD74">
+        <v>4.5</v>
+      </c>
+      <c r="AE74">
+        <v>1.15</v>
+      </c>
+      <c r="AF74">
+        <v>2</v>
+      </c>
+      <c r="AG74">
         <v>1.75</v>
       </c>
-      <c r="AD74">
-        <v>3.2</v>
-      </c>
-      <c r="AE74">
-        <v>1.22</v>
-      </c>
-      <c r="AF74">
-        <v>1.8</v>
-      </c>
-      <c r="AG74">
-        <v>1.9</v>
-      </c>
       <c r="AH74">
-        <v>7.05</v>
+        <v>10</v>
       </c>
       <c r="AI74">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AJ74" t="s">
         <v>286</v>
@@ -9983,76 +10010,76 @@
         <v>284</v>
       </c>
       <c r="L75">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="M75">
         <v>3.2</v>
       </c>
       <c r="N75">
-        <v>2.84</v>
+        <v>3.75</v>
       </c>
       <c r="O75">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="P75">
-        <v>11.75</v>
+        <v>11.25</v>
       </c>
       <c r="Q75">
-        <v>2.26</v>
+        <v>2.88</v>
       </c>
       <c r="R75">
+        <v>1.43</v>
+      </c>
+      <c r="S75">
+        <v>2.82</v>
+      </c>
+      <c r="T75">
+        <v>2.93</v>
+      </c>
+      <c r="U75">
         <v>1.36</v>
       </c>
-      <c r="S75">
-        <v>3.01</v>
-      </c>
-      <c r="T75">
-        <v>2.81</v>
-      </c>
-      <c r="U75">
-        <v>1.43</v>
-      </c>
       <c r="V75">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="W75">
+        <v>1.08</v>
+      </c>
+      <c r="X75">
         <v>1.06</v>
       </c>
-      <c r="X75">
-        <v>1.05</v>
-      </c>
       <c r="Y75">
-        <v>10</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Z75">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AA75">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AB75">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AC75">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AD75">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AE75">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF75">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG75">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AH75">
-        <v>5.5</v>
+        <v>7.05</v>
       </c>
       <c r="AI75">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ75" t="s">
         <v>286</v>
@@ -10099,76 +10126,76 @@
         <v>284</v>
       </c>
       <c r="L76">
-        <v>2.46</v>
+        <v>1.39</v>
       </c>
       <c r="M76">
-        <v>3.33</v>
+        <v>4.33</v>
       </c>
       <c r="N76">
-        <v>2.42</v>
+        <v>5.8</v>
       </c>
       <c r="O76">
-        <v>1.93</v>
+        <v>1.35</v>
       </c>
       <c r="P76">
-        <v>14.5</v>
+        <v>17.75</v>
       </c>
       <c r="Q76">
-        <v>1.98</v>
+        <v>3.4</v>
       </c>
       <c r="R76">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="S76">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="T76">
-        <v>2.48</v>
+        <v>2.21</v>
       </c>
       <c r="U76">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="V76">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="W76">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X76">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="Z76">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AA76">
-        <v>3.94</v>
+        <v>4.6</v>
       </c>
       <c r="AB76">
+        <v>1.56</v>
+      </c>
+      <c r="AC76">
+        <v>2.27</v>
+      </c>
+      <c r="AD76">
+        <v>2.13</v>
+      </c>
+      <c r="AE76">
+        <v>1.63</v>
+      </c>
+      <c r="AF76">
         <v>1.75</v>
       </c>
-      <c r="AC76">
-        <v>1.95</v>
-      </c>
-      <c r="AD76">
-        <v>2.78</v>
-      </c>
-      <c r="AE76">
-        <v>1.36</v>
-      </c>
-      <c r="AF76">
-        <v>1.59</v>
-      </c>
       <c r="AG76">
-        <v>2.21</v>
+        <v>1.96</v>
       </c>
       <c r="AH76">
-        <v>5.2</v>
+        <v>3.88</v>
       </c>
       <c r="AI76">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ76" t="s">
         <v>286</v>
@@ -10215,76 +10242,76 @@
         <v>284</v>
       </c>
       <c r="L77">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="M77">
-        <v>4.33</v>
+        <v>3.45</v>
       </c>
       <c r="N77">
-        <v>5.8</v>
+        <v>3.73</v>
       </c>
       <c r="O77">
+        <v>1.68</v>
+      </c>
+      <c r="P77">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Q77">
+        <v>2.57</v>
+      </c>
+      <c r="R77">
+        <v>1.33</v>
+      </c>
+      <c r="S77">
+        <v>2.93</v>
+      </c>
+      <c r="T77">
+        <v>2.51</v>
+      </c>
+      <c r="U77">
+        <v>1.44</v>
+      </c>
+      <c r="V77">
+        <v>5.75</v>
+      </c>
+      <c r="W77">
+        <v>1.07</v>
+      </c>
+      <c r="X77">
+        <v>1</v>
+      </c>
+      <c r="Y77">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z77">
+        <v>1.22</v>
+      </c>
+      <c r="AA77">
+        <v>3.64</v>
+      </c>
+      <c r="AB77">
+        <v>1.76</v>
+      </c>
+      <c r="AC77">
+        <v>1.94</v>
+      </c>
+      <c r="AD77">
+        <v>2.83</v>
+      </c>
+      <c r="AE77">
         <v>1.35</v>
       </c>
-      <c r="P77">
-        <v>17.75</v>
-      </c>
-      <c r="Q77">
-        <v>3.4</v>
-      </c>
-      <c r="R77">
-        <v>1.23</v>
-      </c>
-      <c r="S77">
-        <v>3.42</v>
-      </c>
-      <c r="T77">
-        <v>2.21</v>
-      </c>
-      <c r="U77">
-        <v>1.59</v>
-      </c>
-      <c r="V77">
-        <v>4.7</v>
-      </c>
-      <c r="W77">
-        <v>1.12</v>
-      </c>
-      <c r="X77">
-        <v>1.03</v>
-      </c>
-      <c r="Y77">
-        <v>11</v>
-      </c>
-      <c r="Z77">
-        <v>1.14</v>
-      </c>
-      <c r="AA77">
-        <v>4.6</v>
-      </c>
-      <c r="AB77">
-        <v>1.56</v>
-      </c>
-      <c r="AC77">
-        <v>2.27</v>
-      </c>
-      <c r="AD77">
-        <v>2.13</v>
-      </c>
-      <c r="AE77">
-        <v>1.63</v>
-      </c>
       <c r="AF77">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG77">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AH77">
-        <v>3.88</v>
+        <v>5.1</v>
       </c>
       <c r="AI77">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ77" t="s">
         <v>286</v>
@@ -10304,7 +10331,7 @@
         <v>66</v>
       </c>
       <c r="C78" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D78" t="s">
         <v>96</v>
@@ -10331,76 +10358,76 @@
         <v>284</v>
       </c>
       <c r="L78">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="M78">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N78">
-        <v>3.31</v>
+        <v>4.8</v>
       </c>
       <c r="O78">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="P78">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="Q78">
+        <v>3.4</v>
+      </c>
+      <c r="R78">
+        <v>1.5</v>
+      </c>
+      <c r="S78">
+        <v>2.45</v>
+      </c>
+      <c r="T78">
+        <v>3.56</v>
+      </c>
+      <c r="U78">
+        <v>1.25</v>
+      </c>
+      <c r="V78">
+        <v>7.8</v>
+      </c>
+      <c r="W78">
+        <v>1.04</v>
+      </c>
+      <c r="X78">
+        <v>1.09</v>
+      </c>
+      <c r="Y78">
+        <v>6.5</v>
+      </c>
+      <c r="Z78">
+        <v>1.53</v>
+      </c>
+      <c r="AA78">
+        <v>2.5</v>
+      </c>
+      <c r="AB78">
+        <v>2.44</v>
+      </c>
+      <c r="AC78">
+        <v>1.5</v>
+      </c>
+      <c r="AD78">
+        <v>4.75</v>
+      </c>
+      <c r="AE78">
+        <v>1.16</v>
+      </c>
+      <c r="AF78">
         <v>2.25</v>
       </c>
-      <c r="R78">
-        <v>1.28</v>
-      </c>
-      <c r="S78">
-        <v>3.4</v>
-      </c>
-      <c r="T78">
-        <v>2.2</v>
-      </c>
-      <c r="U78">
+      <c r="AG78">
         <v>1.6</v>
       </c>
-      <c r="V78">
-        <v>4.75</v>
-      </c>
-      <c r="W78">
-        <v>1.15</v>
-      </c>
-      <c r="X78">
-        <v>1.04</v>
-      </c>
-      <c r="Y78">
-        <v>10</v>
-      </c>
-      <c r="Z78">
-        <v>1.18</v>
-      </c>
-      <c r="AA78">
-        <v>4.75</v>
-      </c>
-      <c r="AB78">
-        <v>1.48</v>
-      </c>
-      <c r="AC78">
-        <v>2.54</v>
-      </c>
-      <c r="AD78">
-        <v>2.25</v>
-      </c>
-      <c r="AE78">
-        <v>1.57</v>
-      </c>
-      <c r="AF78">
-        <v>1.48</v>
-      </c>
-      <c r="AG78">
-        <v>2.5</v>
-      </c>
       <c r="AH78">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="AI78">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AJ78" t="s">
         <v>286</v>
@@ -10652,7 +10679,7 @@
         <v>66</v>
       </c>
       <c r="C81" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D81" t="s">
         <v>96</v>
@@ -10679,76 +10706,76 @@
         <v>284</v>
       </c>
       <c r="L81">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="M81">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N81">
-        <v>4.8</v>
+        <v>3.31</v>
       </c>
       <c r="O81">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="P81">
-        <v>6.25</v>
+        <v>10</v>
       </c>
       <c r="Q81">
+        <v>2.25</v>
+      </c>
+      <c r="R81">
+        <v>1.28</v>
+      </c>
+      <c r="S81">
         <v>3.4</v>
       </c>
-      <c r="R81">
-        <v>1.5</v>
-      </c>
-      <c r="S81">
-        <v>2.45</v>
-      </c>
       <c r="T81">
-        <v>3.56</v>
+        <v>2.2</v>
       </c>
       <c r="U81">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="V81">
-        <v>7.8</v>
+        <v>4.75</v>
       </c>
       <c r="W81">
+        <v>1.15</v>
+      </c>
+      <c r="X81">
         <v>1.04</v>
       </c>
-      <c r="X81">
-        <v>1.09</v>
-      </c>
       <c r="Y81">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="Z81">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="AA81">
+        <v>4.75</v>
+      </c>
+      <c r="AB81">
+        <v>1.48</v>
+      </c>
+      <c r="AC81">
+        <v>2.54</v>
+      </c>
+      <c r="AD81">
+        <v>2.25</v>
+      </c>
+      <c r="AE81">
+        <v>1.57</v>
+      </c>
+      <c r="AF81">
+        <v>1.48</v>
+      </c>
+      <c r="AG81">
         <v>2.5</v>
       </c>
-      <c r="AB81">
-        <v>2.44</v>
-      </c>
-      <c r="AC81">
-        <v>1.5</v>
-      </c>
-      <c r="AD81">
-        <v>4.75</v>
-      </c>
-      <c r="AE81">
-        <v>1.16</v>
-      </c>
-      <c r="AF81">
-        <v>2.25</v>
-      </c>
-      <c r="AG81">
-        <v>1.6</v>
-      </c>
       <c r="AH81">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="AI81">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AJ81" t="s">
         <v>286</v>
@@ -10911,73 +10938,73 @@
         <v>284</v>
       </c>
       <c r="L83">
-        <v>1.78</v>
+        <v>2.46</v>
       </c>
       <c r="M83">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="N83">
-        <v>3.73</v>
+        <v>2.42</v>
       </c>
       <c r="O83">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="P83">
-        <v>9.300000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="Q83">
-        <v>2.57</v>
+        <v>1.98</v>
       </c>
       <c r="R83">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S83">
-        <v>2.93</v>
+        <v>3.18</v>
       </c>
       <c r="T83">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="U83">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V83">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W83">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X83">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y83">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="Z83">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AA83">
-        <v>3.64</v>
+        <v>3.94</v>
       </c>
       <c r="AB83">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC83">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AD83">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AE83">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF83">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AG83">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="AH83">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AI83">
         <v>1.1</v>
@@ -11000,7 +11027,7 @@
         <v>67</v>
       </c>
       <c r="C84" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D84" t="s">
         <v>96</v>
@@ -11116,7 +11143,7 @@
         <v>68</v>
       </c>
       <c r="C85" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D85" t="s">
         <v>96</v>
@@ -11232,7 +11259,7 @@
         <v>69</v>
       </c>
       <c r="C86" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D86" t="s">
         <v>96</v>
@@ -11259,76 +11286,76 @@
         <v>284</v>
       </c>
       <c r="L86">
-        <v>2.86</v>
+        <v>1.62</v>
       </c>
       <c r="M86">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="N86">
-        <v>2.04</v>
+        <v>5.25</v>
       </c>
       <c r="O86">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="P86">
-        <v>12.5</v>
+        <v>7.9</v>
       </c>
       <c r="Q86">
-        <v>1.67</v>
+        <v>2.71</v>
       </c>
       <c r="R86">
+        <v>1.36</v>
+      </c>
+      <c r="S86">
+        <v>2.9</v>
+      </c>
+      <c r="T86">
+        <v>2.7</v>
+      </c>
+      <c r="U86">
+        <v>1.4</v>
+      </c>
+      <c r="V86">
+        <v>6.85</v>
+      </c>
+      <c r="W86">
+        <v>1.08</v>
+      </c>
+      <c r="X86">
+        <v>1</v>
+      </c>
+      <c r="Y86">
+        <v>9</v>
+      </c>
+      <c r="Z86">
+        <v>1.3</v>
+      </c>
+      <c r="AA86">
+        <v>3.14</v>
+      </c>
+      <c r="AB86">
+        <v>1.94</v>
+      </c>
+      <c r="AC86">
+        <v>1.8</v>
+      </c>
+      <c r="AD86">
+        <v>3.45</v>
+      </c>
+      <c r="AE86">
         <v>1.29</v>
       </c>
-      <c r="S86">
-        <v>3.5</v>
-      </c>
-      <c r="T86">
-        <v>2.38</v>
-      </c>
-      <c r="U86">
-        <v>1.53</v>
-      </c>
-      <c r="V86">
-        <v>5.5</v>
-      </c>
-      <c r="W86">
-        <v>1.14</v>
-      </c>
-      <c r="X86">
-        <v>1.04</v>
-      </c>
-      <c r="Y86">
-        <v>10</v>
-      </c>
-      <c r="Z86">
-        <v>1.2</v>
-      </c>
-      <c r="AA86">
-        <v>4.5</v>
-      </c>
-      <c r="AB86">
-        <v>1.67</v>
-      </c>
-      <c r="AC86">
-        <v>2.07</v>
-      </c>
-      <c r="AD86">
-        <v>2.55</v>
-      </c>
-      <c r="AE86">
-        <v>1.5</v>
-      </c>
       <c r="AF86">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG86">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AH86">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AI86">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AJ86" t="s">
         <v>286</v>
@@ -11375,76 +11402,76 @@
         <v>284</v>
       </c>
       <c r="L87">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="M87">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N87">
-        <v>2.94</v>
+        <v>2.48</v>
       </c>
       <c r="O87">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P87">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="Q87">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S87">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T87">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U87">
+        <v>0</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0</v>
+      </c>
+      <c r="X87">
+        <v>0</v>
+      </c>
+      <c r="Y87">
+        <v>0</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+      <c r="AA87">
+        <v>0</v>
+      </c>
+      <c r="AB87">
         <v>1.4</v>
       </c>
-      <c r="V87">
-        <v>7</v>
-      </c>
-      <c r="W87">
-        <v>1.1</v>
-      </c>
-      <c r="X87">
-        <v>1.05</v>
-      </c>
-      <c r="Y87">
-        <v>9.5</v>
-      </c>
-      <c r="Z87">
-        <v>1.28</v>
-      </c>
-      <c r="AA87">
-        <v>3.55</v>
-      </c>
-      <c r="AB87">
-        <v>1.85</v>
-      </c>
       <c r="AC87">
-        <v>1.85</v>
+        <v>2.82</v>
       </c>
       <c r="AD87">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="AE87">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AF87">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH87">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AI87">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ87" t="s">
         <v>286</v>
@@ -11491,76 +11518,76 @@
         <v>284</v>
       </c>
       <c r="L88">
-        <v>1.77</v>
+        <v>2.86</v>
       </c>
       <c r="M88">
-        <v>3.77</v>
+        <v>3.58</v>
       </c>
       <c r="N88">
-        <v>3.45</v>
+        <v>2.04</v>
       </c>
       <c r="O88">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="P88">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q88">
+        <v>1.67</v>
+      </c>
+      <c r="R88">
+        <v>1.29</v>
+      </c>
+      <c r="S88">
+        <v>3.5</v>
+      </c>
+      <c r="T88">
         <v>2.38</v>
       </c>
-      <c r="R88">
-        <v>1.25</v>
-      </c>
-      <c r="S88">
-        <v>3.75</v>
-      </c>
-      <c r="T88">
-        <v>2.1</v>
-      </c>
       <c r="U88">
+        <v>1.53</v>
+      </c>
+      <c r="V88">
+        <v>5.5</v>
+      </c>
+      <c r="W88">
+        <v>1.14</v>
+      </c>
+      <c r="X88">
+        <v>1.04</v>
+      </c>
+      <c r="Y88">
+        <v>10</v>
+      </c>
+      <c r="Z88">
+        <v>1.2</v>
+      </c>
+      <c r="AA88">
+        <v>4.5</v>
+      </c>
+      <c r="AB88">
         <v>1.67</v>
       </c>
-      <c r="V88">
-        <v>5</v>
-      </c>
-      <c r="W88">
-        <v>1.17</v>
-      </c>
-      <c r="X88">
-        <v>1.01</v>
-      </c>
-      <c r="Y88">
-        <v>17</v>
-      </c>
-      <c r="Z88">
-        <v>1.17</v>
-      </c>
-      <c r="AA88">
-        <v>5</v>
-      </c>
-      <c r="AB88">
-        <v>1.45</v>
-      </c>
       <c r="AC88">
-        <v>2.63</v>
+        <v>2.07</v>
       </c>
       <c r="AD88">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AE88">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AF88">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG88">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH88">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AI88">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AJ88" t="s">
         <v>286</v>
@@ -11607,76 +11634,76 @@
         <v>284</v>
       </c>
       <c r="L89">
-        <v>2.34</v>
+        <v>1.77</v>
       </c>
       <c r="M89">
+        <v>3.77</v>
+      </c>
+      <c r="N89">
         <v>3.45</v>
       </c>
-      <c r="N89">
-        <v>2.48</v>
-      </c>
       <c r="O89">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB89">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AC89">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="AD89">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE89">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH89">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ89" t="s">
         <v>286</v>
@@ -11696,7 +11723,7 @@
         <v>69</v>
       </c>
       <c r="C90" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D90" t="s">
         <v>96</v>
@@ -11723,76 +11750,76 @@
         <v>284</v>
       </c>
       <c r="L90">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="M90">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="N90">
-        <v>5.25</v>
+        <v>2.94</v>
       </c>
       <c r="O90">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="P90">
-        <v>7.9</v>
+        <v>9.75</v>
       </c>
       <c r="Q90">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="R90">
         <v>1.36</v>
       </c>
       <c r="S90">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T90">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U90">
         <v>1.4</v>
       </c>
       <c r="V90">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="W90">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X90">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y90">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Z90">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA90">
-        <v>3.14</v>
+        <v>3.55</v>
       </c>
       <c r="AB90">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC90">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD90">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AE90">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF90">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG90">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH90">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="AI90">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AJ90" t="s">
         <v>286</v>
@@ -11839,76 +11866,76 @@
         <v>284</v>
       </c>
       <c r="L91">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="M91">
         <v>3.25</v>
       </c>
       <c r="N91">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="O91">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="P91">
         <v>0</v>
       </c>
       <c r="Q91">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="R91">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S91">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="T91">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="U91">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V91">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W91">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X91">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z91">
         <v>1.22</v>
       </c>
       <c r="AA91">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AB91">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC91">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AD91">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AE91">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF91">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG91">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH91">
-        <v>4.7</v>
+        <v>6.15</v>
       </c>
       <c r="AI91">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AJ91" t="s">
         <v>286</v>
@@ -11955,76 +11982,76 @@
         <v>284</v>
       </c>
       <c r="L92">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="M92">
         <v>3.25</v>
       </c>
       <c r="N92">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="O92">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="P92">
         <v>0</v>
       </c>
       <c r="Q92">
-        <v>2.63</v>
+        <v>1.73</v>
       </c>
       <c r="R92">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S92">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="T92">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="U92">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V92">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W92">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X92">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y92">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z92">
         <v>1.22</v>
       </c>
       <c r="AA92">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AB92">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AC92">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AD92">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="AE92">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF92">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG92">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH92">
-        <v>6.15</v>
+        <v>4.7</v>
       </c>
       <c r="AI92">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AJ92" t="s">
         <v>286</v>

--- a/jogos_2025-07-12.xlsx
+++ b/jogos_2025-07-12.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,16 +1159,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.34</v>
+        <v>6.07</v>
       </c>
       <c r="M6" t="n">
-        <v>3.45</v>
+        <v>4.75</v>
       </c>
       <c r="N6" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>3.29</v>
+        <v>4.05</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>6.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.88</v>
+        <v>2.01</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.36</v>
+        <v>1.76</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AD6" t="n">
         <v>2.2</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.66</v>
+        <v>1.13</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.2</v>
+        <v>2.71</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45850.25</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,16 +1288,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.07</v>
+        <v>3.34</v>
       </c>
       <c r="M7" t="n">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="N7" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="O7" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.67</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>4.05</v>
+        <v>3.29</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>6.05</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.01</v>
+        <v>2.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AD7" t="n">
         <v>2.2</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.13</v>
+        <v>1.66</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.71</v>
+        <v>2.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45850.25</v>
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="M10" t="n">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="N10" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="O10" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
         <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="T10" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="U10" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['46']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45850.29166666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>3.96</v>
+        <v>5.2</v>
       </c>
       <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.22</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD11" t="n">
         <v>2</v>
       </c>
-      <c r="AA11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['64', '79']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '87']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45850.29166666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,23 +1933,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.86</v>
+        <v>1.68</v>
       </c>
       <c r="M12" t="n">
-        <v>3.23</v>
+        <v>3.68</v>
       </c>
       <c r="N12" t="n">
-        <v>2.17</v>
+        <v>3.96</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>2.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.11</v>
+        <v>3.26</v>
       </c>
       <c r="T12" t="n">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="U12" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['81']</t>
-        </is>
-      </c>
       <c r="AG12" t="n">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.41</v>
+        <v>2.03</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.03</v>
+        <v>1.51</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.97</v>
+        <v>2.58</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45850.29166666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,16 +2062,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.16</v>
+        <v>3.33</v>
       </c>
       <c r="M13" t="n">
-        <v>2.82</v>
+        <v>3.22</v>
       </c>
       <c r="N13" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.74</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
         <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="X13" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
+          <t>['69', '51']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG13" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45850.29166666666</v>
@@ -2191,16 +2191,16 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -2209,7 +2209,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>3.15</v>
       </c>
       <c r="M14" t="n">
-        <v>2.89</v>
+        <v>3.14</v>
       </c>
       <c r="N14" t="n">
-        <v>3.29</v>
+        <v>2.06</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.83</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['18', '59']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['38']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45850.29166666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
         <v>1</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>2.13</v>
       </c>
       <c r="M15" t="n">
-        <v>4.33</v>
+        <v>2.89</v>
       </c>
       <c r="N15" t="n">
-        <v>7.1</v>
+        <v>3.29</v>
       </c>
       <c r="O15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P15" t="n">
         <v>1.83</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.42</v>
-      </c>
       <c r="Q15" t="n">
-        <v>6.3</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>1.59</v>
       </c>
       <c r="S15" t="n">
-        <v>3.28</v>
+        <v>2.33</v>
       </c>
       <c r="T15" t="n">
-        <v>2.29</v>
+        <v>3.74</v>
       </c>
       <c r="U15" t="n">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.53</v>
       </c>
       <c r="X15" t="n">
-        <v>4.45</v>
+        <v>2.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.53</v>
+        <v>2.48</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.25</v>
+        <v>1.47</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.26</v>
+        <v>5.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.51</v>
+        <v>1.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['18', '59']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.82</v>
+        <v>1.56</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.33</v>
+        <v>1.88</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.32</v>
+        <v>2.4</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45850.29166666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Q16" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="T16" t="n">
-        <v>2.38</v>
+        <v>3.18</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.2</v>
       </c>
-      <c r="X16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC16" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['64', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['33', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45850.29166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.33</v>
+        <v>2.64</v>
       </c>
       <c r="M17" t="n">
-        <v>3.22</v>
+        <v>3.06</v>
       </c>
       <c r="N17" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
         <v>1.36</v>
       </c>
       <c r="X17" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AA17" t="n">
         <v>4</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['69', '51']</t>
+          <t>['78', '90+1']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '46', '54']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45850.29166666666</v>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.64</v>
+        <v>1.34</v>
       </c>
       <c r="M18" t="n">
-        <v>3.06</v>
+        <v>4.33</v>
       </c>
       <c r="N18" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P18" t="n">
         <v>2.42</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>6.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>2.76</v>
+        <v>3.28</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="U18" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.05</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['78', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['24', '46', '54']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.48</v>
+        <v>2.82</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.05</v>
+        <v>1.33</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.05</v>
+        <v>3.32</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45850.29166666666</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.82</v>
+        <v>3.16</v>
       </c>
       <c r="M19" t="n">
-        <v>3.33</v>
+        <v>2.82</v>
       </c>
       <c r="N19" t="n">
-        <v>3.69</v>
+        <v>2.23</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="S19" t="n">
-        <v>2.78</v>
+        <v>2.23</v>
       </c>
       <c r="T19" t="n">
-        <v>3.18</v>
+        <v>3.74</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="V19" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W19" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AA19" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.77</v>
+        <v>1.29</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45850.29166666666</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z23" t="n">
         <v>2</v>
       </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AA23" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['10', '35']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG23" t="n">
         <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45850.35416666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.44</v>
+        <v>4.52</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="X24" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AA24" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '35']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AG24" t="n">
         <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45850.35416666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="M28" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="N28" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="P28" t="n">
-        <v>2.58</v>
+        <v>3.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="U28" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="V28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.35</v>
+        <v>3.33</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['40', '21', '45+1']</t>
+          <t>['59', '68']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AJ28" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45850.45833333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="M29" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="N29" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.62</v>
       </c>
-      <c r="P29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>8</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.83</v>
-      </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X29" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.33</v>
+        <v>2.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['59', '68']</t>
+          <t>['40', '21', '45+1']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45850.45833333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,109 +4255,109 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="N30" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="O30" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['70', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45850.5</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,34 +4410,34 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.44</v>
+        <v>2.57</v>
       </c>
       <c r="M31" t="n">
-        <v>3.13</v>
+        <v>2.94</v>
       </c>
       <c r="N31" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4461,10 +4461,10 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4483,10 +4483,10 @@
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45850.5</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,54 +4513,54 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.57</v>
+        <v>3.7</v>
       </c>
       <c r="M32" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>2.57</v>
+        <v>1.98</v>
       </c>
       <c r="O32" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="P32" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="R32" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="S32" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T32" t="n">
         <v>3.75</v>
@@ -4569,53 +4569,53 @@
         <v>1.25</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AD32" t="n">
         <v>1.67</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['70', '87']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.05</v>
+        <v>3.18</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45850.5</v>
@@ -4632,119 +4632,119 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '49', '81']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45850.52083333334</v>
@@ -4761,35 +4761,35 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.46</v>
+        <v>3.07</v>
       </c>
       <c r="M34" t="n">
-        <v>3.93</v>
+        <v>2.91</v>
       </c>
       <c r="N34" t="n">
-        <v>5.6</v>
+        <v>2.22</v>
       </c>
       <c r="O34" t="n">
-        <v>1.67</v>
+        <v>4.5</v>
       </c>
       <c r="P34" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="V34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>1.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['32', '49', '81']</t>
+          <t>['81', '90+4', '90+13']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['13', '19', '49']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.22</v>
+        <v>2.63</v>
       </c>
       <c r="AJ34" t="n">
-        <v>4</v>
+        <v>1.57</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45850.52083333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="M35" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3.35</v>
+        <v>2.41</v>
       </c>
       <c r="O35" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD35" t="n">
         <v>2</v>
       </c>
-      <c r="T35" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81', '85', '88', '90+9']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '63']</t>
         </is>
       </c>
       <c r="AG35" t="n">
         <v>1.44</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI35" t="n">
         <v>1.83</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45850.54166666666</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,109 +5029,109 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S36" t="n">
         <v>2</v>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="M36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="O36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T36" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="U36" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="V36" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="W36" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="X36" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.45</v>
+        <v>6.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AD36" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['81', '85', '88', '90+9']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['4', '63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG36" t="n">
         <v>1.44</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AI36" t="n">
         <v>1.83</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45850.54166666666</v>
@@ -5158,25 +5158,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.05</v>
+        <v>2.69</v>
       </c>
       <c r="M37" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q37" t="n">
         <v>3.2</v>
       </c>
-      <c r="N37" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O37" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>4.09</v>
-      </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S37" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U37" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X37" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AB37" t="n">
         <v>1.21</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['3', '53', '83', '76', '89']</t>
+          <t>['38', '83', '78']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['36', '25', '90+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45850.54166666666</v>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" t="n">
         <v>3</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.69</v>
+        <v>2.05</v>
       </c>
       <c r="M38" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="O38" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="P38" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.2</v>
+        <v>4.09</v>
       </c>
       <c r="R38" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S38" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="T38" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V38" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X38" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AA38" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AB38" t="n">
         <v>1.21</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['38', '83', '78']</t>
+          <t>['3', '53', '83', '76', '89']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36', '25', '90+6']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45850.54166666666</v>
@@ -5567,32 +5567,32 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M40" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
         <v>3.3</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P40" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="R40" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="S40" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="T40" t="n">
         <v>3.75</v>
@@ -5601,19 +5601,19 @@
         <v>1.25</v>
       </c>
       <c r="V40" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W40" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="X40" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Y40" t="n">
         <v>2.7</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AA40" t="n">
         <v>5.5</v>
@@ -5622,10 +5622,10 @@
         <v>1.08</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45850.625</v>
@@ -5922,26 +5922,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -5954,69 +5954,69 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45850.64583333334</v>
@@ -6051,32 +6051,32 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="M44" t="n">
-        <v>4.5</v>
+        <v>3.56</v>
       </c>
       <c r="N44" t="n">
-        <v>8.5</v>
+        <v>2.7</v>
       </c>
       <c r="O44" t="n">
-        <v>1.88</v>
+        <v>2.95</v>
       </c>
       <c r="P44" t="n">
-        <v>2.62</v>
+        <v>2.13</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.7</v>
+        <v>3.35</v>
       </c>
       <c r="R44" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S44" t="n">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="T44" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U44" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="V44" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W44" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X44" t="n">
-        <v>4.12</v>
+        <v>3.58</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="Z44" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD44" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA44" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['3', '11', '58']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45850.64583333334</v>
@@ -6190,19 +6190,19 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.9</v>
+        <v>1.73</v>
       </c>
       <c r="M45" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N45" t="n">
-        <v>1.73</v>
+        <v>5.5</v>
       </c>
       <c r="O45" t="n">
-        <v>4.5</v>
+        <v>2.39</v>
       </c>
       <c r="P45" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.38</v>
+        <v>5.75</v>
       </c>
       <c r="R45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI45" t="n">
         <v>1.57</v>
       </c>
-      <c r="S45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T45" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AJ45" t="n">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45850.64583333334</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,22 +6319,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="M46" t="n">
-        <v>3.56</v>
+        <v>3.15</v>
       </c>
       <c r="N46" t="n">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="O46" t="n">
-        <v>2.95</v>
+        <v>4.5</v>
       </c>
       <c r="P46" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.35</v>
+        <v>2.38</v>
       </c>
       <c r="R46" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="S46" t="n">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="T46" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="U46" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="V46" t="n">
         <v>1.05</v>
       </c>
       <c r="W46" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="X46" t="n">
-        <v>3.58</v>
+        <v>2.3</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.77</v>
+        <v>2.62</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.93</v>
+        <v>1.42</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.83</v>
+        <v>5</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['3', '11', '58']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.57</v>
+        <v>1.13</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45850.64583333334</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,22 +6577,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.1</v>
+        <v>2.13</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N48" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X48" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC48" t="n">
         <v>2.2</v>
       </c>
-      <c r="O48" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S48" t="n">
+      <c r="AD48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>['45', '90+2', '71']</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ48" t="n">
         <v>2.88</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X48" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>['12', '39', '61', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>['14', '74']</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.85</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45850.66666666666</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,25 +6706,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="M49" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="N49" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O49" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="P49" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="R49" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S49" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="T49" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="U49" t="n">
         <v>1.44</v>
       </c>
       <c r="V49" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X49" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AD49" t="n">
         <v>2.1</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['31', '56']</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>['20', '85']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AH49" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.63</v>
+        <v>2.11</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45850.66666666666</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,109 +6835,109 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" t="n">
         <v>1</v>
       </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
         <v>1</v>
       </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O50" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y50" t="n">
         <v>1.8</v>
       </c>
-      <c r="M50" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N50" t="n">
-        <v>5</v>
-      </c>
-      <c r="O50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P50" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>6</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>2.7</v>
-      </c>
       <c r="Z50" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AA50" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['31', '56']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['20', '85']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AI50" t="n">
         <v>1.53</v>
       </c>
       <c r="AJ50" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45850.66666666666</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,16 +6964,16 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H51" t="n">
         <v>1</v>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="M51" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>3.79</v>
+        <v>2.95</v>
       </c>
       <c r="O51" t="n">
         <v>2.9</v>
       </c>
       <c r="P51" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.87</v>
+        <v>3.5</v>
       </c>
       <c r="R51" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S51" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="T51" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="U51" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="V51" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W51" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="X51" t="n">
-        <v>2.24</v>
+        <v>2.87</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AA51" t="n">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AC51" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>['33', '56']</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ51" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>['45', '90+2', '71']</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>['35']</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45850.66666666666</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7111,7 +7111,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -7119,83 +7119,83 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.61</v>
+        <v>1.8</v>
       </c>
       <c r="M52" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N52" t="n">
+        <v>5</v>
+      </c>
+      <c r="O52" t="n">
         <v>2.5</v>
       </c>
-      <c r="O52" t="n">
-        <v>3.1</v>
-      </c>
       <c r="P52" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.02</v>
+        <v>6</v>
       </c>
       <c r="R52" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="S52" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="T52" t="n">
-        <v>2.68</v>
+        <v>3.75</v>
       </c>
       <c r="U52" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V52" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="W52" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="X52" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.83</v>
+        <v>2.7</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AA52" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45850.66666666666</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.05</v>
+        <v>2.61</v>
       </c>
       <c r="M53" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N53" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="O53" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="P53" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="R53" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S53" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="T53" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="U53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X53" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH53" t="n">
         <v>1.44</v>
       </c>
-      <c r="V53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X53" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>['66']</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>['52']</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AI53" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AJ53" t="n">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45850.66666666666</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,22 +7351,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G54" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" t="n">
         <v>2</v>
       </c>
-      <c r="H54" t="n">
-        <v>1</v>
-      </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>1</v>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="M54" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N54" t="n">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="O54" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="R54" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S54" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="T54" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U54" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X54" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB54" t="n">
         <v>1.33</v>
       </c>
-      <c r="V54" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="Y54" t="n">
+      <c r="AC54" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD54" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z54" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['33', '56']</t>
+          <t>['12', '39', '61', '90+2']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['14', '74']</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AJ54" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45850.66666666666</v>
@@ -7738,22 +7738,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -7764,65 +7764,65 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="M57" t="n">
         <v>2.96</v>
       </c>
       <c r="N57" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="O57" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="P57" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.8</v>
+        <v>3.86</v>
       </c>
       <c r="R57" t="n">
         <v>1.6</v>
       </c>
       <c r="S57" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T57" t="n">
-        <v>3.94</v>
+        <v>3.09</v>
       </c>
       <c r="U57" t="n">
         <v>1.22</v>
       </c>
       <c r="V57" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="W57" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X57" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AA57" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AB57" t="n">
         <v>1.11</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AD57" t="n">
         <v>1.6</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['11', '66']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -7834,13 +7834,13 @@
         <v>1.4</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AI57" t="n">
         <v>1.8</v>
       </c>
       <c r="AJ57" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45850.70833333334</v>
@@ -7867,22 +7867,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7893,65 +7893,65 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="M58" t="n">
         <v>2.96</v>
       </c>
       <c r="N58" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="O58" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="P58" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.86</v>
+        <v>4.8</v>
       </c>
       <c r="R58" t="n">
         <v>1.6</v>
       </c>
       <c r="S58" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T58" t="n">
-        <v>3.09</v>
+        <v>3.94</v>
       </c>
       <c r="U58" t="n">
         <v>1.22</v>
       </c>
       <c r="V58" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="W58" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X58" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AA58" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AB58" t="n">
         <v>1.11</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AD58" t="n">
         <v>1.6</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '66']</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7963,13 +7963,13 @@
         <v>1.4</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AI58" t="n">
         <v>1.8</v>
       </c>
       <c r="AJ58" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45850.70833333334</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,109 +8383,109 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Huracán</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O62" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X62" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA62" t="n">
         <v>6</v>
       </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M62" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N62" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O62" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="P62" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S62" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="T62" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W62" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X62" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AB62" t="n">
-        <v>1.6</v>
+        <v>1.12</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>['35', '45+2', '53', '66', '73', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '56', '90+5']</t>
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AH62" t="n">
-        <v>3.14</v>
+        <v>1.78</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AJ62" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45850.77083333334</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,25 +8512,25 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
         <v>2</v>
       </c>
-      <c r="H63" t="n">
-        <v>2</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1</v>
-      </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -8538,83 +8538,83 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.76</v>
+        <v>1.35</v>
       </c>
       <c r="M63" t="n">
-        <v>2.78</v>
+        <v>5.1</v>
       </c>
       <c r="N63" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="O63" t="n">
-        <v>3.5</v>
+        <v>1.71</v>
       </c>
       <c r="P63" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.9</v>
+        <v>6.75</v>
       </c>
       <c r="R63" t="n">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="S63" t="n">
-        <v>2.15</v>
+        <v>3.74</v>
       </c>
       <c r="T63" t="n">
-        <v>3.75</v>
+        <v>2.19</v>
       </c>
       <c r="U63" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="V63" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W63" t="n">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="X63" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.36</v>
+        <v>2.63</v>
       </c>
       <c r="AA63" t="n">
-        <v>6</v>
+        <v>2.23</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="AC63" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>['41', '47']</t>
+          <t>['35', '45+2', '53', '66', '73', '82']</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>['45+11', '27']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.44</v>
+        <v>3.14</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.91</v>
+        <v>1.28</v>
       </c>
       <c r="AJ63" t="n">
-        <v>2.4</v>
+        <v>3.48</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45850.77083333334</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,25 +8641,25 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64" t="n">
+        <v>2</v>
+      </c>
+      <c r="I64" t="n">
         <v>1</v>
       </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -8667,83 +8667,83 @@
         </is>
       </c>
       <c r="L64" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O64" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S64" t="n">
         <v>2.15</v>
-      </c>
-      <c r="M64" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N64" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O64" t="n">
-        <v>3</v>
-      </c>
-      <c r="P64" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S64" t="n">
-        <v>2.25</v>
       </c>
       <c r="T64" t="n">
         <v>3.75</v>
       </c>
       <c r="U64" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="V64" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="W64" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="X64" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AA64" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD64" t="n">
         <v>1.62</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '47']</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['45+11', '27']</t>
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45850.77083333334</v>
@@ -8770,19 +8770,19 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Huracán</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Instituto</t>
         </is>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M65" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N65" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="O65" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P65" t="n">
         <v>1.91</v>
       </c>
       <c r="Q65" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="R65" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S65" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T65" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U65" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V65" t="n">
         <v>1.12</v>
       </c>
       <c r="W65" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="X65" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AA65" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AB65" t="n">
         <v>1.12</v>
       </c>
       <c r="AC65" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8859,20 +8859,20 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>['4', '56', '90+5']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AJ65" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45850.77083333334</v>
@@ -9286,69 +9286,69 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G69" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" t="n">
         <v>1</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>2</v>
       </c>
-      <c r="I69" t="n">
+      <c r="J69" t="n">
         <v>1</v>
       </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="M69" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="N69" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="O69" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P69" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="R69" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S69" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="T69" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U69" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V69" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="W69" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X69" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="Y69" t="n">
         <v>3</v>
@@ -9357,38 +9357,38 @@
         <v>1.36</v>
       </c>
       <c r="AA69" t="n">
-        <v>5.7</v>
+        <v>6.55</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AC69" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>['2', '43']</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>['90', '90+5']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AJ69" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AK69" s="3" t="n">
         <v>45850.8125</v>
@@ -9415,25 +9415,25 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="n">
         <v>2</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>1</v>
       </c>
-      <c r="I70" t="n">
-        <v>2</v>
-      </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -9441,43 +9441,43 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="M70" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="N70" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P70" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="R70" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S70" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="T70" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U70" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V70" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="W70" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X70" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Y70" t="n">
         <v>3</v>
@@ -9486,38 +9486,38 @@
         <v>1.36</v>
       </c>
       <c r="AA70" t="n">
-        <v>6.55</v>
+        <v>5.7</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC70" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>['2', '43']</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['90', '90+5']</t>
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ70" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK70" s="3" t="n">
         <v>45850.8125</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,22 +9544,22 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>2</v>
@@ -9570,83 +9570,83 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.14</v>
+        <v>1.79</v>
       </c>
       <c r="M71" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="N71" t="n">
-        <v>3.02</v>
+        <v>4</v>
       </c>
       <c r="O71" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S71" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T71" t="n">
         <v>2.75</v>
       </c>
-      <c r="P71" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>4</v>
-      </c>
-      <c r="R71" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S71" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T71" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U71" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V71" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W71" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="X71" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AA71" t="n">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD71" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>['16', '34', '58']</t>
+          <t>['23', '5']</t>
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AJ71" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="AK71" s="3" t="n">
         <v>45850.83333333334</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,25 +9673,25 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -9699,83 +9699,83 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="M72" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N72" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O72" t="n">
         <v>2.75</v>
       </c>
-      <c r="O72" t="n">
-        <v>2.95</v>
-      </c>
       <c r="P72" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="R72" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="T72" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U72" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V72" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W72" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="X72" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AA72" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AD72" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '34', '58']</t>
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AJ72" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AK72" s="3" t="n">
         <v>45850.83333333334</v>
@@ -9802,25 +9802,25 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G73" t="n">
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -9828,83 +9828,83 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.79</v>
+        <v>2.33</v>
       </c>
       <c r="M73" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N73" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="O73" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P73" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S73" t="n">
+        <v>3</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W73" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X73" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD73" t="n">
         <v>2.1</v>
       </c>
-      <c r="P73" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R73" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S73" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T73" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U73" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V73" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W73" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X73" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD73" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>['23', '5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.91</v>
+        <v>1.51</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AJ73" t="n">
-        <v>2.88</v>
+        <v>2.26</v>
       </c>
       <c r="AK73" s="3" t="n">
         <v>45850.83333333334</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,22 +9931,22 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" t="n">
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -9957,83 +9957,83 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.84</v>
+        <v>2.48</v>
       </c>
       <c r="M74" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N74" t="n">
-        <v>4.8</v>
+        <v>2.44</v>
       </c>
       <c r="O74" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="P74" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="Q74" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R74" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="S74" t="n">
-        <v>2.39</v>
+        <v>3.2</v>
       </c>
       <c r="T74" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="U74" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V74" t="n">
+        <v>1</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X74" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AG74" t="n">
         <v>1.29</v>
       </c>
-      <c r="V74" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W74" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X74" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AG74" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH74" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AJ74" t="n">
-        <v>3.4</v>
+        <v>2.14</v>
       </c>
       <c r="AK74" s="3" t="n">
         <v>45850.85416666666</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,22 +10060,22 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -10086,80 +10086,80 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.39</v>
+        <v>1.84</v>
       </c>
       <c r="M75" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="N75" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="O75" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="P75" t="n">
-        <v>2.58</v>
+        <v>1.93</v>
       </c>
       <c r="Q75" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="R75" t="n">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="S75" t="n">
-        <v>3.42</v>
+        <v>2.39</v>
       </c>
       <c r="T75" t="n">
-        <v>2.21</v>
+        <v>3.4</v>
       </c>
       <c r="U75" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="V75" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W75" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="X75" t="n">
-        <v>4.6</v>
+        <v>2.62</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.56</v>
+        <v>2.45</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.27</v>
+        <v>1.44</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.13</v>
+        <v>4.75</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.63</v>
+        <v>1.16</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD75" t="n">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG75" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AH75" t="n">
-        <v>2.94</v>
+        <v>1.95</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AJ75" t="n">
         <v>3.4</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,83 +10344,83 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.48</v>
+        <v>1.41</v>
       </c>
       <c r="M77" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="N77" t="n">
-        <v>2.44</v>
+        <v>7.5</v>
       </c>
       <c r="O77" t="n">
-        <v>2.59</v>
+        <v>1.85</v>
       </c>
       <c r="P77" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="R77" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S77" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="T77" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="U77" t="n">
-        <v>1.46</v>
+        <v>1.79</v>
       </c>
       <c r="V77" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W77" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="X77" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.94</v>
+        <v>2.92</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AD77" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ77" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
         <v>45850.85416666666</v>
@@ -10447,22 +10447,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -10473,77 +10473,77 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.72</v>
+        <v>2.42</v>
       </c>
       <c r="M78" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N78" t="n">
-        <v>3.76</v>
+        <v>2.78</v>
       </c>
       <c r="O78" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="P78" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="R78" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S78" t="n">
         <v>3.25</v>
       </c>
       <c r="T78" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="U78" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V78" t="n">
         <v>1.04</v>
       </c>
       <c r="W78" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X78" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>['9', '24']</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+11']</t>
         </is>
       </c>
       <c r="AG78" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -10576,22 +10576,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -10602,83 +10602,83 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.46</v>
+        <v>1.72</v>
       </c>
       <c r="M79" t="n">
-        <v>3.33</v>
+        <v>3.65</v>
       </c>
       <c r="N79" t="n">
-        <v>2.42</v>
+        <v>3.76</v>
       </c>
       <c r="O79" t="n">
-        <v>3.04</v>
+        <v>2.49</v>
       </c>
       <c r="P79" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.18</v>
+        <v>3.9</v>
       </c>
       <c r="R79" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S79" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="T79" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="U79" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="V79" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W79" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X79" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AD79" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['9', '24']</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>['90+11']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG79" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AJ79" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
         <v>45850.85416666666</v>
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="M81" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N81" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="O81" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="P81" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="R81" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S81" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T81" t="n">
         <v>2</v>
       </c>
       <c r="U81" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V81" t="n">
         <v>1.01</v>
       </c>
       <c r="W81" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X81" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z81" t="n">
         <v>2.74</v>
       </c>
       <c r="AA81" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AD81" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,16 +10927,16 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AI81" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ81" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK81" s="3" t="n">
         <v>45850.86458333334</v>
@@ -11221,25 +11221,25 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G84" t="n">
+        <v>4</v>
+      </c>
+      <c r="H84" t="n">
         <v>1</v>
       </c>
-      <c r="H84" t="n">
-        <v>2</v>
-      </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -11247,83 +11247,83 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.34</v>
+        <v>1.77</v>
       </c>
       <c r="M84" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N84" t="n">
         <v>3.45</v>
       </c>
-      <c r="N84" t="n">
-        <v>2.48</v>
-      </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['2', '42', '45+5', '90+5']</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>['8', '45+3']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI84" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK84" s="3" t="n">
         <v>45850.89583333334</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,25 +11350,25 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H85" t="n">
         <v>3</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -11376,83 +11376,83 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.86</v>
+        <v>1.74</v>
       </c>
       <c r="M85" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="N85" t="n">
-        <v>2.04</v>
+        <v>4.2</v>
       </c>
       <c r="O85" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P85" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S85" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X85" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA85" t="n">
         <v>3.5</v>
       </c>
-      <c r="P85" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R85" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S85" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T85" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U85" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V85" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W85" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X85" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AA85" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AB85" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AD85" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>['67', '90+6']</t>
+          <t>['16', '9', '76', '90+2']</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>['15', '27', '45+8']</t>
+          <t>['32', '45+2', '62']</t>
         </is>
       </c>
       <c r="AG85" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.37</v>
+        <v>2.15</v>
       </c>
       <c r="AI85" t="n">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AJ85" t="n">
-        <v>1.67</v>
+        <v>2.71</v>
       </c>
       <c r="AK85" s="3" t="n">
         <v>45850.89583333334</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,25 +11479,25 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H86" t="n">
         <v>3</v>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -11505,83 +11505,83 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.74</v>
+        <v>2.86</v>
       </c>
       <c r="M86" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="N86" t="n">
-        <v>4.2</v>
+        <v>2.04</v>
       </c>
       <c r="O86" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="P86" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q86" t="n">
-        <v>5.2</v>
+        <v>2.63</v>
       </c>
       <c r="R86" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S86" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T86" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V86" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W86" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X86" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>['67', '90+6']</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>['15', '27', '45+8']</t>
+        </is>
+      </c>
+      <c r="AG86" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH86" t="n">
         <v>1.37</v>
       </c>
-      <c r="S86" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T86" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U86" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V86" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W86" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X86" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y86" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z86" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA86" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB86" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC86" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD86" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>['16', '9', '76', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>['32', '45+2', '62']</t>
-        </is>
-      </c>
-      <c r="AG86" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH86" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AI86" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="AJ86" t="n">
-        <v>2.71</v>
+        <v>1.67</v>
       </c>
       <c r="AK86" s="3" t="n">
         <v>45850.89583333334</v>
@@ -11737,25 +11737,25 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -11763,83 +11763,83 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.77</v>
+        <v>2.48</v>
       </c>
       <c r="M88" t="n">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="N88" t="n">
-        <v>3.45</v>
+        <v>2.49</v>
       </c>
       <c r="O88" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="P88" t="n">
         <v>2.5</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="R88" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S88" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T88" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V88" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W88" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X88" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>['8', '45+3']</t>
+        </is>
+      </c>
+      <c r="AG88" t="n">
         <v>1.25</v>
       </c>
-      <c r="S88" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T88" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U88" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V88" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W88" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X88" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y88" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z88" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA88" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB88" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC88" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD88" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE88" t="inlineStr">
-        <is>
-          <t>['2', '42', '45+5', '90+5']</t>
-        </is>
-      </c>
-      <c r="AF88" t="inlineStr">
-        <is>
-          <t>['70']</t>
-        </is>
-      </c>
-      <c r="AG88" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH88" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AI88" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ88" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
         <v>45850.89583333334</v>
@@ -11995,19 +11995,19 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G90" t="n">
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -12021,83 +12021,83 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.81</v>
+        <v>2.21</v>
       </c>
       <c r="M90" t="n">
-        <v>2.97</v>
+        <v>3.47</v>
       </c>
       <c r="N90" t="n">
-        <v>2.46</v>
+        <v>2.78</v>
       </c>
       <c r="O90" t="n">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="P90" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.57</v>
+        <v>3.5</v>
       </c>
       <c r="R90" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S90" t="n">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="T90" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U90" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V90" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W90" t="n">
         <v>1.22</v>
       </c>
       <c r="X90" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.59</v>
+        <v>3.25</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AC90" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG90" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH90" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD90" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>['68', '49']</t>
-        </is>
-      </c>
-      <c r="AG90" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH90" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AI90" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AJ90" t="n">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="AK90" s="3" t="n">
         <v>45850.91666666666</v>
@@ -12124,19 +12124,19 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G91" t="n">
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -12150,83 +12150,83 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.21</v>
+        <v>2.81</v>
       </c>
       <c r="M91" t="n">
-        <v>3.47</v>
+        <v>2.97</v>
       </c>
       <c r="N91" t="n">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="O91" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="P91" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="R91" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S91" t="n">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="T91" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U91" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V91" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W91" t="n">
         <v>1.22</v>
       </c>
       <c r="X91" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AA91" t="n">
-        <v>3.25</v>
+        <v>2.59</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AD91" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68', '49']</t>
         </is>
       </c>
       <c r="AG91" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AJ91" t="n">
-        <v>2.63</v>
+        <v>1.73</v>
       </c>
       <c r="AK91" s="3" t="n">
         <v>45850.91666666666</v>
@@ -12253,22 +12253,22 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -12279,65 +12279,65 @@
         </is>
       </c>
       <c r="L92" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M92" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N92" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O92" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P92" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S92" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="T92" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U92" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V92" t="n">
+        <v>1</v>
+      </c>
+      <c r="W92" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X92" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD92" t="n">
         <v>2.2</v>
       </c>
-      <c r="M92" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="N92" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O92" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P92" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R92" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S92" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T92" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U92" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V92" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W92" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X92" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y92" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA92" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB92" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC92" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD92" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>['12', '30', '59']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -12346,16 +12346,16 @@
         </is>
       </c>
       <c r="AG92" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AH92" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AI92" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ92" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
         <v>45850.9375</v>
@@ -12382,22 +12382,22 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -12408,83 +12408,83 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="M93" t="n">
-        <v>3.41</v>
+        <v>3.31</v>
       </c>
       <c r="N93" t="n">
-        <v>3.26</v>
+        <v>2.75</v>
       </c>
       <c r="O93" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="P93" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q93" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R93" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S93" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T93" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="U93" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V93" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W93" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X93" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Z93" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AD93" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>['12', '30', '59']</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG93" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ93" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AE93" t="inlineStr">
-        <is>
-          <t>['42']</t>
-        </is>
-      </c>
-      <c r="AF93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG93" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH93" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI93" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ93" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK93" s="3" t="n">
         <v>45850.9375</v>
@@ -12640,109 +12640,109 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G95" t="n">
         <v>2</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M95" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="N95" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O95" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P95" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>5</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S95" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T95" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U95" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V95" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W95" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X95" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD95" t="n">
         <v>2</v>
       </c>
-      <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L95" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M95" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N95" t="n">
-        <v>6</v>
-      </c>
-      <c r="O95" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P95" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>6</v>
-      </c>
-      <c r="R95" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S95" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T95" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U95" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V95" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W95" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X95" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y95" t="n">
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>['23', '53']</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AG95" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI95" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z95" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AA95" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB95" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC95" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD95" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>['31', '45']</t>
-        </is>
-      </c>
-      <c r="AF95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG95" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH95" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AI95" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AJ95" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AK95" s="3" t="n">
         <v>45850.97916666666</v>
@@ -12769,22 +12769,22 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G96" t="n">
         <v>2</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -12795,83 +12795,83 @@
         </is>
       </c>
       <c r="L96" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M96" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="N96" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P96" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R96" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S96" t="n">
+        <v>4</v>
+      </c>
+      <c r="T96" t="n">
+        <v>2</v>
+      </c>
+      <c r="U96" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V96" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W96" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X96" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC96" t="n">
         <v>1.62</v>
       </c>
-      <c r="M96" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="N96" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O96" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P96" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>5</v>
-      </c>
-      <c r="R96" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S96" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T96" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U96" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V96" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W96" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X96" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y96" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z96" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA96" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB96" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC96" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD96" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>['23', '53']</t>
+          <t>['31', '45']</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG96" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AH96" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="AI96" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ96" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
         <v>45850.97916666666</v>
